--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B9" t="n">
-        <v>80018</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R9" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126915632</v>
+        <v>126918800</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674279</v>
+        <v>674103</v>
       </c>
       <c r="R10" t="n">
-        <v>7092915</v>
+        <v>7093056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918793</v>
+        <v>126916005</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674251</v>
+        <v>673879</v>
       </c>
       <c r="R11" t="n">
-        <v>7092837</v>
+        <v>7092985</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918800</v>
+        <v>126918995</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>80021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674103</v>
+        <v>673947</v>
       </c>
       <c r="R12" t="n">
-        <v>7093056</v>
+        <v>7093045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1866,7 +1866,7 @@
         <v>126919065</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126916005</v>
+        <v>126915632</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673879</v>
+        <v>674279</v>
       </c>
       <c r="R14" t="n">
-        <v>7092985</v>
+        <v>7092915</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126915585</v>
+        <v>126918793</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674324</v>
+        <v>674251</v>
       </c>
       <c r="R15" t="n">
-        <v>7093076</v>
+        <v>7092837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126913215</v>
+        <v>126919040</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674258</v>
+        <v>673649</v>
       </c>
       <c r="R16" t="n">
-        <v>7092817</v>
+        <v>7092943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126919040</v>
+        <v>126913215</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673649</v>
+        <v>674258</v>
       </c>
       <c r="R17" t="n">
-        <v>7092943</v>
+        <v>7092817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915606</v>
+        <v>126912574</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674275</v>
+        <v>674224</v>
       </c>
       <c r="R18" t="n">
-        <v>7092845</v>
+        <v>7092965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,48 +2453,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126913188</v>
+        <v>126915627</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>673761</v>
+        <v>674167</v>
       </c>
       <c r="R19" t="n">
-        <v>7092946</v>
+        <v>7093069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,12 +2550,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2570,32 +2566,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126915611</v>
+        <v>126912616</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2605,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674207</v>
+        <v>674220</v>
       </c>
       <c r="R20" t="n">
-        <v>7092810</v>
+        <v>7092919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,48 +2651,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126912574</v>
+        <v>126919035</v>
       </c>
       <c r="B21" t="n">
-        <v>79629</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674224</v>
+        <v>673577</v>
       </c>
       <c r="R21" t="n">
-        <v>7092965</v>
+        <v>7093132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,44 +2748,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126915627</v>
+        <v>126915611</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2803,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674167</v>
+        <v>674207</v>
       </c>
       <c r="R22" t="n">
-        <v>7093069</v>
+        <v>7092810</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,32 +2865,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912616</v>
+        <v>126913188</v>
       </c>
       <c r="B23" t="n">
-        <v>80142</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674220</v>
+        <v>673761</v>
       </c>
       <c r="R23" t="n">
-        <v>7092919</v>
+        <v>7092946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,22 +2950,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126919035</v>
+        <v>126915606</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673577</v>
+        <v>674275</v>
       </c>
       <c r="R24" t="n">
-        <v>7093132</v>
+        <v>7092845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,12 +3051,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3070,7 +3070,7 @@
         <v>126919077</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>126912667</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>126912633</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
         <v>126919071</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>126915593</v>
       </c>
       <c r="B29" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,32 +3564,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126913209</v>
+        <v>126915590</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>58488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674212</v>
+        <v>674272</v>
       </c>
       <c r="R30" t="n">
-        <v>7092826</v>
+        <v>7092912</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3668,7 +3668,7 @@
         <v>126919043</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3766,32 +3766,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126918783</v>
+        <v>126913209</v>
       </c>
       <c r="B32" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674284</v>
+        <v>674212</v>
       </c>
       <c r="R32" t="n">
-        <v>7093057</v>
+        <v>7092826</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126915590</v>
+        <v>126918783</v>
       </c>
       <c r="B33" t="n">
-        <v>58488</v>
+        <v>98463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208245</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674272</v>
+        <v>674284</v>
       </c>
       <c r="R33" t="n">
-        <v>7092912</v>
+        <v>7093057</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3971,7 +3971,7 @@
         <v>126918803</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>126912691</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126912635</v>
+        <v>126912681</v>
       </c>
       <c r="B36" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674239</v>
+        <v>674304</v>
       </c>
       <c r="R36" t="n">
-        <v>7092908</v>
+        <v>7093019</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912681</v>
+        <v>126919078</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674304</v>
+        <v>673893</v>
       </c>
       <c r="R37" t="n">
-        <v>7093019</v>
+        <v>7092920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,44 +4348,48 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919009</v>
+        <v>126913201</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4395,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673944</v>
+        <v>674120</v>
       </c>
       <c r="R38" t="n">
-        <v>7093050</v>
+        <v>7092901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,11 +4437,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4450,12 +4449,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4466,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919078</v>
+        <v>126912635</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,21 +4476,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4501,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673893</v>
+        <v>674239</v>
       </c>
       <c r="R39" t="n">
-        <v>7092920</v>
+        <v>7092908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,26 +4550,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919008</v>
+        <v>126919009</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673843</v>
+        <v>673944</v>
       </c>
       <c r="R40" t="n">
-        <v>7093104</v>
+        <v>7093050</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4638,6 +4633,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4668,32 +4668,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126913201</v>
+        <v>126919008</v>
       </c>
       <c r="B41" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674120</v>
+        <v>673843</v>
       </c>
       <c r="R41" t="n">
-        <v>7092901</v>
+        <v>7093104</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,12 +4753,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4772,7 +4772,7 @@
         <v>126919067</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>126912685</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4967,32 +4967,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912666</v>
+        <v>126915572</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674176</v>
+        <v>674324</v>
       </c>
       <c r="R44" t="n">
-        <v>7093061</v>
+        <v>7093076</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,44 +5052,48 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126915572</v>
+        <v>126919074</v>
       </c>
       <c r="B45" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5099,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674324</v>
+        <v>673796</v>
       </c>
       <c r="R45" t="n">
-        <v>7093076</v>
+        <v>7092899</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,12 +5153,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5165,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913207</v>
+        <v>126912683</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5200,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674182</v>
+        <v>674310</v>
       </c>
       <c r="R46" t="n">
-        <v>7092837</v>
+        <v>7092998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,26 +5254,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919074</v>
+        <v>126912666</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673796</v>
+        <v>674176</v>
       </c>
       <c r="R47" t="n">
-        <v>7092899</v>
+        <v>7093061</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,26 +5351,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912683</v>
+        <v>126913207</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,10 +5398,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674310</v>
+        <v>674182</v>
       </c>
       <c r="R48" t="n">
-        <v>7092998</v>
+        <v>7092837</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,22 +5448,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>126918790</v>
       </c>
       <c r="B49" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>126915612</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126913208</v>
+        <v>126912576</v>
       </c>
       <c r="B51" t="n">
-        <v>91269</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674181</v>
+        <v>674200</v>
       </c>
       <c r="R51" t="n">
-        <v>7092836</v>
+        <v>7092950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,61 +5751,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919076</v>
+        <v>126913179</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>80021</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673836</v>
+        <v>673719</v>
       </c>
       <c r="R52" t="n">
-        <v>7092910</v>
+        <v>7093035</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5846,18 +5845,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,32 +5868,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915630</v>
+        <v>126919076</v>
       </c>
       <c r="B53" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674328</v>
+        <v>673836</v>
       </c>
       <c r="R53" t="n">
-        <v>7092980</v>
+        <v>7092910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5953,12 +5953,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5969,32 +5969,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912700</v>
+        <v>126913208</v>
       </c>
       <c r="B54" t="n">
-        <v>98353</v>
+        <v>91275</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>112</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674267</v>
+        <v>674181</v>
       </c>
       <c r="R54" t="n">
-        <v>7093044</v>
+        <v>7092836</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,73 +6054,61 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913214</v>
+        <v>126915630</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674219</v>
+        <v>674328</v>
       </c>
       <c r="R55" t="n">
-        <v>7092815</v>
+        <v>7092980</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6161,19 +6149,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6184,32 +6171,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126915608</v>
+        <v>126912700</v>
       </c>
       <c r="B56" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6219,10 +6206,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674257</v>
+        <v>674267</v>
       </c>
       <c r="R56" t="n">
-        <v>7092823</v>
+        <v>7093044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6269,48 +6256,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919000</v>
+        <v>126915608</v>
       </c>
       <c r="B57" t="n">
-        <v>78770</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6320,10 +6303,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673939</v>
+        <v>674257</v>
       </c>
       <c r="R57" t="n">
-        <v>7093012</v>
+        <v>7092823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6375,7 +6358,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6386,45 +6369,61 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912576</v>
+        <v>126913214</v>
       </c>
       <c r="B58" t="n">
-        <v>79629</v>
+        <v>98442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674200</v>
+        <v>674219</v>
       </c>
       <c r="R58" t="n">
-        <v>7092950</v>
+        <v>7092815</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,66 +6464,68 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126913179</v>
+        <v>126919000</v>
       </c>
       <c r="B59" t="n">
-        <v>80018</v>
+        <v>78773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673719</v>
+        <v>673939</v>
       </c>
       <c r="R59" t="n">
-        <v>7093035</v>
+        <v>7093012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,19 +6566,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6588,10 +6588,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126913211</v>
+        <v>126919039</v>
       </c>
       <c r="B60" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674214</v>
+        <v>673525</v>
       </c>
       <c r="R60" t="n">
-        <v>7092818</v>
+        <v>7093040</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,12 +6673,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6689,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126919039</v>
+        <v>126913211</v>
       </c>
       <c r="B61" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673525</v>
+        <v>674214</v>
       </c>
       <c r="R61" t="n">
-        <v>7093040</v>
+        <v>7092818</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6774,12 +6774,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6790,32 +6790,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126915584</v>
+        <v>126912622</v>
       </c>
       <c r="B62" t="n">
-        <v>98457</v>
+        <v>78773</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674316</v>
+        <v>674225</v>
       </c>
       <c r="R62" t="n">
-        <v>7092989</v>
+        <v>7092965</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,48 +6875,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918787</v>
+        <v>126912620</v>
       </c>
       <c r="B63" t="n">
-        <v>98457</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674167</v>
+        <v>674229</v>
       </c>
       <c r="R63" t="n">
-        <v>7092848</v>
+        <v>7092964</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,26 +6972,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126912622</v>
+        <v>126918999</v>
       </c>
       <c r="B64" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674225</v>
+        <v>673919</v>
       </c>
       <c r="R64" t="n">
-        <v>7092965</v>
+        <v>7093017</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7077,22 +7069,26 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126912620</v>
+        <v>126918806</v>
       </c>
       <c r="B65" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7100,21 +7096,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7124,10 +7120,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674229</v>
+        <v>674216</v>
       </c>
       <c r="R65" t="n">
-        <v>7092964</v>
+        <v>7092860</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,44 +7170,48 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918999</v>
+        <v>126912592</v>
       </c>
       <c r="B66" t="n">
-        <v>78770</v>
+        <v>80146</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673919</v>
+        <v>674188</v>
       </c>
       <c r="R66" t="n">
-        <v>7093017</v>
+        <v>7092955</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,26 +7271,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126918806</v>
+        <v>126912687</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7322,10 +7318,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674216</v>
+        <v>674226</v>
       </c>
       <c r="R67" t="n">
-        <v>7092860</v>
+        <v>7092929</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7372,48 +7368,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126912687</v>
+        <v>126918996</v>
       </c>
       <c r="B68" t="n">
-        <v>79011</v>
+        <v>80145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7423,10 +7415,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674226</v>
+        <v>673948</v>
       </c>
       <c r="R68" t="n">
-        <v>7092929</v>
+        <v>7093016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7473,22 +7465,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>126919031</v>
       </c>
       <c r="B69" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7586,10 +7582,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126912592</v>
+        <v>126912617</v>
       </c>
       <c r="B70" t="n">
-        <v>80143</v>
+        <v>80145</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7597,21 +7593,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7621,10 +7617,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674188</v>
+        <v>674214</v>
       </c>
       <c r="R70" t="n">
-        <v>7092955</v>
+        <v>7092881</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7683,10 +7679,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918996</v>
+        <v>126915584</v>
       </c>
       <c r="B71" t="n">
-        <v>80142</v>
+        <v>98463</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7694,21 +7690,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7718,10 +7714,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>673948</v>
+        <v>674316</v>
       </c>
       <c r="R71" t="n">
-        <v>7093016</v>
+        <v>7092989</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7773,7 +7769,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7784,10 +7780,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126912617</v>
+        <v>126918787</v>
       </c>
       <c r="B72" t="n">
-        <v>80142</v>
+        <v>98463</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7795,21 +7791,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7819,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>674214</v>
+        <v>674167</v>
       </c>
       <c r="R72" t="n">
-        <v>7092881</v>
+        <v>7092848</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7869,22 +7865,26 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>126912680</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>126919068</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>126912579</v>
       </c>
       <c r="B75" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>126912625</v>
       </c>
       <c r="B77" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>126912669</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8472,32 +8472,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918802</v>
+        <v>126913210</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674315</v>
+        <v>674282</v>
       </c>
       <c r="R79" t="n">
-        <v>7093023</v>
+        <v>7092828</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,12 +8557,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8573,10 +8573,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913210</v>
+        <v>126912599</v>
       </c>
       <c r="B80" t="n">
-        <v>80143</v>
+        <v>98463</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8584,34 +8584,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674282</v>
+        <v>674251</v>
       </c>
       <c r="R80" t="n">
-        <v>7092828</v>
+        <v>7093028</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8658,48 +8663,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918795</v>
+        <v>126918802</v>
       </c>
       <c r="B81" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8709,10 +8710,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674236</v>
+        <v>674315</v>
       </c>
       <c r="R81" t="n">
-        <v>7092852</v>
+        <v>7093023</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8775,50 +8776,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126912599</v>
+        <v>126918795</v>
       </c>
       <c r="B82" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674251</v>
+        <v>674236</v>
       </c>
       <c r="R82" t="n">
-        <v>7093028</v>
+        <v>7092852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8865,22 +8861,26 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>126912668</v>
       </c>
       <c r="B83" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>126912674</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>126912672</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>126912618</v>
       </c>
       <c r="B86" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9265,32 +9265,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912699</v>
+        <v>126915607</v>
       </c>
       <c r="B87" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674260</v>
+        <v>674262</v>
       </c>
       <c r="R87" t="n">
-        <v>7093031</v>
+        <v>7092824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9350,22 +9350,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126919037</v>
+        <v>126913212</v>
       </c>
       <c r="B88" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9397,10 +9401,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>673555</v>
+        <v>674207</v>
       </c>
       <c r="R88" t="n">
-        <v>7093132</v>
+        <v>7092818</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9451,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,10 +9467,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126913212</v>
+        <v>126919037</v>
       </c>
       <c r="B89" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9498,10 +9502,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674207</v>
+        <v>673555</v>
       </c>
       <c r="R89" t="n">
-        <v>7092818</v>
+        <v>7093132</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9552,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,32 +9568,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126915607</v>
+        <v>126912699</v>
       </c>
       <c r="B90" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9603,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674262</v>
+        <v>674260</v>
       </c>
       <c r="R90" t="n">
-        <v>7092824</v>
+        <v>7093031</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,48 +9653,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912614</v>
+        <v>126912578</v>
       </c>
       <c r="B91" t="n">
-        <v>80142</v>
+        <v>79632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674319</v>
+        <v>674218</v>
       </c>
       <c r="R91" t="n">
-        <v>7093047</v>
+        <v>7092914</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918984</v>
+        <v>126913181</v>
       </c>
       <c r="B92" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>673919</v>
+        <v>674236</v>
       </c>
       <c r="R92" t="n">
-        <v>7093017</v>
+        <v>7093024</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9847,12 +9847,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9863,32 +9863,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912703</v>
+        <v>126912614</v>
       </c>
       <c r="B93" t="n">
-        <v>78678</v>
+        <v>80145</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674269</v>
+        <v>674319</v>
       </c>
       <c r="R93" t="n">
-        <v>7092979</v>
+        <v>7093047</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918807</v>
+        <v>126912634</v>
       </c>
       <c r="B94" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674208</v>
+        <v>674203</v>
       </c>
       <c r="R94" t="n">
-        <v>7092856</v>
+        <v>7092932</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,26 +10045,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912578</v>
+        <v>126918789</v>
       </c>
       <c r="B95" t="n">
-        <v>79629</v>
+        <v>78772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10072,21 +10068,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R95" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,22 +10142,26 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126913181</v>
+        <v>126918984</v>
       </c>
       <c r="B96" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674236</v>
+        <v>673919</v>
       </c>
       <c r="R96" t="n">
-        <v>7093024</v>
+        <v>7093017</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10243,12 +10243,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10259,32 +10259,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126919072</v>
+        <v>126915610</v>
       </c>
       <c r="B97" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>673738</v>
+        <v>674211</v>
       </c>
       <c r="R97" t="n">
-        <v>7092885</v>
+        <v>7092807</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,12 +10344,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10360,32 +10360,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126912634</v>
+        <v>126915609</v>
       </c>
       <c r="B98" t="n">
-        <v>78769</v>
+        <v>98442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674203</v>
+        <v>674231</v>
       </c>
       <c r="R98" t="n">
-        <v>7092932</v>
+        <v>7092812</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10445,22 +10445,26 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918789</v>
+        <v>126912624</v>
       </c>
       <c r="B99" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10468,21 +10472,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10492,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R99" t="n">
-        <v>7092997</v>
+        <v>7092914</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10542,48 +10546,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126915609</v>
+        <v>126918807</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674231</v>
+        <v>674208</v>
       </c>
       <c r="R100" t="n">
-        <v>7092812</v>
+        <v>7092856</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10643,12 +10643,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10659,32 +10659,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915610</v>
+        <v>126919072</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10694,10 +10694,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>674211</v>
+        <v>673738</v>
       </c>
       <c r="R101" t="n">
-        <v>7092807</v>
+        <v>7092885</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10744,12 +10744,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10760,10 +10760,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126912624</v>
+        <v>126912703</v>
       </c>
       <c r="B102" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10771,21 +10771,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674218</v>
+        <v>674269</v>
       </c>
       <c r="R102" t="n">
-        <v>7092914</v>
+        <v>7092979</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10857,54 +10857,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912637</v>
+        <v>126912575</v>
       </c>
       <c r="B103" t="n">
-        <v>98436</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674166</v>
+        <v>674215</v>
       </c>
       <c r="R103" t="n">
-        <v>7092881</v>
+        <v>7092959</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10956,61 +10947,52 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912642</v>
+        <v>126912572</v>
       </c>
       <c r="B104" t="n">
-        <v>98436</v>
+        <v>79632</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674117</v>
+        <v>674310</v>
       </c>
       <c r="R104" t="n">
-        <v>7092933</v>
+        <v>7092998</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11062,52 +11044,61 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912679</v>
+        <v>126912637</v>
       </c>
       <c r="B105" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674324</v>
+        <v>674166</v>
       </c>
       <c r="R105" t="n">
-        <v>7093051</v>
+        <v>7092881</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11166,32 +11157,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912671</v>
+        <v>126915582</v>
       </c>
       <c r="B106" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11201,10 +11192,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674238</v>
+        <v>674302</v>
       </c>
       <c r="R106" t="n">
-        <v>7093012</v>
+        <v>7093071</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11251,22 +11242,26 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126913197</v>
+        <v>126912679</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11298,10 +11293,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>673791</v>
+        <v>674324</v>
       </c>
       <c r="R107" t="n">
-        <v>7092931</v>
+        <v>7093051</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11348,26 +11343,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912572</v>
+        <v>126912671</v>
       </c>
       <c r="B108" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11375,21 +11366,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11399,10 +11390,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674310</v>
+        <v>674238</v>
       </c>
       <c r="R108" t="n">
-        <v>7092998</v>
+        <v>7093012</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11461,10 +11452,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126912686</v>
+        <v>126913197</v>
       </c>
       <c r="B109" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11496,10 +11487,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674222</v>
+        <v>673791</v>
       </c>
       <c r="R109" t="n">
-        <v>7092926</v>
+        <v>7092931</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11546,22 +11537,26 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912575</v>
+        <v>126912686</v>
       </c>
       <c r="B110" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11569,21 +11564,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11593,10 +11588,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674215</v>
+        <v>674222</v>
       </c>
       <c r="R110" t="n">
-        <v>7092959</v>
+        <v>7092926</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11655,45 +11650,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126915582</v>
+        <v>126912642</v>
       </c>
       <c r="B111" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674302</v>
+        <v>674117</v>
       </c>
       <c r="R111" t="n">
-        <v>7093071</v>
+        <v>7092933</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11740,26 +11744,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>126912689</v>
       </c>
       <c r="B112" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918801</v>
+        <v>126912577</v>
       </c>
       <c r="B113" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674148</v>
+        <v>674204</v>
       </c>
       <c r="R113" t="n">
-        <v>7093061</v>
+        <v>7092934</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11938,26 +11938,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126912577</v>
+        <v>126918801</v>
       </c>
       <c r="B114" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11965,21 +11961,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11985,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674204</v>
+        <v>674148</v>
       </c>
       <c r="R114" t="n">
-        <v>7092934</v>
+        <v>7093061</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,22 +12035,26 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>126918810</v>
       </c>
       <c r="B115" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>126915628</v>
       </c>
       <c r="B116" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>126918998</v>
       </c>
       <c r="B117" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>126918776</v>
       </c>
       <c r="B118" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12455,32 +12455,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126913194</v>
+        <v>126918808</v>
       </c>
       <c r="B119" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>673917</v>
+        <v>674199</v>
       </c>
       <c r="R119" t="n">
-        <v>7092948</v>
+        <v>7092849</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12540,12 +12540,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12556,32 +12556,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126918778</v>
+        <v>126912708</v>
       </c>
       <c r="B120" t="n">
-        <v>98340</v>
+        <v>77992</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220093</v>
+        <v>6487</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674279</v>
+        <v>674243</v>
       </c>
       <c r="R120" t="n">
-        <v>7092923</v>
+        <v>7092914</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12629,6 +12629,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12641,26 +12646,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126919026</v>
+        <v>126912573</v>
       </c>
       <c r="B121" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12668,21 +12669,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12692,10 +12693,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>673796</v>
+        <v>674270</v>
       </c>
       <c r="R121" t="n">
-        <v>7092899</v>
+        <v>7092973</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12742,48 +12743,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126912623</v>
+        <v>126918778</v>
       </c>
       <c r="B122" t="n">
-        <v>78770</v>
+        <v>98346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12793,10 +12790,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>674215</v>
+        <v>674279</v>
       </c>
       <c r="R122" t="n">
-        <v>7092959</v>
+        <v>7092923</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12843,44 +12840,48 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126918808</v>
+        <v>126913194</v>
       </c>
       <c r="B123" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12890,10 +12891,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>674199</v>
+        <v>673917</v>
       </c>
       <c r="R123" t="n">
-        <v>7092849</v>
+        <v>7092948</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12940,12 +12941,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12956,10 +12957,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126912573</v>
+        <v>126919026</v>
       </c>
       <c r="B124" t="n">
-        <v>79629</v>
+        <v>78773</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12967,21 +12968,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12991,10 +12992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>674270</v>
+        <v>673796</v>
       </c>
       <c r="R124" t="n">
-        <v>7092973</v>
+        <v>7092899</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13041,22 +13042,26 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126912708</v>
+        <v>126912623</v>
       </c>
       <c r="B125" t="n">
-        <v>77989</v>
+        <v>78773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13064,21 +13069,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13088,10 +13093,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>674243</v>
+        <v>674215</v>
       </c>
       <c r="R125" t="n">
-        <v>7092914</v>
+        <v>7092959</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13124,11 +13129,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13155,32 +13155,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126912665</v>
+        <v>126915614</v>
       </c>
       <c r="B126" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>674174</v>
+        <v>674163</v>
       </c>
       <c r="R126" t="n">
-        <v>7093073</v>
+        <v>7092870</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13240,44 +13240,48 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126919003</v>
+        <v>126919036</v>
       </c>
       <c r="B127" t="n">
-        <v>78769</v>
+        <v>98442</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13291,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>673948</v>
+        <v>673559</v>
       </c>
       <c r="R127" t="n">
-        <v>7093011</v>
+        <v>7093141</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13337,12 +13341,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13356,7 +13360,7 @@
         <v>126912690</v>
       </c>
       <c r="B128" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13450,32 +13454,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126912615</v>
+        <v>126912665</v>
       </c>
       <c r="B129" t="n">
-        <v>80142</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13485,10 +13489,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>674322</v>
+        <v>674174</v>
       </c>
       <c r="R129" t="n">
-        <v>7093041</v>
+        <v>7093073</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13547,32 +13551,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126919036</v>
+        <v>126912615</v>
       </c>
       <c r="B130" t="n">
-        <v>98436</v>
+        <v>80145</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13582,10 +13586,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>673559</v>
+        <v>674322</v>
       </c>
       <c r="R130" t="n">
-        <v>7093141</v>
+        <v>7093041</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13632,48 +13636,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126915614</v>
+        <v>126919003</v>
       </c>
       <c r="B131" t="n">
-        <v>98436</v>
+        <v>78772</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>674163</v>
+        <v>673948</v>
       </c>
       <c r="R131" t="n">
-        <v>7092870</v>
+        <v>7093011</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13752,7 +13752,7 @@
         <v>126912682</v>
       </c>
       <c r="B132" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>126912675</v>
       </c>
       <c r="B133" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>126912593</v>
       </c>
       <c r="B134" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14150,45 +14150,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126918997</v>
+        <v>126912638</v>
       </c>
       <c r="B136" t="n">
-        <v>78770</v>
+        <v>98442</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>673855</v>
+        <v>674111</v>
       </c>
       <c r="R136" t="n">
-        <v>7093043</v>
+        <v>7092937</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14235,70 +14244,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126912638</v>
+        <v>126918997</v>
       </c>
       <c r="B137" t="n">
-        <v>98436</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>674111</v>
+        <v>673855</v>
       </c>
       <c r="R137" t="n">
-        <v>7092937</v>
+        <v>7093043</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14345,22 +14341,26 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>126912678</v>
       </c>
       <c r="B138" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>126918805</v>
       </c>
       <c r="B139" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>126918804</v>
       </c>
       <c r="B140" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>126919027</v>
       </c>
       <c r="B141" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>126913193</v>
       </c>
       <c r="B142" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14858,32 +14858,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126915629</v>
+        <v>126919007</v>
       </c>
       <c r="B143" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>674305</v>
+        <v>673940</v>
       </c>
       <c r="R143" t="n">
-        <v>7093077</v>
+        <v>7093045</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14931,12 +14931,18 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14948,7 +14954,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14959,32 +14965,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126919041</v>
+        <v>126912670</v>
       </c>
       <c r="B144" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14994,10 +15000,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>673735</v>
+        <v>674225</v>
       </c>
       <c r="R144" t="n">
-        <v>7092926</v>
+        <v>7093014</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15044,48 +15050,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126919017</v>
+        <v>126912688</v>
       </c>
       <c r="B145" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15095,10 +15097,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>673668</v>
+        <v>674231</v>
       </c>
       <c r="R145" t="n">
-        <v>7092943</v>
+        <v>7092932</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15133,11 +15135,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -15150,26 +15147,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126919007</v>
+        <v>126919075</v>
       </c>
       <c r="B146" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15201,10 +15194,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>673940</v>
+        <v>673825</v>
       </c>
       <c r="R146" t="n">
-        <v>7093045</v>
+        <v>7092923</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15239,30 +15232,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15273,10 +15260,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126912670</v>
+        <v>126912651</v>
       </c>
       <c r="B147" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15308,10 +15295,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>674225</v>
+        <v>674297</v>
       </c>
       <c r="R147" t="n">
-        <v>7093014</v>
+        <v>7092976</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15344,6 +15331,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15370,10 +15362,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126912688</v>
+        <v>126919069</v>
       </c>
       <c r="B148" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15405,10 +15397,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>674231</v>
+        <v>673685</v>
       </c>
       <c r="R148" t="n">
-        <v>7092932</v>
+        <v>7092946</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15455,44 +15447,48 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126919075</v>
+        <v>126915991</v>
       </c>
       <c r="B149" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15502,13 +15498,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>673825</v>
+        <v>673971</v>
       </c>
       <c r="R149" t="n">
-        <v>7092923</v>
+        <v>7092936</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15552,12 +15548,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15568,10 +15564,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126912651</v>
+        <v>126913182</v>
       </c>
       <c r="B150" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15603,10 +15599,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>674297</v>
+        <v>674316</v>
       </c>
       <c r="R150" t="n">
-        <v>7092976</v>
+        <v>7093018</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15641,11 +15637,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -15658,22 +15649,26 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126919069</v>
+        <v>126912676</v>
       </c>
       <c r="B151" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15705,10 +15700,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>673685</v>
+        <v>674259</v>
       </c>
       <c r="R151" t="n">
-        <v>7092946</v>
+        <v>7093064</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15755,48 +15750,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126913182</v>
+        <v>126919017</v>
       </c>
       <c r="B152" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15806,10 +15797,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>674316</v>
+        <v>673668</v>
       </c>
       <c r="R152" t="n">
-        <v>7093018</v>
+        <v>7092943</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15844,6 +15835,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Skrämde tupp</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -15856,12 +15852,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15872,32 +15868,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126912676</v>
+        <v>126915629</v>
       </c>
       <c r="B153" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15907,10 +15903,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>674259</v>
+        <v>674305</v>
       </c>
       <c r="R153" t="n">
-        <v>7093064</v>
+        <v>7093077</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15957,44 +15953,48 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126915991</v>
+        <v>126919041</v>
       </c>
       <c r="B154" t="n">
-        <v>80143</v>
+        <v>98442</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16004,13 +16004,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>673971</v>
+        <v>673735</v>
       </c>
       <c r="R154" t="n">
-        <v>7092936</v>
+        <v>7092926</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16054,12 +16054,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126915603</v>
+        <v>126912692</v>
       </c>
       <c r="B155" t="n">
-        <v>98340</v>
+        <v>79014</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674278</v>
+        <v>674236</v>
       </c>
       <c r="R155" t="n">
-        <v>7092923</v>
+        <v>7092908</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,48 +16155,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126915602</v>
+        <v>126919070</v>
       </c>
       <c r="B156" t="n">
-        <v>98340</v>
+        <v>79014</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16206,10 +16202,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>674319</v>
+        <v>673731</v>
       </c>
       <c r="R156" t="n">
-        <v>7092980</v>
+        <v>7092924</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16256,12 +16252,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16272,32 +16268,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126915613</v>
+        <v>126919063</v>
       </c>
       <c r="B157" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16307,10 +16303,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>674171</v>
+        <v>673530</v>
       </c>
       <c r="R157" t="n">
-        <v>7092865</v>
+        <v>7093126</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16357,12 +16353,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16373,32 +16369,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126918792</v>
+        <v>126915634</v>
       </c>
       <c r="B158" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16408,10 +16404,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674129</v>
+        <v>674163</v>
       </c>
       <c r="R158" t="n">
-        <v>7093003</v>
+        <v>7092870</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16458,12 +16454,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16474,32 +16470,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126912692</v>
+        <v>126915603</v>
       </c>
       <c r="B159" t="n">
-        <v>79011</v>
+        <v>98346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16509,10 +16505,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674236</v>
+        <v>674278</v>
       </c>
       <c r="R159" t="n">
-        <v>7092908</v>
+        <v>7092923</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16559,44 +16555,48 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126919063</v>
+        <v>126915602</v>
       </c>
       <c r="B160" t="n">
-        <v>79011</v>
+        <v>98346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16606,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>673530</v>
+        <v>674319</v>
       </c>
       <c r="R160" t="n">
-        <v>7093126</v>
+        <v>7092980</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16656,12 +16656,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16672,32 +16672,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126919070</v>
+        <v>126915613</v>
       </c>
       <c r="B161" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>673731</v>
+        <v>674171</v>
       </c>
       <c r="R161" t="n">
-        <v>7092924</v>
+        <v>7092865</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16757,12 +16757,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16773,32 +16773,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126915634</v>
+        <v>126918792</v>
       </c>
       <c r="B162" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>674163</v>
+        <v>674129</v>
       </c>
       <c r="R162" t="n">
-        <v>7092870</v>
+        <v>7093003</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,12 +16858,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16877,7 +16877,7 @@
         <v>126912704</v>
       </c>
       <c r="B163" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16971,32 +16971,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126918809</v>
+        <v>126912594</v>
       </c>
       <c r="B164" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674196</v>
+        <v>674121</v>
       </c>
       <c r="R164" t="n">
-        <v>7092846</v>
+        <v>7092931</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17056,48 +17056,44 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126912684</v>
+        <v>126918993</v>
       </c>
       <c r="B165" t="n">
-        <v>79011</v>
+        <v>80021</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17107,10 +17103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>674292</v>
+        <v>673937</v>
       </c>
       <c r="R165" t="n">
-        <v>7092976</v>
+        <v>7093103</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17151,28 +17147,33 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126912594</v>
+        <v>126915599</v>
       </c>
       <c r="B166" t="n">
-        <v>80143</v>
+        <v>98346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17180,21 +17181,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17204,10 +17205,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674121</v>
+        <v>674272</v>
       </c>
       <c r="R166" t="n">
-        <v>7092931</v>
+        <v>7093054</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17254,44 +17255,48 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126918993</v>
+        <v>126918809</v>
       </c>
       <c r="B167" t="n">
-        <v>80018</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17301,10 +17306,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>673937</v>
+        <v>674196</v>
       </c>
       <c r="R167" t="n">
-        <v>7093103</v>
+        <v>7092846</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17345,19 +17350,18 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17368,32 +17372,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126915599</v>
+        <v>126912684</v>
       </c>
       <c r="B168" t="n">
-        <v>98340</v>
+        <v>79014</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17403,10 +17407,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674272</v>
+        <v>674292</v>
       </c>
       <c r="R168" t="n">
-        <v>7093054</v>
+        <v>7092976</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17453,26 +17457,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>126916006</v>
       </c>
       <c r="B169" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>126916008</v>
       </c>
       <c r="B170" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17671,10 +17671,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126915987</v>
+        <v>126915992</v>
       </c>
       <c r="B171" t="n">
-        <v>79600</v>
+        <v>78773</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17682,21 +17682,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17706,10 +17706,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>673839</v>
+        <v>673832</v>
       </c>
       <c r="R171" t="n">
-        <v>7093005</v>
+        <v>7092995</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Liam Sebestyén, Cajsa Björkén, Martin Axegård, Alva Danielsson, Philipp Weiss, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Philipp Weiss, Alva Danielsson, Martin Axegård, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17772,10 +17772,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126915992</v>
+        <v>126915987</v>
       </c>
       <c r="B172" t="n">
-        <v>78770</v>
+        <v>79603</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17783,21 +17783,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17807,10 +17807,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>673832</v>
+        <v>673839</v>
       </c>
       <c r="R172" t="n">
-        <v>7092995</v>
+        <v>7093005</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Liam Sebestyén, Cajsa Björkén, Martin Axegård, Alva Danielsson, Philipp Weiss, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Philipp Weiss, Alva Danielsson, Martin Axegård, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17876,7 +17876,7 @@
         <v>126916003</v>
       </c>
       <c r="B173" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>126916004</v>
       </c>
       <c r="B174" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>126915981</v>
       </c>
       <c r="B175" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Liam Sebestyén, Cajsa Björkén, Martin Axegård, Alva Danielsson, Philipp Weiss, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Philipp Weiss, Alva Danielsson, Martin Axegård, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18184,7 +18184,7 @@
         <v>126916009</v>
       </c>
       <c r="B176" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>126915996</v>
       </c>
       <c r="B177" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>126916002</v>
       </c>
       <c r="B178" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>126915993</v>
       </c>
       <c r="B179" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Liam Sebestyén, Cajsa Björkén, Martin Axegård, Alva Danielsson, Philipp Weiss, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Philipp Weiss, Alva Danielsson, Martin Axegård, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Liam Sebestyén, Cajsa Björkén, Martin Axegård, Alva Danielsson, Philipp Weiss, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Philipp Weiss, Alva Danielsson, Martin Axegård, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -18701,7 +18701,7 @@
         <v>126916000</v>
       </c>
       <c r="B181" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>126915997</v>
       </c>
       <c r="B183" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>126913458</v>
       </c>
       <c r="B184" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>126913469</v>
       </c>
       <c r="B185" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>126913474</v>
       </c>
       <c r="B186" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>126913445</v>
       </c>
       <c r="B187" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>126913472</v>
       </c>
       <c r="B188" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>126913482</v>
       </c>
       <c r="B189" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>126913479</v>
       </c>
       <c r="B190" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>126913478</v>
       </c>
       <c r="B191" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>126913470</v>
       </c>
       <c r="B192" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19929,10 +19929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126913471</v>
+        <v>126913476</v>
       </c>
       <c r="B193" t="n">
-        <v>78769</v>
+        <v>77992</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19940,21 +19940,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>673564</v>
+        <v>673565</v>
       </c>
       <c r="R193" t="n">
-        <v>7093086</v>
+        <v>7093070</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20008,6 +20008,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20030,10 +20031,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126913476</v>
+        <v>126913471</v>
       </c>
       <c r="B194" t="n">
-        <v>77989</v>
+        <v>78772</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20041,21 +20042,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20065,10 +20066,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>673565</v>
+        <v>673564</v>
       </c>
       <c r="R194" t="n">
-        <v>7093070</v>
+        <v>7093086</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20109,7 +20110,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -20135,7 +20135,7 @@
         <v>126913473</v>
       </c>
       <c r="B195" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>126913448</v>
       </c>
       <c r="B196" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>126913475</v>
       </c>
       <c r="B197" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>126913213</v>
       </c>
       <c r="B198" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126915585</v>
+        <v>126918800</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674324</v>
+        <v>674103</v>
       </c>
       <c r="R9" t="n">
-        <v>7093076</v>
+        <v>7093056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918800</v>
+        <v>126919065</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674103</v>
+        <v>673619</v>
       </c>
       <c r="R10" t="n">
-        <v>7093056</v>
+        <v>7092978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B12" t="n">
-        <v>80021</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R12" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919065</v>
+        <v>126918793</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673619</v>
+        <v>674251</v>
       </c>
       <c r="R13" t="n">
-        <v>7092978</v>
+        <v>7092837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126915632</v>
+        <v>126913215</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674279</v>
+        <v>674258</v>
       </c>
       <c r="R14" t="n">
-        <v>7092915</v>
+        <v>7092817</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,7 +2065,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918793</v>
+        <v>126919040</v>
       </c>
       <c r="B15" t="n">
         <v>98442</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674251</v>
+        <v>673649</v>
       </c>
       <c r="R15" t="n">
-        <v>7092837</v>
+        <v>7092943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126919040</v>
+        <v>126918995</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>80021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673649</v>
+        <v>673947</v>
       </c>
       <c r="R16" t="n">
-        <v>7092943</v>
+        <v>7093045</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126913215</v>
+        <v>126915632</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674258</v>
+        <v>674279</v>
       </c>
       <c r="R17" t="n">
-        <v>7092817</v>
+        <v>7092915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912574</v>
+        <v>126915606</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674224</v>
+        <v>674275</v>
       </c>
       <c r="R18" t="n">
-        <v>7092965</v>
+        <v>7092845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,44 +2453,48 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126915627</v>
+        <v>126913188</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674167</v>
+        <v>673761</v>
       </c>
       <c r="R19" t="n">
-        <v>7093069</v>
+        <v>7092946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,12 +2554,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2566,32 +2570,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126912616</v>
+        <v>126915611</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674220</v>
+        <v>674207</v>
       </c>
       <c r="R20" t="n">
-        <v>7092919</v>
+        <v>7092810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,44 +2655,48 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126919035</v>
+        <v>126912616</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673577</v>
+        <v>674220</v>
       </c>
       <c r="R21" t="n">
-        <v>7093132</v>
+        <v>7092919</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,48 +2756,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126915611</v>
+        <v>126912574</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2799,10 +2803,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674207</v>
+        <v>674224</v>
       </c>
       <c r="R22" t="n">
-        <v>7092810</v>
+        <v>7092965</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,48 +2853,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126913188</v>
+        <v>126915627</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673761</v>
+        <v>674167</v>
       </c>
       <c r="R23" t="n">
-        <v>7092946</v>
+        <v>7093069</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,12 +2950,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2966,7 +2966,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126915606</v>
+        <v>126919035</v>
       </c>
       <c r="B24" t="n">
         <v>98442</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674275</v>
+        <v>673577</v>
       </c>
       <c r="R24" t="n">
-        <v>7092845</v>
+        <v>7093132</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,12 +3051,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3665,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126919043</v>
+        <v>126918783</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673945</v>
+        <v>674284</v>
       </c>
       <c r="R31" t="n">
-        <v>7092938</v>
+        <v>7093057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,12 +3750,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126918783</v>
+        <v>126919043</v>
       </c>
       <c r="B33" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674284</v>
+        <v>673945</v>
       </c>
       <c r="R33" t="n">
-        <v>7093057</v>
+        <v>7092938</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4364,32 +4364,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126913201</v>
+        <v>126912635</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>78772</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674120</v>
+        <v>674239</v>
       </c>
       <c r="R38" t="n">
-        <v>7092901</v>
+        <v>7092908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,26 +4449,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912635</v>
+        <v>126919009</v>
       </c>
       <c r="B39" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,21 +4472,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4496,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674239</v>
+        <v>673944</v>
       </c>
       <c r="R39" t="n">
-        <v>7092908</v>
+        <v>7093050</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4538,6 +4534,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4550,19 +4551,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919009</v>
+        <v>126919008</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4597,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673944</v>
+        <v>673843</v>
       </c>
       <c r="R40" t="n">
-        <v>7093050</v>
+        <v>7093104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4633,11 +4638,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4668,32 +4668,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919008</v>
+        <v>126913201</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>673843</v>
+        <v>674120</v>
       </c>
       <c r="R41" t="n">
-        <v>7093104</v>
+        <v>7092901</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,12 +4753,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126919067</v>
+        <v>126915612</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>673610</v>
+        <v>674198</v>
       </c>
       <c r="R42" t="n">
-        <v>7092955</v>
+        <v>7092843</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,12 +4854,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4870,7 +4870,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912685</v>
+        <v>126919067</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674236</v>
+        <v>673610</v>
       </c>
       <c r="R43" t="n">
-        <v>7092969</v>
+        <v>7092955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,15 +4955,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5068,7 +5072,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126919074</v>
+        <v>126913207</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5103,10 +5107,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673796</v>
+        <v>674182</v>
       </c>
       <c r="R45" t="n">
-        <v>7092899</v>
+        <v>7092837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,12 +5157,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5169,7 +5173,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912683</v>
+        <v>126919074</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5204,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674310</v>
+        <v>673796</v>
       </c>
       <c r="R46" t="n">
-        <v>7092998</v>
+        <v>7092899</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,19 +5258,23 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912666</v>
+        <v>126912683</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5301,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674176</v>
+        <v>674310</v>
       </c>
       <c r="R47" t="n">
-        <v>7093061</v>
+        <v>7092998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5363,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126913207</v>
+        <v>126912685</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5398,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674182</v>
+        <v>674236</v>
       </c>
       <c r="R48" t="n">
-        <v>7092837</v>
+        <v>7092969</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,48 +5456,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126918790</v>
+        <v>126912666</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674101</v>
+        <v>674176</v>
       </c>
       <c r="R49" t="n">
-        <v>7092979</v>
+        <v>7093061</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,23 +5553,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126915612</v>
+        <v>126918790</v>
       </c>
       <c r="B50" t="n">
         <v>98442</v>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674198</v>
+        <v>674101</v>
       </c>
       <c r="R50" t="n">
-        <v>7092843</v>
+        <v>7092979</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6261,39 +6261,39 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126915608</v>
+        <v>126919000</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674257</v>
+        <v>673939</v>
       </c>
       <c r="R57" t="n">
-        <v>7092823</v>
+        <v>7093012</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919000</v>
+        <v>126915608</v>
       </c>
       <c r="B59" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673939</v>
+        <v>674257</v>
       </c>
       <c r="R59" t="n">
-        <v>7093012</v>
+        <v>7092823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126919039</v>
+        <v>126912622</v>
       </c>
       <c r="B60" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>673525</v>
+        <v>674225</v>
       </c>
       <c r="R60" t="n">
-        <v>7093040</v>
+        <v>7092965</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,48 +6673,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913211</v>
+        <v>126912620</v>
       </c>
       <c r="B61" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6720,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674214</v>
+        <v>674229</v>
       </c>
       <c r="R61" t="n">
-        <v>7092818</v>
+        <v>7092964</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6774,23 +6770,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912622</v>
+        <v>126918999</v>
       </c>
       <c r="B62" t="n">
         <v>78773</v>
@@ -6825,10 +6817,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674225</v>
+        <v>673919</v>
       </c>
       <c r="R62" t="n">
-        <v>7092965</v>
+        <v>7093017</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,44 +6867,48 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912620</v>
+        <v>126918787</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>98463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6918,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674229</v>
+        <v>674167</v>
       </c>
       <c r="R63" t="n">
-        <v>7092964</v>
+        <v>7092848</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,44 +6968,48 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918999</v>
+        <v>126915584</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>98463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673919</v>
+        <v>674316</v>
       </c>
       <c r="R64" t="n">
-        <v>7093017</v>
+        <v>7092989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7085,32 +7085,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126918806</v>
+        <v>126913211</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674216</v>
+        <v>674214</v>
       </c>
       <c r="R65" t="n">
-        <v>7092860</v>
+        <v>7092818</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7170,12 +7170,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7186,32 +7186,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126912592</v>
+        <v>126919039</v>
       </c>
       <c r="B66" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674188</v>
+        <v>673525</v>
       </c>
       <c r="R66" t="n">
-        <v>7092955</v>
+        <v>7093040</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,19 +7271,23 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126912687</v>
+        <v>126918806</v>
       </c>
       <c r="B67" t="n">
         <v>79014</v>
@@ -7318,10 +7322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674226</v>
+        <v>674216</v>
       </c>
       <c r="R67" t="n">
-        <v>7092929</v>
+        <v>7092860</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,44 +7372,48 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918996</v>
+        <v>126912687</v>
       </c>
       <c r="B68" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7415,10 +7423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673948</v>
+        <v>674226</v>
       </c>
       <c r="R68" t="n">
-        <v>7093016</v>
+        <v>7092929</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,48 +7473,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126919031</v>
+        <v>126912592</v>
       </c>
       <c r="B69" t="n">
-        <v>78772</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7516,10 +7520,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>673796</v>
+        <v>674188</v>
       </c>
       <c r="R69" t="n">
-        <v>7092899</v>
+        <v>7092955</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7566,23 +7570,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126912617</v>
+        <v>126918996</v>
       </c>
       <c r="B70" t="n">
         <v>80145</v>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674214</v>
+        <v>673948</v>
       </c>
       <c r="R70" t="n">
-        <v>7092881</v>
+        <v>7093016</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,22 +7667,26 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126915584</v>
+        <v>126912617</v>
       </c>
       <c r="B71" t="n">
-        <v>98463</v>
+        <v>80145</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7690,21 +7694,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7714,10 +7718,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674316</v>
+        <v>674214</v>
       </c>
       <c r="R71" t="n">
-        <v>7092989</v>
+        <v>7092881</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,48 +7768,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918787</v>
+        <v>126919031</v>
       </c>
       <c r="B72" t="n">
-        <v>98463</v>
+        <v>78772</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>674167</v>
+        <v>673796</v>
       </c>
       <c r="R72" t="n">
-        <v>7092848</v>
+        <v>7092899</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912680</v>
+        <v>126912590</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,34 +7892,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674302</v>
+        <v>673958</v>
       </c>
       <c r="R73" t="n">
-        <v>7093031</v>
+        <v>7093109</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7978,10 +7983,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126919068</v>
+        <v>126912579</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,21 +7994,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8013,10 +8018,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>673630</v>
+        <v>674239</v>
       </c>
       <c r="R74" t="n">
-        <v>7092929</v>
+        <v>7092908</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8063,26 +8068,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912579</v>
+        <v>126912680</v>
       </c>
       <c r="B75" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8090,21 +8091,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8114,10 +8115,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674239</v>
+        <v>674302</v>
       </c>
       <c r="R75" t="n">
-        <v>7092908</v>
+        <v>7093031</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8176,10 +8177,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912590</v>
+        <v>126919068</v>
       </c>
       <c r="B76" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8187,39 +8188,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673958</v>
+        <v>673630</v>
       </c>
       <c r="R76" t="n">
-        <v>7093109</v>
+        <v>7092929</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8266,15 +8262,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126912669</v>
+        <v>126913210</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674218</v>
+        <v>674282</v>
       </c>
       <c r="R78" t="n">
-        <v>7093013</v>
+        <v>7092828</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,44 +8460,48 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913210</v>
+        <v>126912669</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8507,10 +8511,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674282</v>
+        <v>674218</v>
       </c>
       <c r="R79" t="n">
-        <v>7092828</v>
+        <v>7093013</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,66 +8561,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126912599</v>
+        <v>126918802</v>
       </c>
       <c r="B80" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674251</v>
+        <v>674315</v>
       </c>
       <c r="R80" t="n">
-        <v>7093028</v>
+        <v>7093023</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8663,57 +8658,66 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918802</v>
+        <v>126912599</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674315</v>
+        <v>674251</v>
       </c>
       <c r="R81" t="n">
-        <v>7093023</v>
+        <v>7093028</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8760,19 +8764,15 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8877,32 +8877,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126912668</v>
+        <v>126913212</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674214</v>
+        <v>674207</v>
       </c>
       <c r="R83" t="n">
-        <v>7093041</v>
+        <v>7092818</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,44 +8962,48 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126912674</v>
+        <v>126919037</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9009,10 +9013,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674251</v>
+        <v>673555</v>
       </c>
       <c r="R84" t="n">
-        <v>7093028</v>
+        <v>7093132</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9059,44 +9063,48 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912672</v>
+        <v>126912699</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9106,10 +9114,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674248</v>
+        <v>674260</v>
       </c>
       <c r="R85" t="n">
-        <v>7093018</v>
+        <v>7093031</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9161,39 +9169,39 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126912618</v>
+        <v>126915607</v>
       </c>
       <c r="B86" t="n">
-        <v>80145</v>
+        <v>98442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9203,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674104</v>
+        <v>674262</v>
       </c>
       <c r="R86" t="n">
-        <v>7092938</v>
+        <v>7092824</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9253,44 +9261,48 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915607</v>
+        <v>126912668</v>
       </c>
       <c r="B87" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9312,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674262</v>
+        <v>674214</v>
       </c>
       <c r="R87" t="n">
-        <v>7092824</v>
+        <v>7093041</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9350,48 +9362,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126913212</v>
+        <v>126912674</v>
       </c>
       <c r="B88" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9401,10 +9409,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674207</v>
+        <v>674251</v>
       </c>
       <c r="R88" t="n">
-        <v>7092818</v>
+        <v>7093028</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9451,48 +9459,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126919037</v>
+        <v>126912672</v>
       </c>
       <c r="B89" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9502,10 +9506,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>673555</v>
+        <v>674248</v>
       </c>
       <c r="R89" t="n">
-        <v>7093132</v>
+        <v>7093018</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9552,26 +9556,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126912699</v>
+        <v>126912618</v>
       </c>
       <c r="B90" t="n">
-        <v>98359</v>
+        <v>80145</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674260</v>
+        <v>674104</v>
       </c>
       <c r="R90" t="n">
-        <v>7093031</v>
+        <v>7092938</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9665,32 +9665,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912578</v>
+        <v>126912614</v>
       </c>
       <c r="B91" t="n">
-        <v>79632</v>
+        <v>80145</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674218</v>
+        <v>674319</v>
       </c>
       <c r="R91" t="n">
-        <v>7092914</v>
+        <v>7093047</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9863,32 +9863,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912614</v>
+        <v>126912703</v>
       </c>
       <c r="B93" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674319</v>
+        <v>674269</v>
       </c>
       <c r="R93" t="n">
-        <v>7093047</v>
+        <v>7092979</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9953,17 +9953,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126912634</v>
+        <v>126918807</v>
       </c>
       <c r="B94" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674203</v>
+        <v>674208</v>
       </c>
       <c r="R94" t="n">
-        <v>7092932</v>
+        <v>7092856</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,22 +10045,26 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918789</v>
+        <v>126912578</v>
       </c>
       <c r="B95" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10068,21 +10072,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R95" t="n">
-        <v>7092997</v>
+        <v>7092914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10142,26 +10146,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918984</v>
+        <v>126919072</v>
       </c>
       <c r="B96" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10169,21 +10169,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>673919</v>
+        <v>673738</v>
       </c>
       <c r="R96" t="n">
-        <v>7093017</v>
+        <v>7092885</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10243,12 +10243,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10259,32 +10259,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126915610</v>
+        <v>126912634</v>
       </c>
       <c r="B97" t="n">
-        <v>98442</v>
+        <v>78772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674211</v>
+        <v>674203</v>
       </c>
       <c r="R97" t="n">
-        <v>7092807</v>
+        <v>7092932</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,48 +10344,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126915609</v>
+        <v>126918789</v>
       </c>
       <c r="B98" t="n">
-        <v>98442</v>
+        <v>78772</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10395,10 +10391,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674231</v>
+        <v>674310</v>
       </c>
       <c r="R98" t="n">
-        <v>7092812</v>
+        <v>7092997</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10445,12 +10441,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10461,10 +10457,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126912624</v>
+        <v>126918984</v>
       </c>
       <c r="B99" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10472,21 +10468,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10496,10 +10492,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674218</v>
+        <v>673919</v>
       </c>
       <c r="R99" t="n">
-        <v>7092914</v>
+        <v>7093017</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10546,22 +10542,26 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918807</v>
+        <v>126912624</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10569,21 +10569,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674208</v>
+        <v>674218</v>
       </c>
       <c r="R100" t="n">
-        <v>7092856</v>
+        <v>7092914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10643,48 +10643,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126919072</v>
+        <v>126915609</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10694,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>673738</v>
+        <v>674231</v>
       </c>
       <c r="R101" t="n">
-        <v>7092885</v>
+        <v>7092812</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10744,12 +10740,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10760,32 +10756,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126912703</v>
+        <v>126915610</v>
       </c>
       <c r="B102" t="n">
-        <v>78681</v>
+        <v>98442</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10795,10 +10791,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674269</v>
+        <v>674211</v>
       </c>
       <c r="R102" t="n">
-        <v>7092979</v>
+        <v>7092807</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10845,22 +10841,26 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912575</v>
+        <v>126912671</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674215</v>
+        <v>674238</v>
       </c>
       <c r="R103" t="n">
-        <v>7092959</v>
+        <v>7093012</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,10 +10954,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912572</v>
+        <v>126913197</v>
       </c>
       <c r="B104" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10965,21 +10965,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674310</v>
+        <v>673791</v>
       </c>
       <c r="R104" t="n">
-        <v>7092998</v>
+        <v>7092931</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11039,66 +11039,61 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912637</v>
+        <v>126912686</v>
       </c>
       <c r="B105" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674166</v>
+        <v>674222</v>
       </c>
       <c r="R105" t="n">
-        <v>7092881</v>
+        <v>7092926</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11157,32 +11152,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126915582</v>
+        <v>126912575</v>
       </c>
       <c r="B106" t="n">
-        <v>98463</v>
+        <v>79632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11192,10 +11187,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674302</v>
+        <v>674215</v>
       </c>
       <c r="R106" t="n">
-        <v>7093071</v>
+        <v>7092959</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11242,19 +11237,15 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11355,10 +11346,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912671</v>
+        <v>126912572</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11366,21 +11357,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11390,10 +11381,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674238</v>
+        <v>674310</v>
       </c>
       <c r="R108" t="n">
-        <v>7093012</v>
+        <v>7092998</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11452,32 +11443,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126913197</v>
+        <v>126915582</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11487,10 +11478,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>673791</v>
+        <v>674302</v>
       </c>
       <c r="R109" t="n">
-        <v>7092931</v>
+        <v>7093071</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11537,12 +11528,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11553,45 +11544,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912686</v>
+        <v>126912637</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674222</v>
+        <v>674166</v>
       </c>
       <c r="R110" t="n">
-        <v>7092926</v>
+        <v>7092881</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126912577</v>
+        <v>126918801</v>
       </c>
       <c r="B113" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674204</v>
+        <v>674148</v>
       </c>
       <c r="R113" t="n">
-        <v>7092934</v>
+        <v>7093061</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11938,22 +11938,26 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918801</v>
+        <v>126912577</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11961,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11985,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674148</v>
+        <v>674204</v>
       </c>
       <c r="R114" t="n">
-        <v>7093061</v>
+        <v>7092934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12035,19 +12039,15 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12152,32 +12152,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126915628</v>
+        <v>126918998</v>
       </c>
       <c r="B116" t="n">
-        <v>98359</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674258</v>
+        <v>673861</v>
       </c>
       <c r="R116" t="n">
-        <v>7093046</v>
+        <v>7093031</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12253,7 +12253,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918998</v>
+        <v>126918776</v>
       </c>
       <c r="B117" t="n">
         <v>78773</v>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>673861</v>
+        <v>674139</v>
       </c>
       <c r="R117" t="n">
-        <v>7093031</v>
+        <v>7092939</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12338,12 +12338,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12354,32 +12354,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126918776</v>
+        <v>126915628</v>
       </c>
       <c r="B118" t="n">
-        <v>78773</v>
+        <v>98359</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674139</v>
+        <v>674258</v>
       </c>
       <c r="R118" t="n">
-        <v>7092939</v>
+        <v>7093046</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12439,12 +12439,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12455,10 +12455,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126918808</v>
+        <v>126912708</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>674199</v>
+        <v>674243</v>
       </c>
       <c r="R119" t="n">
-        <v>7092849</v>
+        <v>7092914</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12528,6 +12528,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12540,26 +12545,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126912708</v>
+        <v>126918808</v>
       </c>
       <c r="B120" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12567,21 +12568,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12591,10 +12592,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674243</v>
+        <v>674199</v>
       </c>
       <c r="R120" t="n">
-        <v>7092914</v>
+        <v>7092849</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12629,11 +12630,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12646,15 +12642,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12856,32 +12856,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126913194</v>
+        <v>126919026</v>
       </c>
       <c r="B123" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12891,10 +12891,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>673917</v>
+        <v>673796</v>
       </c>
       <c r="R123" t="n">
-        <v>7092948</v>
+        <v>7092899</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,12 +12941,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12957,7 +12957,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126919026</v>
+        <v>126912623</v>
       </c>
       <c r="B124" t="n">
         <v>78773</v>
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>673796</v>
+        <v>674215</v>
       </c>
       <c r="R124" t="n">
-        <v>7092899</v>
+        <v>7092959</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13042,48 +13042,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126912623</v>
+        <v>126913194</v>
       </c>
       <c r="B125" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13093,10 +13089,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>674215</v>
+        <v>673917</v>
       </c>
       <c r="R125" t="n">
-        <v>7092959</v>
+        <v>7092948</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13143,44 +13139,48 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126915614</v>
+        <v>126912690</v>
       </c>
       <c r="B126" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>674163</v>
+        <v>674243</v>
       </c>
       <c r="R126" t="n">
-        <v>7092870</v>
+        <v>7092914</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13240,48 +13240,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126919036</v>
+        <v>126912615</v>
       </c>
       <c r="B127" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13291,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>673559</v>
+        <v>674322</v>
       </c>
       <c r="R127" t="n">
-        <v>7093141</v>
+        <v>7093041</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13341,23 +13337,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126912690</v>
+        <v>126912665</v>
       </c>
       <c r="B128" t="n">
         <v>79014</v>
@@ -13392,10 +13384,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>674243</v>
+        <v>674174</v>
       </c>
       <c r="R128" t="n">
-        <v>7092914</v>
+        <v>7093073</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13454,10 +13446,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126912665</v>
+        <v>126919003</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13465,21 +13457,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13489,10 +13481,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>674174</v>
+        <v>673948</v>
       </c>
       <c r="R129" t="n">
-        <v>7093073</v>
+        <v>7093011</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13539,44 +13531,48 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126912615</v>
+        <v>126919036</v>
       </c>
       <c r="B130" t="n">
-        <v>80145</v>
+        <v>98442</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13586,10 +13582,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>674322</v>
+        <v>673559</v>
       </c>
       <c r="R130" t="n">
-        <v>7093041</v>
+        <v>7093141</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13636,44 +13632,48 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126919003</v>
+        <v>126915614</v>
       </c>
       <c r="B131" t="n">
-        <v>78772</v>
+        <v>98442</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>673948</v>
+        <v>674163</v>
       </c>
       <c r="R131" t="n">
-        <v>7093011</v>
+        <v>7092870</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13749,32 +13749,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126912682</v>
+        <v>126912593</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13784,10 +13784,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>674304</v>
+        <v>674210</v>
       </c>
       <c r="R132" t="n">
-        <v>7093013</v>
+        <v>7092877</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912675</v>
+        <v>126912682</v>
       </c>
       <c r="B133" t="n">
         <v>79014</v>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674268</v>
+        <v>674304</v>
       </c>
       <c r="R133" t="n">
-        <v>7093042</v>
+        <v>7093013</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13943,32 +13943,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126912593</v>
+        <v>126912675</v>
       </c>
       <c r="B134" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>674210</v>
+        <v>674268</v>
       </c>
       <c r="R134" t="n">
-        <v>7092877</v>
+        <v>7093042</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14040,10 +14040,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126913960</v>
+        <v>126918997</v>
       </c>
       <c r="B135" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14051,38 +14051,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>673577</v>
+        <v>673855</v>
       </c>
       <c r="R135" t="n">
-        <v>7093132</v>
+        <v>7093043</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14117,11 +14113,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14134,12 +14125,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14150,54 +14141,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126912638</v>
+        <v>126913960</v>
       </c>
       <c r="B136" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>674111</v>
+        <v>673577</v>
       </c>
       <c r="R136" t="n">
-        <v>7092937</v>
+        <v>7093132</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14232,6 +14218,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14244,57 +14235,70 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126918997</v>
+        <v>126912638</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>98442</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>673855</v>
+        <v>674111</v>
       </c>
       <c r="R137" t="n">
-        <v>7093043</v>
+        <v>7092937</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14341,26 +14345,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126912678</v>
+        <v>126919027</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>674334</v>
+        <v>673554</v>
       </c>
       <c r="R138" t="n">
-        <v>7093055</v>
+        <v>7093135</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,19 +14442,23 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126918805</v>
+        <v>126912678</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -14489,10 +14493,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>674241</v>
+        <v>674334</v>
       </c>
       <c r="R139" t="n">
-        <v>7092850</v>
+        <v>7093055</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14539,23 +14543,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126918804</v>
+        <v>126918805</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -14590,10 +14590,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>674299</v>
+        <v>674241</v>
       </c>
       <c r="R140" t="n">
-        <v>7092979</v>
+        <v>7092850</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14656,10 +14656,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126919027</v>
+        <v>126918804</v>
       </c>
       <c r="B141" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14667,21 +14667,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14691,10 +14691,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>673554</v>
+        <v>674299</v>
       </c>
       <c r="R141" t="n">
-        <v>7093135</v>
+        <v>7092979</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14741,12 +14741,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14858,7 +14858,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126919007</v>
+        <v>126919075</v>
       </c>
       <c r="B143" t="n">
         <v>79014</v>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>673940</v>
+        <v>673825</v>
       </c>
       <c r="R143" t="n">
-        <v>7093045</v>
+        <v>7092923</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14931,30 +14931,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14965,7 +14959,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126912670</v>
+        <v>126919069</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -15000,10 +14994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>674225</v>
+        <v>673685</v>
       </c>
       <c r="R144" t="n">
-        <v>7093014</v>
+        <v>7092946</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15050,19 +15044,23 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126912688</v>
+        <v>126913182</v>
       </c>
       <c r="B145" t="n">
         <v>79014</v>
@@ -15097,10 +15095,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>674231</v>
+        <v>674316</v>
       </c>
       <c r="R145" t="n">
-        <v>7092932</v>
+        <v>7093018</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15147,44 +15145,48 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126919075</v>
+        <v>126919017</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15194,10 +15196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>673825</v>
+        <v>673668</v>
       </c>
       <c r="R146" t="n">
-        <v>7092923</v>
+        <v>7092943</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15230,6 +15232,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15260,32 +15267,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126912651</v>
+        <v>126915991</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15295,13 +15302,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>674297</v>
+        <v>673971</v>
       </c>
       <c r="R147" t="n">
-        <v>7092976</v>
+        <v>7092936</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15331,11 +15338,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15350,19 +15352,23 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126919069</v>
+        <v>126919007</v>
       </c>
       <c r="B148" t="n">
         <v>79014</v>
@@ -15397,10 +15403,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>673685</v>
+        <v>673940</v>
       </c>
       <c r="R148" t="n">
-        <v>7092946</v>
+        <v>7093045</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15435,24 +15441,30 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15463,32 +15475,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126915991</v>
+        <v>126912670</v>
       </c>
       <c r="B149" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15498,13 +15510,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>673971</v>
+        <v>674225</v>
       </c>
       <c r="R149" t="n">
-        <v>7092936</v>
+        <v>7093014</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15548,23 +15560,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126913182</v>
+        <v>126912688</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -15599,10 +15607,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>674316</v>
+        <v>674231</v>
       </c>
       <c r="R150" t="n">
-        <v>7093018</v>
+        <v>7092932</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15649,23 +15657,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126912676</v>
+        <v>126912651</v>
       </c>
       <c r="B151" t="n">
         <v>79014</v>
@@ -15700,10 +15704,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>674259</v>
+        <v>674297</v>
       </c>
       <c r="R151" t="n">
-        <v>7093064</v>
+        <v>7092976</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15736,6 +15740,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15762,32 +15771,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126919017</v>
+        <v>126912676</v>
       </c>
       <c r="B152" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15797,10 +15806,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>673668</v>
+        <v>674259</v>
       </c>
       <c r="R152" t="n">
-        <v>7092943</v>
+        <v>7093064</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15835,11 +15844,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -15852,48 +15856,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126915629</v>
+        <v>126919041</v>
       </c>
       <c r="B153" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>674305</v>
+        <v>673735</v>
       </c>
       <c r="R153" t="n">
-        <v>7093077</v>
+        <v>7092926</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15953,12 +15953,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -15969,32 +15969,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126919041</v>
+        <v>126915629</v>
       </c>
       <c r="B154" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16004,10 +16004,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>673735</v>
+        <v>674305</v>
       </c>
       <c r="R154" t="n">
-        <v>7092926</v>
+        <v>7093077</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16054,12 +16054,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126912692</v>
+        <v>126915634</v>
       </c>
       <c r="B155" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674236</v>
+        <v>674163</v>
       </c>
       <c r="R155" t="n">
-        <v>7092908</v>
+        <v>7092870</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,44 +16155,48 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126919070</v>
+        <v>126915603</v>
       </c>
       <c r="B156" t="n">
-        <v>79014</v>
+        <v>98346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16202,10 +16206,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>673731</v>
+        <v>674278</v>
       </c>
       <c r="R156" t="n">
-        <v>7092924</v>
+        <v>7092923</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16252,12 +16256,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16268,32 +16272,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126919063</v>
+        <v>126915602</v>
       </c>
       <c r="B157" t="n">
-        <v>79014</v>
+        <v>98346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16303,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>673530</v>
+        <v>674319</v>
       </c>
       <c r="R157" t="n">
-        <v>7093126</v>
+        <v>7092980</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16353,12 +16357,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16369,32 +16373,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126915634</v>
+        <v>126912692</v>
       </c>
       <c r="B158" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16404,10 +16408,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674163</v>
+        <v>674236</v>
       </c>
       <c r="R158" t="n">
-        <v>7092870</v>
+        <v>7092908</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16454,48 +16458,44 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126915603</v>
+        <v>126919063</v>
       </c>
       <c r="B159" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16505,10 +16505,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674278</v>
+        <v>673530</v>
       </c>
       <c r="R159" t="n">
-        <v>7092923</v>
+        <v>7093126</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16555,12 +16555,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16571,32 +16571,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126915602</v>
+        <v>126919070</v>
       </c>
       <c r="B160" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16606,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>674319</v>
+        <v>673731</v>
       </c>
       <c r="R160" t="n">
-        <v>7092980</v>
+        <v>7092924</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16656,12 +16656,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16874,32 +16874,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126912704</v>
+        <v>126912594</v>
       </c>
       <c r="B163" t="n">
-        <v>78681</v>
+        <v>80146</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674200</v>
+        <v>674121</v>
       </c>
       <c r="R163" t="n">
-        <v>7092950</v>
+        <v>7092931</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16971,10 +16971,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912594</v>
+        <v>126918993</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>80021</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16982,21 +16982,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674121</v>
+        <v>673937</v>
       </c>
       <c r="R164" t="n">
-        <v>7092931</v>
+        <v>7093103</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17050,50 +17050,55 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126918993</v>
+        <v>126918809</v>
       </c>
       <c r="B165" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17103,10 +17108,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>673937</v>
+        <v>674196</v>
       </c>
       <c r="R165" t="n">
-        <v>7093103</v>
+        <v>7092846</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17147,19 +17152,18 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17170,32 +17174,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126915599</v>
+        <v>126912684</v>
       </c>
       <c r="B166" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17205,10 +17209,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674272</v>
+        <v>674292</v>
       </c>
       <c r="R166" t="n">
-        <v>7093054</v>
+        <v>7092976</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17255,26 +17259,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126918809</v>
+        <v>126912704</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17282,21 +17282,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17306,10 +17306,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>674196</v>
+        <v>674200</v>
       </c>
       <c r="R167" t="n">
-        <v>7092846</v>
+        <v>7092950</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17356,48 +17356,44 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126912684</v>
+        <v>126915599</v>
       </c>
       <c r="B168" t="n">
-        <v>79014</v>
+        <v>98346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17407,10 +17403,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674292</v>
+        <v>674272</v>
       </c>
       <c r="R168" t="n">
-        <v>7092976</v>
+        <v>7093054</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17457,15 +17453,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918800</v>
+        <v>126918793</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674103</v>
+        <v>674251</v>
       </c>
       <c r="R9" t="n">
-        <v>7093056</v>
+        <v>7092837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919065</v>
+        <v>126918800</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673619</v>
+        <v>674103</v>
       </c>
       <c r="R10" t="n">
-        <v>7092978</v>
+        <v>7093056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916005</v>
+        <v>126919065</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673879</v>
+        <v>673619</v>
       </c>
       <c r="R11" t="n">
-        <v>7092985</v>
+        <v>7092978</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126915585</v>
+        <v>126916005</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,21 +1773,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674324</v>
+        <v>673879</v>
       </c>
       <c r="R12" t="n">
-        <v>7093076</v>
+        <v>7092985</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918793</v>
+        <v>126918995</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>80021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674251</v>
+        <v>673947</v>
       </c>
       <c r="R13" t="n">
-        <v>7092837</v>
+        <v>7093045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126913215</v>
+        <v>126915585</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674258</v>
+        <v>674324</v>
       </c>
       <c r="R14" t="n">
-        <v>7092817</v>
+        <v>7093076</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919040</v>
+        <v>126915632</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673649</v>
+        <v>674279</v>
       </c>
       <c r="R15" t="n">
-        <v>7092943</v>
+        <v>7092915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918995</v>
+        <v>126913215</v>
       </c>
       <c r="B16" t="n">
-        <v>80021</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673947</v>
+        <v>674258</v>
       </c>
       <c r="R16" t="n">
-        <v>7093045</v>
+        <v>7092817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126915632</v>
+        <v>126919040</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674279</v>
+        <v>673649</v>
       </c>
       <c r="R17" t="n">
-        <v>7092915</v>
+        <v>7092943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3067,32 +3067,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126919077</v>
+        <v>126915593</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>673852</v>
+        <v>674310</v>
       </c>
       <c r="R25" t="n">
-        <v>7092910</v>
+        <v>7093054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,12 +3152,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3168,7 +3168,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126912667</v>
+        <v>126919077</v>
       </c>
       <c r="B26" t="n">
         <v>79014</v>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674201</v>
+        <v>673852</v>
       </c>
       <c r="R26" t="n">
-        <v>7093054</v>
+        <v>7092910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,22 +3253,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126912633</v>
+        <v>126912667</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,21 +3280,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3304,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674218</v>
+        <v>674201</v>
       </c>
       <c r="R27" t="n">
-        <v>7092957</v>
+        <v>7093054</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3362,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126919071</v>
+        <v>126912633</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673738</v>
+        <v>674218</v>
       </c>
       <c r="R28" t="n">
-        <v>7092907</v>
+        <v>7092957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,48 +3451,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126915593</v>
+        <v>126919071</v>
       </c>
       <c r="B29" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674310</v>
+        <v>673738</v>
       </c>
       <c r="R29" t="n">
-        <v>7093054</v>
+        <v>7092907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,12 +3548,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126915590</v>
+        <v>126918783</v>
       </c>
       <c r="B30" t="n">
-        <v>58488</v>
+        <v>98463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208245</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674272</v>
+        <v>674284</v>
       </c>
       <c r="R30" t="n">
-        <v>7092912</v>
+        <v>7093057</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3665,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918783</v>
+        <v>126913209</v>
       </c>
       <c r="B31" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674284</v>
+        <v>674212</v>
       </c>
       <c r="R31" t="n">
-        <v>7093057</v>
+        <v>7092826</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,12 +3750,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126913209</v>
+        <v>126919043</v>
       </c>
       <c r="B32" t="n">
         <v>98442</v>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674212</v>
+        <v>673945</v>
       </c>
       <c r="R32" t="n">
-        <v>7092826</v>
+        <v>7092938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126919043</v>
+        <v>126915590</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>58488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>673945</v>
+        <v>674272</v>
       </c>
       <c r="R33" t="n">
-        <v>7092938</v>
+        <v>7092912</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915612</v>
+        <v>126912685</v>
       </c>
       <c r="B42" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674198</v>
+        <v>674236</v>
       </c>
       <c r="R42" t="n">
-        <v>7092843</v>
+        <v>7092969</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,23 +4854,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126919067</v>
+        <v>126912666</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4905,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673610</v>
+        <v>674176</v>
       </c>
       <c r="R43" t="n">
-        <v>7092955</v>
+        <v>7093061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,48 +4951,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126915572</v>
+        <v>126919067</v>
       </c>
       <c r="B44" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5006,10 +4998,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674324</v>
+        <v>673610</v>
       </c>
       <c r="R44" t="n">
-        <v>7093076</v>
+        <v>7092955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,12 +5048,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5072,32 +5064,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913207</v>
+        <v>126915572</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5107,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674182</v>
+        <v>674324</v>
       </c>
       <c r="R45" t="n">
-        <v>7092837</v>
+        <v>7093076</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,12 +5149,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5173,7 +5165,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919074</v>
+        <v>126913207</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5208,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673796</v>
+        <v>674182</v>
       </c>
       <c r="R46" t="n">
-        <v>7092899</v>
+        <v>7092837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5258,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5274,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912683</v>
+        <v>126919074</v>
       </c>
       <c r="B47" t="n">
         <v>79014</v>
@@ -5309,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674310</v>
+        <v>673796</v>
       </c>
       <c r="R47" t="n">
-        <v>7092998</v>
+        <v>7092899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,19 +5351,23 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912685</v>
+        <v>126912683</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5406,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674236</v>
+        <v>674310</v>
       </c>
       <c r="R48" t="n">
-        <v>7092969</v>
+        <v>7092998</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,32 +5464,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912666</v>
+        <v>126915612</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674176</v>
+        <v>674198</v>
       </c>
       <c r="R49" t="n">
-        <v>7093061</v>
+        <v>7092843</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5553,15 +5549,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8674,50 +8674,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126912599</v>
+        <v>126918795</v>
       </c>
       <c r="B81" t="n">
-        <v>98463</v>
+        <v>98442</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674251</v>
+        <v>674236</v>
       </c>
       <c r="R81" t="n">
-        <v>7093028</v>
+        <v>7092852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8764,57 +8759,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918795</v>
+        <v>126912599</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674236</v>
+        <v>674251</v>
       </c>
       <c r="R82" t="n">
-        <v>7092852</v>
+        <v>7093028</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8861,19 +8865,15 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11756,32 +11756,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126912689</v>
+        <v>126915628</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674237</v>
+        <v>674258</v>
       </c>
       <c r="R112" t="n">
-        <v>7092921</v>
+        <v>7093046</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,19 +11841,23 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918801</v>
+        <v>126912689</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -11888,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674148</v>
+        <v>674237</v>
       </c>
       <c r="R113" t="n">
-        <v>7093061</v>
+        <v>7092921</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11938,26 +11942,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126912577</v>
+        <v>126918801</v>
       </c>
       <c r="B114" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674204</v>
+        <v>674148</v>
       </c>
       <c r="R114" t="n">
-        <v>7092934</v>
+        <v>7093061</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,22 +12039,26 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918810</v>
+        <v>126912577</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12062,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12086,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674189</v>
+        <v>674204</v>
       </c>
       <c r="R115" t="n">
-        <v>7092854</v>
+        <v>7092934</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12136,26 +12140,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918998</v>
+        <v>126918810</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12163,21 +12163,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>673861</v>
+        <v>674189</v>
       </c>
       <c r="R116" t="n">
-        <v>7093031</v>
+        <v>7092854</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12237,12 +12237,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12253,7 +12253,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918776</v>
+        <v>126918998</v>
       </c>
       <c r="B117" t="n">
         <v>78773</v>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674139</v>
+        <v>673861</v>
       </c>
       <c r="R117" t="n">
-        <v>7092939</v>
+        <v>7093031</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12338,12 +12338,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12354,32 +12354,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126915628</v>
+        <v>126918776</v>
       </c>
       <c r="B118" t="n">
-        <v>98359</v>
+        <v>78773</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674258</v>
+        <v>674139</v>
       </c>
       <c r="R118" t="n">
-        <v>7093046</v>
+        <v>7092939</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12439,12 +12439,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14357,10 +14357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126919027</v>
+        <v>126913193</v>
       </c>
       <c r="B138" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>673554</v>
+        <v>673849</v>
       </c>
       <c r="R138" t="n">
-        <v>7093135</v>
+        <v>7092944</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,12 +14442,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14757,10 +14757,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126913193</v>
+        <v>126919027</v>
       </c>
       <c r="B142" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>673849</v>
+        <v>673554</v>
       </c>
       <c r="R142" t="n">
-        <v>7092944</v>
+        <v>7093135</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -16874,32 +16874,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126912594</v>
+        <v>126912684</v>
       </c>
       <c r="B163" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674121</v>
+        <v>674292</v>
       </c>
       <c r="R163" t="n">
-        <v>7092931</v>
+        <v>7092976</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16971,10 +16971,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126918993</v>
+        <v>126912594</v>
       </c>
       <c r="B164" t="n">
-        <v>80021</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16982,21 +16982,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>673937</v>
+        <v>674121</v>
       </c>
       <c r="R164" t="n">
-        <v>7093103</v>
+        <v>7092931</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17050,55 +17050,50 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126918809</v>
+        <v>126918993</v>
       </c>
       <c r="B165" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17108,10 +17103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>674196</v>
+        <v>673937</v>
       </c>
       <c r="R165" t="n">
-        <v>7092846</v>
+        <v>7093103</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17152,18 +17147,19 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17174,32 +17170,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126912684</v>
+        <v>126915599</v>
       </c>
       <c r="B166" t="n">
-        <v>79014</v>
+        <v>98346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17209,10 +17205,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674292</v>
+        <v>674272</v>
       </c>
       <c r="R166" t="n">
-        <v>7092976</v>
+        <v>7093054</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17259,15 +17255,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17368,32 +17368,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126915599</v>
+        <v>126918809</v>
       </c>
       <c r="B168" t="n">
-        <v>98346</v>
+        <v>79014</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17403,10 +17403,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674272</v>
+        <v>674196</v>
       </c>
       <c r="R168" t="n">
-        <v>7093054</v>
+        <v>7092846</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17453,12 +17453,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -19929,10 +19929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126913476</v>
+        <v>126913471</v>
       </c>
       <c r="B193" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19940,21 +19940,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>673565</v>
+        <v>673564</v>
       </c>
       <c r="R193" t="n">
-        <v>7093070</v>
+        <v>7093086</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20008,7 +20008,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20031,10 +20030,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126913471</v>
+        <v>126913476</v>
       </c>
       <c r="B194" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20042,21 +20041,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20066,10 +20065,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>673564</v>
+        <v>673565</v>
       </c>
       <c r="R194" t="n">
-        <v>7093086</v>
+        <v>7093070</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20110,6 +20109,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918793</v>
+        <v>126919065</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674251</v>
+        <v>673619</v>
       </c>
       <c r="R9" t="n">
-        <v>7092837</v>
+        <v>7092978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918800</v>
+        <v>126916005</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674103</v>
+        <v>673879</v>
       </c>
       <c r="R10" t="n">
-        <v>7093056</v>
+        <v>7092985</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919065</v>
+        <v>126918800</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673619</v>
+        <v>674103</v>
       </c>
       <c r="R11" t="n">
-        <v>7092978</v>
+        <v>7093056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126916005</v>
+        <v>126918995</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673879</v>
+        <v>673947</v>
       </c>
       <c r="R12" t="n">
-        <v>7092985</v>
+        <v>7093045</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B13" t="n">
-        <v>80021</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R13" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126915585</v>
+        <v>126913215</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674324</v>
+        <v>674258</v>
       </c>
       <c r="R14" t="n">
-        <v>7093076</v>
+        <v>7092817</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126915632</v>
+        <v>126919040</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674279</v>
+        <v>673649</v>
       </c>
       <c r="R15" t="n">
-        <v>7092915</v>
+        <v>7092943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126913215</v>
+        <v>126918793</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674258</v>
+        <v>674251</v>
       </c>
       <c r="R16" t="n">
-        <v>7092817</v>
+        <v>7092837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126919040</v>
+        <v>126915632</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673649</v>
+        <v>674279</v>
       </c>
       <c r="R17" t="n">
-        <v>7092943</v>
+        <v>7092915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915606</v>
+        <v>126915627</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674275</v>
+        <v>674167</v>
       </c>
       <c r="R18" t="n">
-        <v>7092845</v>
+        <v>7093069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,32 +2469,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126913188</v>
+        <v>126912574</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>673761</v>
+        <v>674224</v>
       </c>
       <c r="R19" t="n">
-        <v>7092946</v>
+        <v>7092965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,26 +2554,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126915611</v>
+        <v>126913188</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674207</v>
+        <v>673761</v>
       </c>
       <c r="R20" t="n">
-        <v>7092810</v>
+        <v>7092946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,12 +2651,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2671,32 +2667,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126912616</v>
+        <v>126915606</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2702,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674220</v>
+        <v>674275</v>
       </c>
       <c r="R21" t="n">
-        <v>7092919</v>
+        <v>7092845</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,44 +2752,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912574</v>
+        <v>126919035</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674224</v>
+        <v>673577</v>
       </c>
       <c r="R22" t="n">
-        <v>7092965</v>
+        <v>7093132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2853,44 +2853,48 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126915627</v>
+        <v>126915611</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2900,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674167</v>
+        <v>674207</v>
       </c>
       <c r="R23" t="n">
-        <v>7093069</v>
+        <v>7092810</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,32 +2970,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126919035</v>
+        <v>126912616</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3005,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673577</v>
+        <v>674220</v>
       </c>
       <c r="R24" t="n">
-        <v>7093132</v>
+        <v>7092919</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,48 +3055,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126915593</v>
+        <v>126912633</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R25" t="n">
-        <v>7093054</v>
+        <v>7092957</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,48 +3152,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126919077</v>
+        <v>126915590</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>58488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673852</v>
+        <v>674272</v>
       </c>
       <c r="R26" t="n">
-        <v>7092910</v>
+        <v>7092912</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,12 +3249,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3269,32 +3265,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126912667</v>
+        <v>126918783</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3304,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674201</v>
+        <v>674284</v>
       </c>
       <c r="R27" t="n">
-        <v>7093054</v>
+        <v>7093057</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,44 +3350,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912633</v>
+        <v>126913209</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674218</v>
+        <v>674212</v>
       </c>
       <c r="R28" t="n">
-        <v>7092957</v>
+        <v>7092826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,44 +3451,48 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126919071</v>
+        <v>126919043</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673738</v>
+        <v>673945</v>
       </c>
       <c r="R29" t="n">
-        <v>7092907</v>
+        <v>7092938</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,32 +3568,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918783</v>
+        <v>126919077</v>
       </c>
       <c r="B30" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3603,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674284</v>
+        <v>673852</v>
       </c>
       <c r="R30" t="n">
-        <v>7093057</v>
+        <v>7092910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3653,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3665,32 +3669,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126913209</v>
+        <v>126912667</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3704,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674212</v>
+        <v>674201</v>
       </c>
       <c r="R31" t="n">
-        <v>7092826</v>
+        <v>7093054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,48 +3754,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126919043</v>
+        <v>126919071</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>673945</v>
+        <v>673738</v>
       </c>
       <c r="R32" t="n">
-        <v>7092938</v>
+        <v>7092907</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126915590</v>
+        <v>126915593</v>
       </c>
       <c r="B33" t="n">
-        <v>58488</v>
+        <v>80145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208245</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674272</v>
+        <v>674310</v>
       </c>
       <c r="R33" t="n">
-        <v>7092912</v>
+        <v>7093054</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918803</v>
+        <v>126912691</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674314</v>
+        <v>674239</v>
       </c>
       <c r="R34" t="n">
-        <v>7093009</v>
+        <v>7092910</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,23 +4053,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912691</v>
+        <v>126912681</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -4104,10 +4100,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674239</v>
+        <v>674304</v>
       </c>
       <c r="R35" t="n">
-        <v>7092910</v>
+        <v>7093019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4166,7 +4162,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126912681</v>
+        <v>126919078</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4201,10 +4197,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674304</v>
+        <v>673893</v>
       </c>
       <c r="R36" t="n">
-        <v>7093019</v>
+        <v>7092920</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4251,44 +4247,48 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919078</v>
+        <v>126913201</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673893</v>
+        <v>674120</v>
       </c>
       <c r="R37" t="n">
-        <v>7092920</v>
+        <v>7092901</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,12 +4348,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912635</v>
+        <v>126919009</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674239</v>
+        <v>673944</v>
       </c>
       <c r="R38" t="n">
-        <v>7092908</v>
+        <v>7093050</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,6 +4437,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4449,19 +4454,23 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919009</v>
+        <v>126919008</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4496,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673944</v>
+        <v>673843</v>
       </c>
       <c r="R39" t="n">
-        <v>7093050</v>
+        <v>7093104</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4532,11 +4541,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4567,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919008</v>
+        <v>126918803</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4602,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673843</v>
+        <v>674314</v>
       </c>
       <c r="R40" t="n">
-        <v>7093104</v>
+        <v>7093009</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,12 +4656,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4668,32 +4672,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126913201</v>
+        <v>126912635</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>78772</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4707,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674120</v>
+        <v>674239</v>
       </c>
       <c r="R41" t="n">
-        <v>7092901</v>
+        <v>7092908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,19 +4757,15 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4866,32 +4866,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912666</v>
+        <v>126915572</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674176</v>
+        <v>674324</v>
       </c>
       <c r="R43" t="n">
-        <v>7093061</v>
+        <v>7093076</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,19 +4951,23 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126919067</v>
+        <v>126913207</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -4998,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673610</v>
+        <v>674182</v>
       </c>
       <c r="R44" t="n">
-        <v>7092955</v>
+        <v>7092837</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,12 +5052,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5064,32 +5068,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126915572</v>
+        <v>126919067</v>
       </c>
       <c r="B45" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5099,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674324</v>
+        <v>673610</v>
       </c>
       <c r="R45" t="n">
-        <v>7093076</v>
+        <v>7092955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,12 +5153,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5165,7 +5169,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913207</v>
+        <v>126912666</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5200,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674182</v>
+        <v>674176</v>
       </c>
       <c r="R46" t="n">
-        <v>7092837</v>
+        <v>7093061</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,19 +5254,15 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5467,7 +5467,7 @@
         <v>126915612</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>126918790</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912576</v>
+        <v>126913208</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>91276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674200</v>
+        <v>674181</v>
       </c>
       <c r="R51" t="n">
-        <v>7092950</v>
+        <v>7092836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,60 +5751,61 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126913179</v>
+        <v>126919076</v>
       </c>
       <c r="B52" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673719</v>
+        <v>673836</v>
       </c>
       <c r="R52" t="n">
-        <v>7093035</v>
+        <v>7092910</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5845,19 +5846,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126919076</v>
+        <v>126912576</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>673836</v>
+        <v>674200</v>
       </c>
       <c r="R53" t="n">
-        <v>7092910</v>
+        <v>7092950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5953,61 +5953,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913208</v>
+        <v>126913179</v>
       </c>
       <c r="B54" t="n">
-        <v>91275</v>
+        <v>80021</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674181</v>
+        <v>673719</v>
       </c>
       <c r="R54" t="n">
-        <v>7092836</v>
+        <v>7093035</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6048,6 +6047,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>126915630</v>
       </c>
       <c r="B55" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>126912700</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6261,52 +6261,68 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919000</v>
+        <v>126913214</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673939</v>
+        <v>674219</v>
       </c>
       <c r="R57" t="n">
-        <v>7093012</v>
+        <v>7092815</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6347,18 +6363,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6369,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126913214</v>
+        <v>126915608</v>
       </c>
       <c r="B58" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,33 +6414,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674219</v>
+        <v>674257</v>
       </c>
       <c r="R58" t="n">
-        <v>7092815</v>
+        <v>7092823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6464,19 +6465,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126915608</v>
+        <v>126919000</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674257</v>
+        <v>673939</v>
       </c>
       <c r="R59" t="n">
-        <v>7092823</v>
+        <v>7093012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6588,10 +6588,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912622</v>
+        <v>126912687</v>
       </c>
       <c r="B60" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6599,21 +6599,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674225</v>
+        <v>674226</v>
       </c>
       <c r="R60" t="n">
-        <v>7092965</v>
+        <v>7092929</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6685,10 +6685,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912620</v>
+        <v>126918806</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6696,21 +6696,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674229</v>
+        <v>674216</v>
       </c>
       <c r="R61" t="n">
-        <v>7092964</v>
+        <v>7092860</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6770,44 +6770,48 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918999</v>
+        <v>126912592</v>
       </c>
       <c r="B62" t="n">
-        <v>78773</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6817,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673919</v>
+        <v>674188</v>
       </c>
       <c r="R62" t="n">
-        <v>7093017</v>
+        <v>7092955</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6867,26 +6871,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918787</v>
+        <v>126918996</v>
       </c>
       <c r="B63" t="n">
-        <v>98463</v>
+        <v>80145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,21 +6894,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674167</v>
+        <v>673948</v>
       </c>
       <c r="R63" t="n">
-        <v>7092848</v>
+        <v>7093016</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6968,12 +6968,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6984,10 +6984,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126915584</v>
+        <v>126912617</v>
       </c>
       <c r="B64" t="n">
-        <v>98463</v>
+        <v>80145</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6995,21 +6995,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674316</v>
+        <v>674214</v>
       </c>
       <c r="R64" t="n">
-        <v>7092989</v>
+        <v>7092881</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,26 +7069,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>126913211</v>
       </c>
       <c r="B65" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,32 +7182,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126919039</v>
+        <v>126918787</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7221,10 +7217,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673525</v>
+        <v>674167</v>
       </c>
       <c r="R66" t="n">
-        <v>7093040</v>
+        <v>7092848</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,12 +7267,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7287,32 +7283,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126918806</v>
+        <v>126915584</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7322,10 +7318,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674216</v>
+        <v>674316</v>
       </c>
       <c r="R67" t="n">
-        <v>7092860</v>
+        <v>7092989</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7372,12 +7368,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7388,32 +7384,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126912687</v>
+        <v>126919039</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7423,10 +7419,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674226</v>
+        <v>673525</v>
       </c>
       <c r="R68" t="n">
-        <v>7092929</v>
+        <v>7093040</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7473,44 +7469,48 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126912592</v>
+        <v>126919031</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>674188</v>
+        <v>673796</v>
       </c>
       <c r="R69" t="n">
-        <v>7092955</v>
+        <v>7092899</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,44 +7570,48 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918996</v>
+        <v>126912622</v>
       </c>
       <c r="B70" t="n">
-        <v>80145</v>
+        <v>78773</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7617,10 +7621,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>673948</v>
+        <v>674225</v>
       </c>
       <c r="R70" t="n">
-        <v>7093016</v>
+        <v>7092965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,48 +7671,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126912617</v>
+        <v>126912620</v>
       </c>
       <c r="B71" t="n">
-        <v>80145</v>
+        <v>78773</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7718,10 +7718,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674214</v>
+        <v>674229</v>
       </c>
       <c r="R71" t="n">
-        <v>7092881</v>
+        <v>7092964</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126919031</v>
+        <v>126918999</v>
       </c>
       <c r="B72" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7791,21 +7791,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>673796</v>
+        <v>673919</v>
       </c>
       <c r="R72" t="n">
-        <v>7092899</v>
+        <v>7093017</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912590</v>
+        <v>126912680</v>
       </c>
       <c r="B73" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,39 +7892,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>673958</v>
+        <v>674302</v>
       </c>
       <c r="R73" t="n">
-        <v>7093109</v>
+        <v>7093031</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7983,10 +7978,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912579</v>
+        <v>126919068</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7994,21 +7989,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8018,10 +8013,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>674239</v>
+        <v>673630</v>
       </c>
       <c r="R74" t="n">
-        <v>7092908</v>
+        <v>7092929</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8068,22 +8063,26 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912680</v>
+        <v>126912579</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8091,21 +8090,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8115,10 +8114,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674302</v>
+        <v>674239</v>
       </c>
       <c r="R75" t="n">
-        <v>7093031</v>
+        <v>7092908</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8177,10 +8176,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126919068</v>
+        <v>126912590</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,34 +8187,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673630</v>
+        <v>673958</v>
       </c>
       <c r="R76" t="n">
-        <v>7092929</v>
+        <v>7093109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8262,19 +8266,15 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126913210</v>
+        <v>126912669</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674282</v>
+        <v>674218</v>
       </c>
       <c r="R78" t="n">
-        <v>7092828</v>
+        <v>7093013</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,23 +8460,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126912669</v>
+        <v>126918802</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8511,10 +8507,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674218</v>
+        <v>674315</v>
       </c>
       <c r="R79" t="n">
-        <v>7093013</v>
+        <v>7093023</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8561,44 +8557,48 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918802</v>
+        <v>126913210</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674315</v>
+        <v>674282</v>
       </c>
       <c r="R80" t="n">
-        <v>7093023</v>
+        <v>7092828</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8658,12 +8658,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8677,7 +8677,7 @@
         <v>126918795</v>
       </c>
       <c r="B81" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>126912599</v>
       </c>
       <c r="B82" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8877,32 +8877,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126913212</v>
+        <v>126912674</v>
       </c>
       <c r="B83" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674207</v>
+        <v>674251</v>
       </c>
       <c r="R83" t="n">
-        <v>7092818</v>
+        <v>7093028</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,48 +8962,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126919037</v>
+        <v>126912668</v>
       </c>
       <c r="B84" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9013,10 +9009,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>673555</v>
+        <v>674214</v>
       </c>
       <c r="R84" t="n">
-        <v>7093132</v>
+        <v>7093041</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9063,48 +9059,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912699</v>
+        <v>126912672</v>
       </c>
       <c r="B85" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9114,10 +9106,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674260</v>
+        <v>674248</v>
       </c>
       <c r="R85" t="n">
-        <v>7093031</v>
+        <v>7093018</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9169,39 +9161,39 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126915607</v>
+        <v>126912618</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9211,10 +9203,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674262</v>
+        <v>674104</v>
       </c>
       <c r="R86" t="n">
-        <v>7092824</v>
+        <v>7092938</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9261,48 +9253,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912668</v>
+        <v>126912699</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9312,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674214</v>
+        <v>674260</v>
       </c>
       <c r="R87" t="n">
-        <v>7093041</v>
+        <v>7093031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9374,32 +9362,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126912674</v>
+        <v>126919037</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9409,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674251</v>
+        <v>673555</v>
       </c>
       <c r="R88" t="n">
-        <v>7093028</v>
+        <v>7093132</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9459,44 +9447,48 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126912672</v>
+        <v>126915607</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9506,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674248</v>
+        <v>674262</v>
       </c>
       <c r="R89" t="n">
-        <v>7093018</v>
+        <v>7092824</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9556,44 +9548,48 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126912618</v>
+        <v>126913212</v>
       </c>
       <c r="B90" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9603,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674104</v>
+        <v>674207</v>
       </c>
       <c r="R90" t="n">
-        <v>7092938</v>
+        <v>7092818</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9653,44 +9649,48 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912614</v>
+        <v>126915610</v>
       </c>
       <c r="B91" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674319</v>
+        <v>674211</v>
       </c>
       <c r="R91" t="n">
-        <v>7093047</v>
+        <v>7092807</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,44 +9750,48 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126913181</v>
+        <v>126915609</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9797,10 +9801,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674236</v>
+        <v>674231</v>
       </c>
       <c r="R92" t="n">
-        <v>7093024</v>
+        <v>7092812</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9847,12 +9851,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9863,10 +9867,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912703</v>
+        <v>126912624</v>
       </c>
       <c r="B93" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9874,21 +9878,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9902,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674269</v>
+        <v>674218</v>
       </c>
       <c r="R93" t="n">
-        <v>7092979</v>
+        <v>7092914</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9953,17 +9957,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918807</v>
+        <v>126912703</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9975,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9999,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674208</v>
+        <v>674269</v>
       </c>
       <c r="R94" t="n">
-        <v>7092856</v>
+        <v>7092979</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,26 +10049,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912578</v>
+        <v>126913181</v>
       </c>
       <c r="B95" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10072,21 +10072,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674218</v>
+        <v>674236</v>
       </c>
       <c r="R95" t="n">
-        <v>7092914</v>
+        <v>7093024</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,15 +10146,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10259,10 +10263,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126912634</v>
+        <v>126918807</v>
       </c>
       <c r="B97" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,21 +10274,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10298,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674203</v>
+        <v>674208</v>
       </c>
       <c r="R97" t="n">
-        <v>7092932</v>
+        <v>7092856</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,22 +10348,26 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918789</v>
+        <v>126912578</v>
       </c>
       <c r="B98" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10367,21 +10375,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10391,10 +10399,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R98" t="n">
-        <v>7092997</v>
+        <v>7092914</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,26 +10449,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918984</v>
+        <v>126912634</v>
       </c>
       <c r="B99" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10468,21 +10472,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10492,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>673919</v>
+        <v>674203</v>
       </c>
       <c r="R99" t="n">
-        <v>7093017</v>
+        <v>7092932</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10542,26 +10546,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126912624</v>
+        <v>126918789</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10569,21 +10569,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R100" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10643,44 +10643,48 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915609</v>
+        <v>126912614</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10694,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>674231</v>
+        <v>674319</v>
       </c>
       <c r="R101" t="n">
-        <v>7092812</v>
+        <v>7093047</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,48 +10744,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126915610</v>
+        <v>126918984</v>
       </c>
       <c r="B102" t="n">
-        <v>98442</v>
+        <v>79632</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674211</v>
+        <v>673919</v>
       </c>
       <c r="R102" t="n">
-        <v>7092807</v>
+        <v>7093017</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -10857,7 +10857,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912671</v>
+        <v>126912679</v>
       </c>
       <c r="B103" t="n">
         <v>79014</v>
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674238</v>
+        <v>674324</v>
       </c>
       <c r="R103" t="n">
-        <v>7093012</v>
+        <v>7093051</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126913197</v>
+        <v>126912671</v>
       </c>
       <c r="B104" t="n">
         <v>79014</v>
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>673791</v>
+        <v>674238</v>
       </c>
       <c r="R104" t="n">
-        <v>7092931</v>
+        <v>7093012</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11039,23 +11039,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912686</v>
+        <v>126913197</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11090,10 +11086,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674222</v>
+        <v>673791</v>
       </c>
       <c r="R105" t="n">
-        <v>7092926</v>
+        <v>7092931</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11140,22 +11136,26 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912575</v>
+        <v>126912686</v>
       </c>
       <c r="B106" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11163,21 +11163,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674215</v>
+        <v>674222</v>
       </c>
       <c r="R106" t="n">
-        <v>7092959</v>
+        <v>7092926</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11242,17 +11242,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126912679</v>
+        <v>126912575</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11260,21 +11260,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674324</v>
+        <v>674215</v>
       </c>
       <c r="R107" t="n">
-        <v>7093051</v>
+        <v>7092959</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11443,45 +11443,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126915582</v>
+        <v>126912637</v>
       </c>
       <c r="B109" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674302</v>
+        <v>674166</v>
       </c>
       <c r="R109" t="n">
-        <v>7093071</v>
+        <v>7092881</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11528,26 +11537,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912637</v>
+        <v>126912642</v>
       </c>
       <c r="B110" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11574,7 +11579,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11588,10 +11593,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674166</v>
+        <v>674117</v>
       </c>
       <c r="R110" t="n">
-        <v>7092881</v>
+        <v>7092933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11650,54 +11655,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126912642</v>
+        <v>126915582</v>
       </c>
       <c r="B111" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674117</v>
+        <v>674302</v>
       </c>
       <c r="R111" t="n">
-        <v>7092933</v>
+        <v>7093071</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11744,44 +11740,48 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126915628</v>
+        <v>126918801</v>
       </c>
       <c r="B112" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674258</v>
+        <v>674148</v>
       </c>
       <c r="R112" t="n">
-        <v>7093046</v>
+        <v>7093061</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,12 +11841,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -11857,7 +11857,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126912689</v>
+        <v>126918810</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674237</v>
+        <v>674189</v>
       </c>
       <c r="R113" t="n">
-        <v>7092921</v>
+        <v>7092854</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11942,22 +11942,26 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918801</v>
+        <v>126912577</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11965,21 +11969,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11993,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674148</v>
+        <v>674204</v>
       </c>
       <c r="R114" t="n">
-        <v>7093061</v>
+        <v>7092934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,26 +12043,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126912577</v>
+        <v>126912689</v>
       </c>
       <c r="B115" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674204</v>
+        <v>674237</v>
       </c>
       <c r="R115" t="n">
-        <v>7092934</v>
+        <v>7092921</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12152,32 +12152,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918810</v>
+        <v>126915628</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674189</v>
+        <v>674258</v>
       </c>
       <c r="R116" t="n">
-        <v>7092854</v>
+        <v>7093046</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12237,12 +12237,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12455,10 +12455,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126912708</v>
+        <v>126918808</v>
       </c>
       <c r="B119" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>674243</v>
+        <v>674199</v>
       </c>
       <c r="R119" t="n">
-        <v>7092914</v>
+        <v>7092849</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12528,11 +12528,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12545,44 +12540,48 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126918808</v>
+        <v>126918778</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12592,10 +12591,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674199</v>
+        <v>674279</v>
       </c>
       <c r="R120" t="n">
-        <v>7092849</v>
+        <v>7092923</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12755,32 +12754,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126918778</v>
+        <v>126912708</v>
       </c>
       <c r="B122" t="n">
-        <v>98346</v>
+        <v>77992</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220093</v>
+        <v>6487</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12790,10 +12789,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>674279</v>
+        <v>674243</v>
       </c>
       <c r="R122" t="n">
-        <v>7092923</v>
+        <v>7092914</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12828,6 +12827,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12840,48 +12844,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126919026</v>
+        <v>126913194</v>
       </c>
       <c r="B123" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12891,10 +12891,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>673796</v>
+        <v>673917</v>
       </c>
       <c r="R123" t="n">
-        <v>7092899</v>
+        <v>7092948</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,12 +12941,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12957,7 +12957,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126912623</v>
+        <v>126919026</v>
       </c>
       <c r="B124" t="n">
         <v>78773</v>
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>674215</v>
+        <v>673796</v>
       </c>
       <c r="R124" t="n">
-        <v>7092959</v>
+        <v>7092899</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13042,44 +13042,48 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126913194</v>
+        <v>126912623</v>
       </c>
       <c r="B125" t="n">
-        <v>98442</v>
+        <v>78773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13089,10 +13093,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>673917</v>
+        <v>674215</v>
       </c>
       <c r="R125" t="n">
-        <v>7092948</v>
+        <v>7092959</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13139,19 +13143,15 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13252,32 +13252,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126912615</v>
+        <v>126919003</v>
       </c>
       <c r="B127" t="n">
-        <v>80145</v>
+        <v>78772</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>674322</v>
+        <v>673948</v>
       </c>
       <c r="R127" t="n">
-        <v>7093041</v>
+        <v>7093011</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13337,44 +13337,48 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126912665</v>
+        <v>126919036</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13384,10 +13388,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>674174</v>
+        <v>673559</v>
       </c>
       <c r="R128" t="n">
-        <v>7093073</v>
+        <v>7093141</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13434,44 +13438,48 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126919003</v>
+        <v>126915614</v>
       </c>
       <c r="B129" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13481,10 +13489,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>673948</v>
+        <v>674163</v>
       </c>
       <c r="R129" t="n">
-        <v>7093011</v>
+        <v>7092870</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13536,7 +13544,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13547,32 +13555,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126919036</v>
+        <v>126912665</v>
       </c>
       <c r="B130" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13582,10 +13590,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>673559</v>
+        <v>674174</v>
       </c>
       <c r="R130" t="n">
-        <v>7093141</v>
+        <v>7093073</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13632,48 +13640,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126915614</v>
+        <v>126912615</v>
       </c>
       <c r="B131" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13683,10 +13687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>674163</v>
+        <v>674322</v>
       </c>
       <c r="R131" t="n">
-        <v>7092870</v>
+        <v>7093041</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13733,48 +13737,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126912593</v>
+        <v>126912682</v>
       </c>
       <c r="B132" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13784,10 +13784,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>674210</v>
+        <v>674304</v>
       </c>
       <c r="R132" t="n">
-        <v>7092877</v>
+        <v>7093013</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912682</v>
+        <v>126912675</v>
       </c>
       <c r="B133" t="n">
         <v>79014</v>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674304</v>
+        <v>674268</v>
       </c>
       <c r="R133" t="n">
-        <v>7093013</v>
+        <v>7093042</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13943,32 +13943,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126912675</v>
+        <v>126912593</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>674268</v>
+        <v>674210</v>
       </c>
       <c r="R134" t="n">
-        <v>7093042</v>
+        <v>7092877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14040,45 +14040,54 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126918997</v>
+        <v>126912638</v>
       </c>
       <c r="B135" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>673855</v>
+        <v>674111</v>
       </c>
       <c r="R135" t="n">
-        <v>7093043</v>
+        <v>7092937</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14125,26 +14134,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126913960</v>
+        <v>126918997</v>
       </c>
       <c r="B136" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14152,38 +14157,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>673577</v>
+        <v>673855</v>
       </c>
       <c r="R136" t="n">
-        <v>7093132</v>
+        <v>7093043</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14218,11 +14219,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14235,12 +14231,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14251,54 +14247,49 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126912638</v>
+        <v>126913960</v>
       </c>
       <c r="B137" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>674111</v>
+        <v>673577</v>
       </c>
       <c r="R137" t="n">
-        <v>7092937</v>
+        <v>7093132</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14333,6 +14324,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -14345,22 +14341,26 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126913193</v>
+        <v>126912678</v>
       </c>
       <c r="B138" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>673849</v>
+        <v>674334</v>
       </c>
       <c r="R138" t="n">
-        <v>7092944</v>
+        <v>7093055</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,26 +14442,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126912678</v>
+        <v>126919027</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14469,21 +14465,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14493,10 +14489,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>674334</v>
+        <v>673554</v>
       </c>
       <c r="R139" t="n">
-        <v>7093055</v>
+        <v>7093135</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14543,22 +14539,26 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126918805</v>
+        <v>126913193</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14566,21 +14566,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14590,10 +14590,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>674241</v>
+        <v>673849</v>
       </c>
       <c r="R140" t="n">
-        <v>7092850</v>
+        <v>7092944</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14640,12 +14640,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14656,7 +14656,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126918804</v>
+        <v>126918805</v>
       </c>
       <c r="B141" t="n">
         <v>79014</v>
@@ -14691,10 +14691,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>674299</v>
+        <v>674241</v>
       </c>
       <c r="R141" t="n">
-        <v>7092979</v>
+        <v>7092850</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14757,10 +14757,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126919027</v>
+        <v>126918804</v>
       </c>
       <c r="B142" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>673554</v>
+        <v>674299</v>
       </c>
       <c r="R142" t="n">
-        <v>7093135</v>
+        <v>7092979</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -14858,7 +14858,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126919075</v>
+        <v>126912670</v>
       </c>
       <c r="B143" t="n">
         <v>79014</v>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>673825</v>
+        <v>674225</v>
       </c>
       <c r="R143" t="n">
-        <v>7092923</v>
+        <v>7093014</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14943,23 +14943,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126919069</v>
+        <v>126919075</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -14994,10 +14990,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>673685</v>
+        <v>673825</v>
       </c>
       <c r="R144" t="n">
-        <v>7092946</v>
+        <v>7092923</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15060,7 +15056,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126913182</v>
+        <v>126919069</v>
       </c>
       <c r="B145" t="n">
         <v>79014</v>
@@ -15095,10 +15091,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>674316</v>
+        <v>673685</v>
       </c>
       <c r="R145" t="n">
-        <v>7093018</v>
+        <v>7092946</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15145,12 +15141,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15161,32 +15157,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126919017</v>
+        <v>126912676</v>
       </c>
       <c r="B146" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15196,10 +15192,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>673668</v>
+        <v>674259</v>
       </c>
       <c r="R146" t="n">
-        <v>7092943</v>
+        <v>7093064</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15234,11 +15230,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -15251,19 +15242,15 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15368,32 +15355,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126919007</v>
+        <v>126919017</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15403,10 +15390,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>673940</v>
+        <v>673668</v>
       </c>
       <c r="R148" t="n">
-        <v>7093045</v>
+        <v>7092943</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15443,7 +15430,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Äldre tal</t>
+          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15452,19 +15439,18 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15475,32 +15461,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126912670</v>
+        <v>126915629</v>
       </c>
       <c r="B149" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15510,10 +15496,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>674225</v>
+        <v>674305</v>
       </c>
       <c r="R149" t="n">
-        <v>7093014</v>
+        <v>7093077</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15560,19 +15546,23 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126912688</v>
+        <v>126919007</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -15607,10 +15597,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>674231</v>
+        <v>673940</v>
       </c>
       <c r="R150" t="n">
-        <v>7092932</v>
+        <v>7093045</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15645,31 +15635,41 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126912651</v>
+        <v>126912688</v>
       </c>
       <c r="B151" t="n">
         <v>79014</v>
@@ -15704,10 +15704,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>674297</v>
+        <v>674231</v>
       </c>
       <c r="R151" t="n">
-        <v>7092976</v>
+        <v>7092932</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15740,11 +15740,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15771,7 +15766,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126912676</v>
+        <v>126912651</v>
       </c>
       <c r="B152" t="n">
         <v>79014</v>
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>674259</v>
+        <v>674297</v>
       </c>
       <c r="R152" t="n">
-        <v>7093064</v>
+        <v>7092976</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15842,6 +15837,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15868,32 +15868,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126919041</v>
+        <v>126913182</v>
       </c>
       <c r="B153" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>673735</v>
+        <v>674316</v>
       </c>
       <c r="R153" t="n">
-        <v>7092926</v>
+        <v>7093018</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15953,12 +15953,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -15969,32 +15969,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126915629</v>
+        <v>126919041</v>
       </c>
       <c r="B154" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16004,10 +16004,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>674305</v>
+        <v>673735</v>
       </c>
       <c r="R154" t="n">
-        <v>7093077</v>
+        <v>7092926</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16054,12 +16054,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126915634</v>
+        <v>126918792</v>
       </c>
       <c r="B155" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674163</v>
+        <v>674129</v>
       </c>
       <c r="R155" t="n">
-        <v>7092870</v>
+        <v>7093003</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,12 +16155,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16171,10 +16171,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126915603</v>
+        <v>126915634</v>
       </c>
       <c r="B156" t="n">
-        <v>98346</v>
+        <v>98360</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>674278</v>
+        <v>674163</v>
       </c>
       <c r="R156" t="n">
-        <v>7092923</v>
+        <v>7092870</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16272,10 +16272,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126915602</v>
+        <v>126915603</v>
       </c>
       <c r="B157" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16307,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>674319</v>
+        <v>674278</v>
       </c>
       <c r="R157" t="n">
-        <v>7092980</v>
+        <v>7092923</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16373,32 +16373,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126912692</v>
+        <v>126915602</v>
       </c>
       <c r="B158" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16408,10 +16408,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674236</v>
+        <v>674319</v>
       </c>
       <c r="R158" t="n">
-        <v>7092908</v>
+        <v>7092980</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16458,19 +16458,23 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126919063</v>
+        <v>126912692</v>
       </c>
       <c r="B159" t="n">
         <v>79014</v>
@@ -16505,10 +16509,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>673530</v>
+        <v>674236</v>
       </c>
       <c r="R159" t="n">
-        <v>7093126</v>
+        <v>7092908</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16555,23 +16559,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126919070</v>
+        <v>126919063</v>
       </c>
       <c r="B160" t="n">
         <v>79014</v>
@@ -16606,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>673731</v>
+        <v>673530</v>
       </c>
       <c r="R160" t="n">
-        <v>7092924</v>
+        <v>7093126</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16672,32 +16672,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126915613</v>
+        <v>126919070</v>
       </c>
       <c r="B161" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>674171</v>
+        <v>673731</v>
       </c>
       <c r="R161" t="n">
-        <v>7092865</v>
+        <v>7092924</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16757,12 +16757,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16773,10 +16773,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126918792</v>
+        <v>126915613</v>
       </c>
       <c r="B162" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>674129</v>
+        <v>674171</v>
       </c>
       <c r="R162" t="n">
-        <v>7093003</v>
+        <v>7092865</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,12 +16858,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16874,10 +16874,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126912684</v>
+        <v>126912704</v>
       </c>
       <c r="B163" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16885,21 +16885,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674292</v>
+        <v>674200</v>
       </c>
       <c r="R163" t="n">
-        <v>7092976</v>
+        <v>7092950</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16971,32 +16971,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912594</v>
+        <v>126912684</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674121</v>
+        <v>674292</v>
       </c>
       <c r="R164" t="n">
-        <v>7092931</v>
+        <v>7092976</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17068,32 +17068,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126918993</v>
+        <v>126918809</v>
       </c>
       <c r="B165" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>673937</v>
+        <v>674196</v>
       </c>
       <c r="R165" t="n">
-        <v>7093103</v>
+        <v>7092846</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17147,19 +17147,18 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17170,10 +17169,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126915599</v>
+        <v>126912594</v>
       </c>
       <c r="B166" t="n">
-        <v>98346</v>
+        <v>80146</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17181,21 +17180,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17205,10 +17204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674272</v>
+        <v>674121</v>
       </c>
       <c r="R166" t="n">
-        <v>7093054</v>
+        <v>7092931</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17255,48 +17254,44 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126912704</v>
+        <v>126918993</v>
       </c>
       <c r="B167" t="n">
-        <v>78681</v>
+        <v>80021</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17306,10 +17301,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>674200</v>
+        <v>673937</v>
       </c>
       <c r="R167" t="n">
-        <v>7092950</v>
+        <v>7093103</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17350,50 +17345,55 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126918809</v>
+        <v>126915599</v>
       </c>
       <c r="B168" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17403,10 +17403,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674196</v>
+        <v>674272</v>
       </c>
       <c r="R168" t="n">
-        <v>7092846</v>
+        <v>7093054</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17453,12 +17453,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18083,7 +18083,7 @@
         <v>126915981</v>
       </c>
       <c r="B175" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>126915997</v>
       </c>
       <c r="B183" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19929,10 +19929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126913471</v>
+        <v>126913476</v>
       </c>
       <c r="B193" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19940,21 +19940,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>673564</v>
+        <v>673565</v>
       </c>
       <c r="R193" t="n">
-        <v>7093086</v>
+        <v>7093070</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20008,6 +20008,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20030,10 +20031,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126913476</v>
+        <v>126913471</v>
       </c>
       <c r="B194" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20041,21 +20042,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20065,10 +20066,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>673565</v>
+        <v>673564</v>
       </c>
       <c r="R194" t="n">
-        <v>7093070</v>
+        <v>7093086</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20109,7 +20110,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919065</v>
+        <v>126918800</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673619</v>
+        <v>674103</v>
       </c>
       <c r="R9" t="n">
-        <v>7092978</v>
+        <v>7093056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916005</v>
+        <v>126918995</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673879</v>
+        <v>673947</v>
       </c>
       <c r="R10" t="n">
-        <v>7092985</v>
+        <v>7093045</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918800</v>
+        <v>126915585</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674103</v>
+        <v>674324</v>
       </c>
       <c r="R11" t="n">
-        <v>7093056</v>
+        <v>7093076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918995</v>
+        <v>126918793</v>
       </c>
       <c r="B12" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673947</v>
+        <v>674251</v>
       </c>
       <c r="R12" t="n">
-        <v>7093045</v>
+        <v>7092837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126915585</v>
+        <v>126919040</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674324</v>
+        <v>673649</v>
       </c>
       <c r="R13" t="n">
-        <v>7093076</v>
+        <v>7092943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126913215</v>
+        <v>126919065</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674258</v>
+        <v>673619</v>
       </c>
       <c r="R14" t="n">
-        <v>7092817</v>
+        <v>7092978</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919040</v>
+        <v>126916005</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673649</v>
+        <v>673879</v>
       </c>
       <c r="R15" t="n">
-        <v>7092943</v>
+        <v>7092985</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918793</v>
+        <v>126915632</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674251</v>
+        <v>674279</v>
       </c>
       <c r="R16" t="n">
-        <v>7092837</v>
+        <v>7092915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126915632</v>
+        <v>126913215</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674279</v>
+        <v>674258</v>
       </c>
       <c r="R17" t="n">
-        <v>7092915</v>
+        <v>7092817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915627</v>
+        <v>126912574</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674167</v>
+        <v>674224</v>
       </c>
       <c r="R18" t="n">
-        <v>7093069</v>
+        <v>7092965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,48 +2453,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912574</v>
+        <v>126912616</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>80145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674224</v>
+        <v>674220</v>
       </c>
       <c r="R19" t="n">
-        <v>7092965</v>
+        <v>7092919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2562,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126913188</v>
+        <v>126919035</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2601,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673761</v>
+        <v>673577</v>
       </c>
       <c r="R20" t="n">
-        <v>7092946</v>
+        <v>7093132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,12 +2647,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2667,7 +2663,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126915606</v>
+        <v>126915611</v>
       </c>
       <c r="B21" t="n">
         <v>98443</v>
@@ -2702,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674275</v>
+        <v>674207</v>
       </c>
       <c r="R21" t="n">
-        <v>7092845</v>
+        <v>7092810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,32 +2764,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126919035</v>
+        <v>126915627</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2803,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673577</v>
+        <v>674167</v>
       </c>
       <c r="R22" t="n">
-        <v>7093132</v>
+        <v>7093069</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2853,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2869,7 +2865,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126915611</v>
+        <v>126913188</v>
       </c>
       <c r="B23" t="n">
         <v>98443</v>
@@ -2904,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674207</v>
+        <v>673761</v>
       </c>
       <c r="R23" t="n">
-        <v>7092810</v>
+        <v>7092946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,12 +2950,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2970,32 +2966,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126912616</v>
+        <v>126915606</v>
       </c>
       <c r="B24" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3005,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674220</v>
+        <v>674275</v>
       </c>
       <c r="R24" t="n">
-        <v>7092919</v>
+        <v>7092845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,22 +3051,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126912633</v>
+        <v>126919077</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,21 +3078,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674218</v>
+        <v>673852</v>
       </c>
       <c r="R25" t="n">
-        <v>7092957</v>
+        <v>7092910</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,44 +3152,48 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126915590</v>
+        <v>126912667</v>
       </c>
       <c r="B26" t="n">
-        <v>58488</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674272</v>
+        <v>674201</v>
       </c>
       <c r="R26" t="n">
-        <v>7092912</v>
+        <v>7093054</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,48 +3253,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918783</v>
+        <v>126919071</v>
       </c>
       <c r="B27" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674284</v>
+        <v>673738</v>
       </c>
       <c r="R27" t="n">
-        <v>7093057</v>
+        <v>7092907</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,12 +3350,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3366,32 +3366,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126913209</v>
+        <v>126912633</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>78772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674212</v>
+        <v>674218</v>
       </c>
       <c r="R28" t="n">
-        <v>7092826</v>
+        <v>7092957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,48 +3451,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126919043</v>
+        <v>126915593</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3502,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673945</v>
+        <v>674310</v>
       </c>
       <c r="R29" t="n">
-        <v>7092938</v>
+        <v>7093054</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3552,12 +3548,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3568,32 +3564,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126919077</v>
+        <v>126915590</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>58488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3603,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>673852</v>
+        <v>674272</v>
       </c>
       <c r="R30" t="n">
-        <v>7092910</v>
+        <v>7092912</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3669,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912667</v>
+        <v>126918783</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3704,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674201</v>
+        <v>674284</v>
       </c>
       <c r="R31" t="n">
-        <v>7093054</v>
+        <v>7093057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,44 +3750,48 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126919071</v>
+        <v>126913209</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>673738</v>
+        <v>674212</v>
       </c>
       <c r="R32" t="n">
-        <v>7092907</v>
+        <v>7092826</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126915593</v>
+        <v>126919043</v>
       </c>
       <c r="B33" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674310</v>
+        <v>673945</v>
       </c>
       <c r="R33" t="n">
-        <v>7093054</v>
+        <v>7092938</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912685</v>
+        <v>126918790</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674236</v>
+        <v>674101</v>
       </c>
       <c r="R42" t="n">
-        <v>7092969</v>
+        <v>7092979</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,44 +4854,48 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915572</v>
+        <v>126919067</v>
       </c>
       <c r="B43" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674324</v>
+        <v>673610</v>
       </c>
       <c r="R43" t="n">
-        <v>7093076</v>
+        <v>7092955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,12 +4955,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4967,7 +4971,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126913207</v>
+        <v>126912666</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5002,10 +5006,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674182</v>
+        <v>674176</v>
       </c>
       <c r="R44" t="n">
-        <v>7092837</v>
+        <v>7093061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,23 +5056,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126919067</v>
+        <v>126919074</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673610</v>
+        <v>673796</v>
       </c>
       <c r="R45" t="n">
-        <v>7092955</v>
+        <v>7092899</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912666</v>
+        <v>126912683</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674176</v>
+        <v>674310</v>
       </c>
       <c r="R46" t="n">
-        <v>7093061</v>
+        <v>7092998</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,32 +5266,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919074</v>
+        <v>126915612</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673796</v>
+        <v>674198</v>
       </c>
       <c r="R47" t="n">
-        <v>7092899</v>
+        <v>7092843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912683</v>
+        <v>126912685</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674310</v>
+        <v>674236</v>
       </c>
       <c r="R48" t="n">
-        <v>7092998</v>
+        <v>7092969</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5464,32 +5464,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126915612</v>
+        <v>126915572</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674198</v>
+        <v>674324</v>
       </c>
       <c r="R49" t="n">
-        <v>7092843</v>
+        <v>7093076</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,32 +5565,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918790</v>
+        <v>126913207</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674101</v>
+        <v>674182</v>
       </c>
       <c r="R50" t="n">
-        <v>7092979</v>
+        <v>7092837</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5767,45 +5767,61 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919076</v>
+        <v>126913214</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673836</v>
+        <v>674219</v>
       </c>
       <c r="R52" t="n">
-        <v>7092910</v>
+        <v>7092815</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5846,18 +5862,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,32 +5885,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912576</v>
+        <v>126915608</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5920,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674200</v>
+        <v>674257</v>
       </c>
       <c r="R53" t="n">
-        <v>7092950</v>
+        <v>7092823</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5953,60 +5970,61 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913179</v>
+        <v>126919000</v>
       </c>
       <c r="B54" t="n">
-        <v>80021</v>
+        <v>78773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>673719</v>
+        <v>673939</v>
       </c>
       <c r="R54" t="n">
-        <v>7093035</v>
+        <v>7093012</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,19 +6065,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6268,61 +6285,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126913214</v>
+        <v>126919076</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674219</v>
+        <v>673836</v>
       </c>
       <c r="R57" t="n">
-        <v>7092815</v>
+        <v>7092910</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6363,19 +6364,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6386,32 +6386,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126915608</v>
+        <v>126912576</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674257</v>
+        <v>674200</v>
       </c>
       <c r="R58" t="n">
-        <v>7092823</v>
+        <v>7092950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6471,61 +6471,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919000</v>
+        <v>126913179</v>
       </c>
       <c r="B59" t="n">
-        <v>78773</v>
+        <v>80021</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673939</v>
+        <v>673719</v>
       </c>
       <c r="R59" t="n">
-        <v>7093012</v>
+        <v>7093035</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6566,18 +6565,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6786,32 +6786,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912592</v>
+        <v>126919031</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674188</v>
+        <v>673796</v>
       </c>
       <c r="R62" t="n">
-        <v>7092955</v>
+        <v>7092899</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,22 +6871,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918996</v>
+        <v>126912592</v>
       </c>
       <c r="B63" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,21 +6898,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6918,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673948</v>
+        <v>674188</v>
       </c>
       <c r="R63" t="n">
-        <v>7093016</v>
+        <v>7092955</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6968,23 +6972,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126912617</v>
+        <v>126918996</v>
       </c>
       <c r="B64" t="n">
         <v>80145</v>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674214</v>
+        <v>673948</v>
       </c>
       <c r="R64" t="n">
-        <v>7092881</v>
+        <v>7093016</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,44 +7069,48 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126913211</v>
+        <v>126912617</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7119,7 +7123,7 @@
         <v>674214</v>
       </c>
       <c r="R65" t="n">
-        <v>7092818</v>
+        <v>7092881</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,48 +7170,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918787</v>
+        <v>126913211</v>
       </c>
       <c r="B66" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674167</v>
+        <v>674214</v>
       </c>
       <c r="R66" t="n">
-        <v>7092848</v>
+        <v>7092818</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7267,12 +7267,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7283,7 +7283,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126915584</v>
+        <v>126918787</v>
       </c>
       <c r="B67" t="n">
         <v>98464</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674316</v>
+        <v>674167</v>
       </c>
       <c r="R67" t="n">
-        <v>7092989</v>
+        <v>7092848</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,12 +7368,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126919039</v>
+        <v>126915584</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673525</v>
+        <v>674316</v>
       </c>
       <c r="R68" t="n">
-        <v>7093040</v>
+        <v>7092989</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7469,12 +7469,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7485,32 +7485,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126919031</v>
+        <v>126919039</v>
       </c>
       <c r="B69" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>673796</v>
+        <v>673525</v>
       </c>
       <c r="R69" t="n">
-        <v>7092899</v>
+        <v>7093040</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,32 +8375,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126912669</v>
+        <v>126918795</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674218</v>
+        <v>674236</v>
       </c>
       <c r="R78" t="n">
-        <v>7093013</v>
+        <v>7092852</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,57 +8460,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918802</v>
+        <v>126912599</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674315</v>
+        <v>674251</v>
       </c>
       <c r="R79" t="n">
-        <v>7093023</v>
+        <v>7093028</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,48 +8566,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913210</v>
+        <v>126912669</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8608,10 +8613,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674282</v>
+        <v>674218</v>
       </c>
       <c r="R80" t="n">
-        <v>7092828</v>
+        <v>7093013</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8658,48 +8663,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918795</v>
+        <v>126918802</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8709,10 +8710,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674236</v>
+        <v>674315</v>
       </c>
       <c r="R81" t="n">
-        <v>7092852</v>
+        <v>7093023</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8775,10 +8776,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126912599</v>
+        <v>126913210</v>
       </c>
       <c r="B82" t="n">
-        <v>98464</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8786,39 +8787,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674251</v>
+        <v>674282</v>
       </c>
       <c r="R82" t="n">
-        <v>7093028</v>
+        <v>7092828</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8865,44 +8861,48 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126912674</v>
+        <v>126913212</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674251</v>
+        <v>674207</v>
       </c>
       <c r="R83" t="n">
-        <v>7093028</v>
+        <v>7092818</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,19 +8962,23 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126912668</v>
+        <v>126912674</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9009,10 +9013,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674214</v>
+        <v>674251</v>
       </c>
       <c r="R84" t="n">
-        <v>7093041</v>
+        <v>7093028</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9071,7 +9075,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912672</v>
+        <v>126912668</v>
       </c>
       <c r="B85" t="n">
         <v>79014</v>
@@ -9106,10 +9110,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674248</v>
+        <v>674214</v>
       </c>
       <c r="R85" t="n">
-        <v>7093018</v>
+        <v>7093041</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9168,32 +9172,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126912618</v>
+        <v>126912672</v>
       </c>
       <c r="B86" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9203,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674104</v>
+        <v>674248</v>
       </c>
       <c r="R86" t="n">
-        <v>7092938</v>
+        <v>7093018</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9265,10 +9269,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912699</v>
+        <v>126912618</v>
       </c>
       <c r="B87" t="n">
-        <v>98360</v>
+        <v>80145</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9276,21 +9280,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219790</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9304,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674260</v>
+        <v>674104</v>
       </c>
       <c r="R87" t="n">
-        <v>7093031</v>
+        <v>7092938</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9362,32 +9366,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126919037</v>
+        <v>126912699</v>
       </c>
       <c r="B88" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9401,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>673555</v>
+        <v>674260</v>
       </c>
       <c r="R88" t="n">
-        <v>7093132</v>
+        <v>7093031</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,23 +9451,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126915607</v>
+        <v>126919037</v>
       </c>
       <c r="B89" t="n">
         <v>98443</v>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674262</v>
+        <v>673555</v>
       </c>
       <c r="R89" t="n">
-        <v>7092824</v>
+        <v>7093132</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,7 +9564,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126913212</v>
+        <v>126915607</v>
       </c>
       <c r="B90" t="n">
         <v>98443</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674207</v>
+        <v>674262</v>
       </c>
       <c r="R90" t="n">
-        <v>7092818</v>
+        <v>7092824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,32 +9665,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126915610</v>
+        <v>126912624</v>
       </c>
       <c r="B91" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674211</v>
+        <v>674218</v>
       </c>
       <c r="R91" t="n">
-        <v>7092807</v>
+        <v>7092914</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,48 +9750,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126915609</v>
+        <v>126912703</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>78681</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9801,10 +9797,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674231</v>
+        <v>674269</v>
       </c>
       <c r="R92" t="n">
-        <v>7092812</v>
+        <v>7092979</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9851,26 +9847,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912624</v>
+        <v>126913181</v>
       </c>
       <c r="B93" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9878,21 +9870,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9902,10 +9894,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674218</v>
+        <v>674236</v>
       </c>
       <c r="R93" t="n">
-        <v>7092914</v>
+        <v>7093024</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9952,22 +9944,26 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126912703</v>
+        <v>126919072</v>
       </c>
       <c r="B94" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9975,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9999,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674269</v>
+        <v>673738</v>
       </c>
       <c r="R94" t="n">
-        <v>7092979</v>
+        <v>7092885</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10049,19 +10045,23 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126913181</v>
+        <v>126918807</v>
       </c>
       <c r="B95" t="n">
         <v>79014</v>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674236</v>
+        <v>674208</v>
       </c>
       <c r="R95" t="n">
-        <v>7093024</v>
+        <v>7092856</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,12 +10146,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10162,10 +10162,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126919072</v>
+        <v>126912578</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10173,21 +10173,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>673738</v>
+        <v>674218</v>
       </c>
       <c r="R96" t="n">
-        <v>7092885</v>
+        <v>7092914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10247,26 +10247,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918807</v>
+        <v>126912634</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10274,21 +10270,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10298,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674208</v>
+        <v>674203</v>
       </c>
       <c r="R97" t="n">
-        <v>7092856</v>
+        <v>7092932</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10348,26 +10344,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126912578</v>
+        <v>126918789</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10375,21 +10367,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10399,10 +10391,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R98" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10449,44 +10441,48 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126912634</v>
+        <v>126912614</v>
       </c>
       <c r="B99" t="n">
-        <v>78772</v>
+        <v>80145</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10496,10 +10492,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674203</v>
+        <v>674319</v>
       </c>
       <c r="R99" t="n">
-        <v>7092932</v>
+        <v>7093047</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10558,10 +10554,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918789</v>
+        <v>126918984</v>
       </c>
       <c r="B100" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10569,21 +10565,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10589,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674310</v>
+        <v>673919</v>
       </c>
       <c r="R100" t="n">
-        <v>7092997</v>
+        <v>7093017</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10643,12 +10639,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10659,32 +10655,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126912614</v>
+        <v>126915610</v>
       </c>
       <c r="B101" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10694,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>674319</v>
+        <v>674211</v>
       </c>
       <c r="R101" t="n">
-        <v>7093047</v>
+        <v>7092807</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10744,44 +10740,48 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126918984</v>
+        <v>126915609</v>
       </c>
       <c r="B102" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>673919</v>
+        <v>674231</v>
       </c>
       <c r="R102" t="n">
-        <v>7093017</v>
+        <v>7092812</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11249,32 +11249,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126912575</v>
+        <v>126915582</v>
       </c>
       <c r="B107" t="n">
-        <v>79632</v>
+        <v>98464</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674215</v>
+        <v>674302</v>
       </c>
       <c r="R107" t="n">
-        <v>7092959</v>
+        <v>7093071</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11334,57 +11334,70 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912572</v>
+        <v>126912637</v>
       </c>
       <c r="B108" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674310</v>
+        <v>674166</v>
       </c>
       <c r="R108" t="n">
-        <v>7092998</v>
+        <v>7092881</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11443,7 +11456,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126912637</v>
+        <v>126912642</v>
       </c>
       <c r="B109" t="n">
         <v>98443</v>
@@ -11473,7 +11486,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11487,10 +11500,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674166</v>
+        <v>674117</v>
       </c>
       <c r="R109" t="n">
-        <v>7092881</v>
+        <v>7092933</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11549,54 +11562,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912642</v>
+        <v>126912575</v>
       </c>
       <c r="B110" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674117</v>
+        <v>674215</v>
       </c>
       <c r="R110" t="n">
-        <v>7092933</v>
+        <v>7092959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11655,32 +11659,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126915582</v>
+        <v>126912572</v>
       </c>
       <c r="B111" t="n">
-        <v>98464</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674302</v>
+        <v>674310</v>
       </c>
       <c r="R111" t="n">
-        <v>7093071</v>
+        <v>7092998</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11740,23 +11744,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918801</v>
+        <v>126912689</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674148</v>
+        <v>674237</v>
       </c>
       <c r="R112" t="n">
-        <v>7093061</v>
+        <v>7092921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,48 +11841,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918810</v>
+        <v>126915628</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11892,10 +11888,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674189</v>
+        <v>674258</v>
       </c>
       <c r="R113" t="n">
-        <v>7092854</v>
+        <v>7093046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11942,12 +11938,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11958,10 +11954,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126912577</v>
+        <v>126918998</v>
       </c>
       <c r="B114" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11969,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11993,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674204</v>
+        <v>673861</v>
       </c>
       <c r="R114" t="n">
-        <v>7092934</v>
+        <v>7093031</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12043,22 +12039,26 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126912689</v>
+        <v>126918776</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674237</v>
+        <v>674139</v>
       </c>
       <c r="R115" t="n">
-        <v>7092921</v>
+        <v>7092939</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12140,44 +12140,48 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126915628</v>
+        <v>126918801</v>
       </c>
       <c r="B116" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12191,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674258</v>
+        <v>674148</v>
       </c>
       <c r="R116" t="n">
-        <v>7093046</v>
+        <v>7093061</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12237,12 +12241,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12253,10 +12257,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918998</v>
+        <v>126918810</v>
       </c>
       <c r="B117" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12264,21 +12268,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12288,10 +12292,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>673861</v>
+        <v>674189</v>
       </c>
       <c r="R117" t="n">
-        <v>7093031</v>
+        <v>7092854</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12338,12 +12342,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12354,10 +12358,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126918776</v>
+        <v>126912577</v>
       </c>
       <c r="B118" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12365,21 +12369,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12393,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674139</v>
+        <v>674204</v>
       </c>
       <c r="R118" t="n">
-        <v>7092939</v>
+        <v>7092934</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12439,26 +12443,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126918808</v>
+        <v>126912708</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>674199</v>
+        <v>674243</v>
       </c>
       <c r="R119" t="n">
-        <v>7092849</v>
+        <v>7092914</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12528,6 +12528,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12540,19 +12545,15 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12657,32 +12658,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126912573</v>
+        <v>126913194</v>
       </c>
       <c r="B121" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12692,10 +12693,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>674270</v>
+        <v>673917</v>
       </c>
       <c r="R121" t="n">
-        <v>7092973</v>
+        <v>7092948</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12742,22 +12743,26 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126912708</v>
+        <v>126919026</v>
       </c>
       <c r="B122" t="n">
-        <v>77992</v>
+        <v>78773</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12765,21 +12770,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12789,10 +12794,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>674243</v>
+        <v>673796</v>
       </c>
       <c r="R122" t="n">
-        <v>7092914</v>
+        <v>7092899</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12827,11 +12832,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12844,44 +12844,48 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126913194</v>
+        <v>126912623</v>
       </c>
       <c r="B123" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12891,10 +12895,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>673917</v>
+        <v>674215</v>
       </c>
       <c r="R123" t="n">
-        <v>7092948</v>
+        <v>7092959</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,26 +12945,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126919026</v>
+        <v>126918808</v>
       </c>
       <c r="B124" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12968,21 +12968,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>673796</v>
+        <v>674199</v>
       </c>
       <c r="R124" t="n">
-        <v>7092899</v>
+        <v>7092849</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13042,12 +13042,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13058,10 +13058,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126912623</v>
+        <v>126912573</v>
       </c>
       <c r="B125" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13069,21 +13069,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>674215</v>
+        <v>674270</v>
       </c>
       <c r="R125" t="n">
-        <v>7092959</v>
+        <v>7092973</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13252,10 +13252,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126919003</v>
+        <v>126912665</v>
       </c>
       <c r="B127" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13263,21 +13263,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>673948</v>
+        <v>674174</v>
       </c>
       <c r="R127" t="n">
-        <v>7093011</v>
+        <v>7093073</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13337,19 +13337,15 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13555,10 +13551,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126912665</v>
+        <v>126919003</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13566,21 +13562,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13590,10 +13586,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>674174</v>
+        <v>673948</v>
       </c>
       <c r="R130" t="n">
-        <v>7093073</v>
+        <v>7093011</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13640,15 +13636,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14040,54 +14040,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126912638</v>
+        <v>126913960</v>
       </c>
       <c r="B135" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>674111</v>
+        <v>673577</v>
       </c>
       <c r="R135" t="n">
-        <v>7092937</v>
+        <v>7093132</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14122,6 +14117,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14134,57 +14134,70 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126918997</v>
+        <v>126912638</v>
       </c>
       <c r="B136" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>673855</v>
+        <v>674111</v>
       </c>
       <c r="R136" t="n">
-        <v>7093043</v>
+        <v>7092937</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14231,26 +14244,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126913960</v>
+        <v>126918997</v>
       </c>
       <c r="B137" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14258,38 +14267,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>673577</v>
+        <v>673855</v>
       </c>
       <c r="R137" t="n">
-        <v>7093132</v>
+        <v>7093043</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14324,11 +14329,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -14341,12 +14341,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -19929,10 +19929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126913476</v>
+        <v>126913471</v>
       </c>
       <c r="B193" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19940,21 +19940,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>673565</v>
+        <v>673564</v>
       </c>
       <c r="R193" t="n">
-        <v>7093070</v>
+        <v>7093086</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20008,7 +20008,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20031,10 +20030,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126913471</v>
+        <v>126913476</v>
       </c>
       <c r="B194" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20042,21 +20041,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20066,10 +20065,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>673564</v>
+        <v>673565</v>
       </c>
       <c r="R194" t="n">
-        <v>7093086</v>
+        <v>7093070</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20110,6 +20109,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918800</v>
+        <v>126919065</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674103</v>
+        <v>673619</v>
       </c>
       <c r="R9" t="n">
-        <v>7093056</v>
+        <v>7092978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918995</v>
+        <v>126918800</v>
       </c>
       <c r="B10" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673947</v>
+        <v>674103</v>
       </c>
       <c r="R10" t="n">
-        <v>7093045</v>
+        <v>7093056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126915585</v>
+        <v>126916005</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674324</v>
+        <v>673879</v>
       </c>
       <c r="R11" t="n">
-        <v>7093076</v>
+        <v>7092985</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918793</v>
+        <v>126918995</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>80021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674251</v>
+        <v>673947</v>
       </c>
       <c r="R12" t="n">
-        <v>7092837</v>
+        <v>7093045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919040</v>
+        <v>126915585</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673649</v>
+        <v>674324</v>
       </c>
       <c r="R13" t="n">
-        <v>7092943</v>
+        <v>7093076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919065</v>
+        <v>126919040</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673619</v>
+        <v>673649</v>
       </c>
       <c r="R14" t="n">
-        <v>7092978</v>
+        <v>7092943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126916005</v>
+        <v>126918793</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673879</v>
+        <v>674251</v>
       </c>
       <c r="R15" t="n">
-        <v>7092985</v>
+        <v>7092837</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126915632</v>
+        <v>126913215</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674279</v>
+        <v>674258</v>
       </c>
       <c r="R16" t="n">
-        <v>7092915</v>
+        <v>7092817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126913215</v>
+        <v>126915632</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674258</v>
+        <v>674279</v>
       </c>
       <c r="R17" t="n">
-        <v>7092817</v>
+        <v>7092915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912574</v>
+        <v>126915627</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674224</v>
+        <v>674167</v>
       </c>
       <c r="R18" t="n">
-        <v>7092965</v>
+        <v>7093069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,44 +2453,48 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912616</v>
+        <v>126912574</v>
       </c>
       <c r="B19" t="n">
-        <v>80145</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674220</v>
+        <v>674224</v>
       </c>
       <c r="R19" t="n">
-        <v>7092919</v>
+        <v>7092965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,32 +2566,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126919035</v>
+        <v>126912616</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673577</v>
+        <v>674220</v>
       </c>
       <c r="R20" t="n">
-        <v>7093132</v>
+        <v>7092919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,23 +2651,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126915611</v>
+        <v>126919035</v>
       </c>
       <c r="B21" t="n">
         <v>98443</v>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674207</v>
+        <v>673577</v>
       </c>
       <c r="R21" t="n">
-        <v>7092810</v>
+        <v>7093132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,12 +2748,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2764,32 +2764,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126915627</v>
+        <v>126915611</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674167</v>
+        <v>674207</v>
       </c>
       <c r="R22" t="n">
-        <v>7093069</v>
+        <v>7092810</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126919077</v>
+        <v>126912667</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>673852</v>
+        <v>674201</v>
       </c>
       <c r="R25" t="n">
-        <v>7092910</v>
+        <v>7093054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,26 +3152,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126912667</v>
+        <v>126912633</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674201</v>
+        <v>674218</v>
       </c>
       <c r="R26" t="n">
-        <v>7093054</v>
+        <v>7092957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,32 +3261,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126919071</v>
+        <v>126915593</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>673738</v>
+        <v>674310</v>
       </c>
       <c r="R27" t="n">
-        <v>7092907</v>
+        <v>7093054</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,12 +3346,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3366,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912633</v>
+        <v>126919071</v>
       </c>
       <c r="B28" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,21 +3373,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674218</v>
+        <v>673738</v>
       </c>
       <c r="R28" t="n">
-        <v>7092957</v>
+        <v>7092907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,44 +3447,48 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126915593</v>
+        <v>126919077</v>
       </c>
       <c r="B29" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674310</v>
+        <v>673852</v>
       </c>
       <c r="R29" t="n">
-        <v>7093054</v>
+        <v>7092910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,12 +3548,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126913209</v>
+        <v>126919043</v>
       </c>
       <c r="B32" t="n">
         <v>98443</v>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674212</v>
+        <v>673945</v>
       </c>
       <c r="R32" t="n">
-        <v>7092826</v>
+        <v>7092938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126919043</v>
+        <v>126913209</v>
       </c>
       <c r="B33" t="n">
         <v>98443</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>673945</v>
+        <v>674212</v>
       </c>
       <c r="R33" t="n">
-        <v>7092938</v>
+        <v>7092826</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3968,7 +3968,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912691</v>
+        <v>126918803</v>
       </c>
       <c r="B34" t="n">
         <v>79014</v>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674239</v>
+        <v>674314</v>
       </c>
       <c r="R34" t="n">
-        <v>7092910</v>
+        <v>7093009</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,19 +4053,23 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912681</v>
+        <v>126912691</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -4100,10 +4104,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674304</v>
+        <v>674239</v>
       </c>
       <c r="R35" t="n">
-        <v>7093019</v>
+        <v>7092910</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,7 +4166,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919078</v>
+        <v>126912681</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4197,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673893</v>
+        <v>674304</v>
       </c>
       <c r="R36" t="n">
-        <v>7092920</v>
+        <v>7093019</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,48 +4251,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126913201</v>
+        <v>126919009</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674120</v>
+        <v>673944</v>
       </c>
       <c r="R37" t="n">
-        <v>7092901</v>
+        <v>7093050</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,6 +4336,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4348,12 +4353,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4364,7 +4369,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919009</v>
+        <v>126919008</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4399,10 +4404,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673944</v>
+        <v>673843</v>
       </c>
       <c r="R38" t="n">
-        <v>7093050</v>
+        <v>7093104</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4435,11 +4440,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919008</v>
+        <v>126912635</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673843</v>
+        <v>674239</v>
       </c>
       <c r="R39" t="n">
-        <v>7093104</v>
+        <v>7092908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,23 +4555,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918803</v>
+        <v>126919078</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4606,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>674314</v>
+        <v>673893</v>
       </c>
       <c r="R40" t="n">
-        <v>7093009</v>
+        <v>7092920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,12 +4652,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4672,32 +4668,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912635</v>
+        <v>126913201</v>
       </c>
       <c r="B41" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4707,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>674239</v>
+        <v>674120</v>
       </c>
       <c r="R41" t="n">
-        <v>7092908</v>
+        <v>7092901</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,15 +4753,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4870,32 +4870,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126919067</v>
+        <v>126915612</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673610</v>
+        <v>674198</v>
       </c>
       <c r="R43" t="n">
-        <v>7092955</v>
+        <v>7092843</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,12 +4955,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4971,7 +4971,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912666</v>
+        <v>126912685</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674176</v>
+        <v>674236</v>
       </c>
       <c r="R44" t="n">
-        <v>7093061</v>
+        <v>7092969</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126919074</v>
+        <v>126912666</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673796</v>
+        <v>674176</v>
       </c>
       <c r="R45" t="n">
-        <v>7092899</v>
+        <v>7093061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,23 +5153,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912683</v>
+        <v>126913207</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5204,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674310</v>
+        <v>674182</v>
       </c>
       <c r="R46" t="n">
-        <v>7092998</v>
+        <v>7092837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,44 +5250,48 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126915612</v>
+        <v>126912683</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674198</v>
+        <v>674310</v>
       </c>
       <c r="R47" t="n">
-        <v>7092843</v>
+        <v>7092998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,23 +5351,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912685</v>
+        <v>126919067</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5402,10 +5398,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674236</v>
+        <v>673610</v>
       </c>
       <c r="R48" t="n">
-        <v>7092969</v>
+        <v>7092955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,15 +5448,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5565,7 +5565,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126913207</v>
+        <v>126919074</v>
       </c>
       <c r="B50" t="n">
         <v>79014</v>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674182</v>
+        <v>673796</v>
       </c>
       <c r="R50" t="n">
-        <v>7092837</v>
+        <v>7092899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126913208</v>
+        <v>126919076</v>
       </c>
       <c r="B51" t="n">
-        <v>91276</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674181</v>
+        <v>673836</v>
       </c>
       <c r="R51" t="n">
-        <v>7092836</v>
+        <v>7092910</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,12 +5751,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5767,61 +5767,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126913214</v>
+        <v>126913208</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>91276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674219</v>
+        <v>674181</v>
       </c>
       <c r="R52" t="n">
-        <v>7092815</v>
+        <v>7092836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5862,7 +5846,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5885,32 +5868,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126915608</v>
+        <v>126912576</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5920,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674257</v>
+        <v>674200</v>
       </c>
       <c r="R53" t="n">
-        <v>7092823</v>
+        <v>7092950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5970,61 +5953,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126919000</v>
+        <v>126913179</v>
       </c>
       <c r="B54" t="n">
-        <v>78773</v>
+        <v>80021</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>673939</v>
+        <v>673719</v>
       </c>
       <c r="R54" t="n">
-        <v>7093012</v>
+        <v>7093035</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6065,18 +6047,19 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6087,32 +6070,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915630</v>
+        <v>126919000</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>78773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6105,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674328</v>
+        <v>673939</v>
       </c>
       <c r="R55" t="n">
-        <v>7092980</v>
+        <v>7093012</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6177,7 +6160,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6188,7 +6171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912700</v>
+        <v>126915630</v>
       </c>
       <c r="B56" t="n">
         <v>98360</v>
@@ -6223,10 +6206,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674267</v>
+        <v>674328</v>
       </c>
       <c r="R56" t="n">
-        <v>7093044</v>
+        <v>7092980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6273,44 +6256,48 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919076</v>
+        <v>126912700</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6320,10 +6307,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673836</v>
+        <v>674267</v>
       </c>
       <c r="R57" t="n">
-        <v>7092910</v>
+        <v>7093044</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6370,48 +6357,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912576</v>
+        <v>126915608</v>
       </c>
       <c r="B58" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6421,10 +6404,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674200</v>
+        <v>674257</v>
       </c>
       <c r="R58" t="n">
-        <v>7092950</v>
+        <v>7092823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6471,49 +6454,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126913179</v>
+        <v>126913214</v>
       </c>
       <c r="B59" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673719</v>
+        <v>674219</v>
       </c>
       <c r="R59" t="n">
-        <v>7093035</v>
+        <v>7092815</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912687</v>
+        <v>126918787</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674226</v>
+        <v>674167</v>
       </c>
       <c r="R60" t="n">
-        <v>7092929</v>
+        <v>7092848</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,44 +6673,48 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918806</v>
+        <v>126915584</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6720,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674216</v>
+        <v>674316</v>
       </c>
       <c r="R61" t="n">
-        <v>7092860</v>
+        <v>7092989</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6770,12 +6774,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6786,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919031</v>
+        <v>126918806</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673796</v>
+        <v>674216</v>
       </c>
       <c r="R62" t="n">
-        <v>7092899</v>
+        <v>7092860</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,12 +6875,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7085,32 +7089,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126912617</v>
+        <v>126919031</v>
       </c>
       <c r="B65" t="n">
-        <v>80145</v>
+        <v>78772</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7120,10 +7124,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674214</v>
+        <v>673796</v>
       </c>
       <c r="R65" t="n">
-        <v>7092881</v>
+        <v>7092899</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7170,44 +7174,48 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126913211</v>
+        <v>126912617</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>80145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7220,7 +7228,7 @@
         <v>674214</v>
       </c>
       <c r="R66" t="n">
-        <v>7092818</v>
+        <v>7092881</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7267,48 +7275,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126918787</v>
+        <v>126912687</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7318,10 +7322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674167</v>
+        <v>674226</v>
       </c>
       <c r="R67" t="n">
-        <v>7092848</v>
+        <v>7092929</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,48 +7372,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126915584</v>
+        <v>126912622</v>
       </c>
       <c r="B68" t="n">
-        <v>98464</v>
+        <v>78773</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674316</v>
+        <v>674225</v>
       </c>
       <c r="R68" t="n">
-        <v>7092989</v>
+        <v>7092965</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7469,48 +7469,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126919039</v>
+        <v>126912620</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7520,10 +7516,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>673525</v>
+        <v>674229</v>
       </c>
       <c r="R69" t="n">
-        <v>7093040</v>
+        <v>7092964</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,23 +7566,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126912622</v>
+        <v>126918999</v>
       </c>
       <c r="B70" t="n">
         <v>78773</v>
@@ -7621,10 +7613,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>674225</v>
+        <v>673919</v>
       </c>
       <c r="R70" t="n">
-        <v>7092965</v>
+        <v>7093017</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7671,44 +7663,48 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126912620</v>
+        <v>126919039</v>
       </c>
       <c r="B71" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7718,10 +7714,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674229</v>
+        <v>673525</v>
       </c>
       <c r="R71" t="n">
-        <v>7092964</v>
+        <v>7093040</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7768,44 +7764,48 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126918999</v>
+        <v>126913211</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>673919</v>
+        <v>674214</v>
       </c>
       <c r="R72" t="n">
-        <v>7093017</v>
+        <v>7092818</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912680</v>
+        <v>126912579</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674302</v>
+        <v>674239</v>
       </c>
       <c r="R73" t="n">
-        <v>7093031</v>
+        <v>7092908</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126919068</v>
+        <v>126912680</v>
       </c>
       <c r="B74" t="n">
         <v>79014</v>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>673630</v>
+        <v>674302</v>
       </c>
       <c r="R74" t="n">
-        <v>7092929</v>
+        <v>7093031</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8063,26 +8063,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912579</v>
+        <v>126919068</v>
       </c>
       <c r="B75" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8090,21 +8086,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8114,10 +8110,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674239</v>
+        <v>673630</v>
       </c>
       <c r="R75" t="n">
-        <v>7092908</v>
+        <v>7092929</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8164,15 +8160,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8375,45 +8375,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126918795</v>
+        <v>126912599</v>
       </c>
       <c r="B78" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674236</v>
+        <v>674251</v>
       </c>
       <c r="R78" t="n">
-        <v>7092852</v>
+        <v>7093028</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,66 +8465,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126912599</v>
+        <v>126918795</v>
       </c>
       <c r="B79" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674251</v>
+        <v>674236</v>
       </c>
       <c r="R79" t="n">
-        <v>7093028</v>
+        <v>7092852</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8566,15 +8562,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8877,32 +8877,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126913212</v>
+        <v>126912668</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674207</v>
+        <v>674214</v>
       </c>
       <c r="R83" t="n">
-        <v>7092818</v>
+        <v>7093041</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,23 +8962,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126912674</v>
+        <v>126912672</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9013,10 +9009,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674251</v>
+        <v>674248</v>
       </c>
       <c r="R84" t="n">
-        <v>7093028</v>
+        <v>7093018</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9075,32 +9071,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912668</v>
+        <v>126912618</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9110,10 +9106,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674214</v>
+        <v>674104</v>
       </c>
       <c r="R85" t="n">
-        <v>7093041</v>
+        <v>7092938</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9172,7 +9168,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126912672</v>
+        <v>126912674</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -9207,10 +9203,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674248</v>
+        <v>674251</v>
       </c>
       <c r="R86" t="n">
-        <v>7093018</v>
+        <v>7093028</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9269,10 +9265,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912618</v>
+        <v>126912699</v>
       </c>
       <c r="B87" t="n">
-        <v>80145</v>
+        <v>98360</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9280,21 +9276,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9304,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674104</v>
+        <v>674260</v>
       </c>
       <c r="R87" t="n">
-        <v>7092938</v>
+        <v>7093031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9366,32 +9362,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126912699</v>
+        <v>126915607</v>
       </c>
       <c r="B88" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9401,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674260</v>
+        <v>674262</v>
       </c>
       <c r="R88" t="n">
-        <v>7093031</v>
+        <v>7092824</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9451,19 +9447,23 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126919037</v>
+        <v>126913212</v>
       </c>
       <c r="B89" t="n">
         <v>98443</v>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>673555</v>
+        <v>674207</v>
       </c>
       <c r="R89" t="n">
-        <v>7093132</v>
+        <v>7092818</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,7 +9564,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126915607</v>
+        <v>126919037</v>
       </c>
       <c r="B90" t="n">
         <v>98443</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674262</v>
+        <v>673555</v>
       </c>
       <c r="R90" t="n">
-        <v>7092824</v>
+        <v>7093132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,10 +9665,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912624</v>
+        <v>126918807</v>
       </c>
       <c r="B91" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674218</v>
+        <v>674208</v>
       </c>
       <c r="R91" t="n">
-        <v>7092914</v>
+        <v>7092856</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,22 +9750,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126912703</v>
+        <v>126913181</v>
       </c>
       <c r="B92" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9773,21 +9777,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9797,10 +9801,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674269</v>
+        <v>674236</v>
       </c>
       <c r="R92" t="n">
-        <v>7092979</v>
+        <v>7093024</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9847,22 +9851,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126913181</v>
+        <v>126912578</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9870,21 +9878,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9894,10 +9902,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674236</v>
+        <v>674218</v>
       </c>
       <c r="R93" t="n">
-        <v>7093024</v>
+        <v>7092914</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9944,48 +9952,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126919072</v>
+        <v>126912614</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9999,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>673738</v>
+        <v>674319</v>
       </c>
       <c r="R94" t="n">
-        <v>7092885</v>
+        <v>7093047</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,26 +10049,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918807</v>
+        <v>126912634</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10072,21 +10072,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674208</v>
+        <v>674203</v>
       </c>
       <c r="R95" t="n">
-        <v>7092856</v>
+        <v>7092932</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,26 +10146,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126912578</v>
+        <v>126918789</v>
       </c>
       <c r="B96" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10173,21 +10169,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10197,10 +10193,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R96" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10247,22 +10243,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126912634</v>
+        <v>126918984</v>
       </c>
       <c r="B97" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,21 +10270,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674203</v>
+        <v>673919</v>
       </c>
       <c r="R97" t="n">
-        <v>7092932</v>
+        <v>7093017</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,22 +10344,26 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918789</v>
+        <v>126919072</v>
       </c>
       <c r="B98" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10367,21 +10371,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10391,10 +10395,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674310</v>
+        <v>673738</v>
       </c>
       <c r="R98" t="n">
-        <v>7092997</v>
+        <v>7092885</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,12 +10445,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10457,32 +10461,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126912614</v>
+        <v>126915609</v>
       </c>
       <c r="B99" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10492,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674319</v>
+        <v>674231</v>
       </c>
       <c r="R99" t="n">
-        <v>7093047</v>
+        <v>7092812</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10542,22 +10546,26 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126918984</v>
+        <v>126912703</v>
       </c>
       <c r="B100" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10565,21 +10573,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10589,10 +10597,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>673919</v>
+        <v>674269</v>
       </c>
       <c r="R100" t="n">
-        <v>7093017</v>
+        <v>7092979</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10639,19 +10647,15 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10756,32 +10760,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126915609</v>
+        <v>126912624</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10791,10 +10795,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674231</v>
+        <v>674218</v>
       </c>
       <c r="R102" t="n">
-        <v>7092812</v>
+        <v>7092914</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10841,26 +10845,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912679</v>
+        <v>126912575</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10868,21 +10868,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674324</v>
+        <v>674215</v>
       </c>
       <c r="R103" t="n">
-        <v>7093051</v>
+        <v>7092959</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,10 +10954,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912671</v>
+        <v>126912572</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10965,21 +10965,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674238</v>
+        <v>674310</v>
       </c>
       <c r="R104" t="n">
-        <v>7093012</v>
+        <v>7092998</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11051,7 +11051,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126913197</v>
+        <v>126912679</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11086,10 +11086,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>673791</v>
+        <v>674324</v>
       </c>
       <c r="R105" t="n">
-        <v>7092931</v>
+        <v>7093051</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11136,23 +11136,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912686</v>
+        <v>126912671</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11187,10 +11183,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674222</v>
+        <v>674238</v>
       </c>
       <c r="R106" t="n">
-        <v>7092926</v>
+        <v>7093012</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11249,32 +11245,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126915582</v>
+        <v>126913197</v>
       </c>
       <c r="B107" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11284,10 +11280,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674302</v>
+        <v>673791</v>
       </c>
       <c r="R107" t="n">
-        <v>7093071</v>
+        <v>7092931</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11334,12 +11330,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11350,54 +11346,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912637</v>
+        <v>126912686</v>
       </c>
       <c r="B108" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674166</v>
+        <v>674222</v>
       </c>
       <c r="R108" t="n">
-        <v>7092881</v>
+        <v>7092926</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11456,54 +11443,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126912642</v>
+        <v>126915582</v>
       </c>
       <c r="B109" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674117</v>
+        <v>674302</v>
       </c>
       <c r="R109" t="n">
-        <v>7092933</v>
+        <v>7093071</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11550,57 +11528,70 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912575</v>
+        <v>126912642</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674215</v>
+        <v>674117</v>
       </c>
       <c r="R110" t="n">
-        <v>7092959</v>
+        <v>7092933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11659,45 +11650,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126912572</v>
+        <v>126912637</v>
       </c>
       <c r="B111" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674310</v>
+        <v>674166</v>
       </c>
       <c r="R111" t="n">
-        <v>7092998</v>
+        <v>7092881</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11853,32 +11853,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126915628</v>
+        <v>126918801</v>
       </c>
       <c r="B113" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674258</v>
+        <v>674148</v>
       </c>
       <c r="R113" t="n">
-        <v>7093046</v>
+        <v>7093061</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11938,12 +11938,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11954,10 +11954,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918998</v>
+        <v>126918810</v>
       </c>
       <c r="B114" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>673861</v>
+        <v>674189</v>
       </c>
       <c r="R114" t="n">
-        <v>7093031</v>
+        <v>7092854</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,12 +12039,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12055,10 +12055,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918776</v>
+        <v>126912577</v>
       </c>
       <c r="B115" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674139</v>
+        <v>674204</v>
       </c>
       <c r="R115" t="n">
-        <v>7092939</v>
+        <v>7092934</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12140,26 +12140,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918801</v>
+        <v>126918998</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12167,21 +12163,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12191,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674148</v>
+        <v>673861</v>
       </c>
       <c r="R116" t="n">
-        <v>7093061</v>
+        <v>7093031</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12241,12 +12237,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12257,10 +12253,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918810</v>
+        <v>126918776</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12268,21 +12264,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12292,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674189</v>
+        <v>674139</v>
       </c>
       <c r="R117" t="n">
-        <v>7092854</v>
+        <v>7092939</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12358,32 +12354,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126912577</v>
+        <v>126915628</v>
       </c>
       <c r="B118" t="n">
-        <v>79632</v>
+        <v>98360</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12393,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674204</v>
+        <v>674258</v>
       </c>
       <c r="R118" t="n">
-        <v>7092934</v>
+        <v>7093046</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12443,15 +12439,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12557,32 +12557,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126918778</v>
+        <v>126918808</v>
       </c>
       <c r="B120" t="n">
-        <v>98347</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12592,10 +12592,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674279</v>
+        <v>674199</v>
       </c>
       <c r="R120" t="n">
-        <v>7092923</v>
+        <v>7092849</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12658,32 +12658,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126913194</v>
+        <v>126912573</v>
       </c>
       <c r="B121" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12693,10 +12693,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>673917</v>
+        <v>674270</v>
       </c>
       <c r="R121" t="n">
-        <v>7092948</v>
+        <v>7092973</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12743,19 +12743,15 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12957,32 +12953,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126918808</v>
+        <v>126913194</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12992,10 +12988,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>674199</v>
+        <v>673917</v>
       </c>
       <c r="R124" t="n">
-        <v>7092849</v>
+        <v>7092948</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13042,12 +13038,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13058,32 +13054,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126912573</v>
+        <v>126918778</v>
       </c>
       <c r="B125" t="n">
-        <v>79632</v>
+        <v>98347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>220093</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13093,10 +13089,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>674270</v>
+        <v>674279</v>
       </c>
       <c r="R125" t="n">
-        <v>7092973</v>
+        <v>7092923</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13143,44 +13139,48 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126912690</v>
+        <v>126912615</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>674243</v>
+        <v>674322</v>
       </c>
       <c r="R126" t="n">
-        <v>7092914</v>
+        <v>7093041</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13252,10 +13252,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126912665</v>
+        <v>126919003</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13263,21 +13263,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>674174</v>
+        <v>673948</v>
       </c>
       <c r="R127" t="n">
-        <v>7093073</v>
+        <v>7093011</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13337,44 +13337,48 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126919036</v>
+        <v>126912665</v>
       </c>
       <c r="B128" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13384,10 +13388,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>673559</v>
+        <v>674174</v>
       </c>
       <c r="R128" t="n">
-        <v>7093141</v>
+        <v>7093073</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13434,48 +13438,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126915614</v>
+        <v>126912690</v>
       </c>
       <c r="B129" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13485,10 +13485,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>674163</v>
+        <v>674243</v>
       </c>
       <c r="R129" t="n">
-        <v>7092870</v>
+        <v>7092914</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13535,48 +13535,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126919003</v>
+        <v>126915614</v>
       </c>
       <c r="B130" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13586,10 +13582,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>673948</v>
+        <v>674163</v>
       </c>
       <c r="R130" t="n">
-        <v>7093011</v>
+        <v>7092870</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13641,7 +13637,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13652,32 +13648,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126912615</v>
+        <v>126919036</v>
       </c>
       <c r="B131" t="n">
-        <v>80145</v>
+        <v>98443</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13687,10 +13683,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>674322</v>
+        <v>673559</v>
       </c>
       <c r="R131" t="n">
-        <v>7093041</v>
+        <v>7093141</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13737,15 +13733,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13943,32 +13943,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126912593</v>
+        <v>126918997</v>
       </c>
       <c r="B134" t="n">
-        <v>80146</v>
+        <v>78773</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13978,10 +13978,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>674210</v>
+        <v>673855</v>
       </c>
       <c r="R134" t="n">
-        <v>7092877</v>
+        <v>7093043</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14028,61 +14028,70 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126913960</v>
+        <v>126912638</v>
       </c>
       <c r="B135" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>673577</v>
+        <v>674111</v>
       </c>
       <c r="R135" t="n">
-        <v>7093132</v>
+        <v>7092937</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14117,11 +14126,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14134,70 +14138,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126912638</v>
+        <v>126912593</v>
       </c>
       <c r="B136" t="n">
-        <v>98443</v>
+        <v>80146</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>674111</v>
+        <v>674210</v>
       </c>
       <c r="R136" t="n">
-        <v>7092937</v>
+        <v>7092877</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14256,10 +14247,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126918997</v>
+        <v>126913960</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14267,34 +14258,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>673855</v>
+        <v>673577</v>
       </c>
       <c r="R137" t="n">
-        <v>7093043</v>
+        <v>7093132</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14329,6 +14324,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -14341,12 +14341,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14357,7 +14357,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126912678</v>
+        <v>126918805</v>
       </c>
       <c r="B138" t="n">
         <v>79014</v>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>674334</v>
+        <v>674241</v>
       </c>
       <c r="R138" t="n">
-        <v>7093055</v>
+        <v>7092850</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,22 +14442,26 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126919027</v>
+        <v>126918804</v>
       </c>
       <c r="B139" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14465,21 +14469,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14489,10 +14493,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>673554</v>
+        <v>674299</v>
       </c>
       <c r="R139" t="n">
-        <v>7093135</v>
+        <v>7092979</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14539,12 +14543,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14555,10 +14559,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126913193</v>
+        <v>126919027</v>
       </c>
       <c r="B140" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14566,21 +14570,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14590,10 +14594,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>673849</v>
+        <v>673554</v>
       </c>
       <c r="R140" t="n">
-        <v>7092944</v>
+        <v>7093135</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14640,12 +14644,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14656,7 +14660,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126918805</v>
+        <v>126912678</v>
       </c>
       <c r="B141" t="n">
         <v>79014</v>
@@ -14691,10 +14695,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>674241</v>
+        <v>674334</v>
       </c>
       <c r="R141" t="n">
-        <v>7092850</v>
+        <v>7093055</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14741,26 +14745,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126918804</v>
+        <v>126913193</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>674299</v>
+        <v>673849</v>
       </c>
       <c r="R142" t="n">
-        <v>7092979</v>
+        <v>7092944</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -14858,32 +14858,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126912670</v>
+        <v>126915991</v>
       </c>
       <c r="B143" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14893,13 +14893,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>674225</v>
+        <v>673971</v>
       </c>
       <c r="R143" t="n">
-        <v>7093014</v>
+        <v>7092936</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14943,19 +14943,23 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126919075</v>
+        <v>126919007</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -14990,10 +14994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>673825</v>
+        <v>673940</v>
       </c>
       <c r="R144" t="n">
-        <v>7092923</v>
+        <v>7093045</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15028,24 +15032,30 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15056,7 +15066,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126919069</v>
+        <v>126912670</v>
       </c>
       <c r="B145" t="n">
         <v>79014</v>
@@ -15091,10 +15101,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>673685</v>
+        <v>674225</v>
       </c>
       <c r="R145" t="n">
-        <v>7092946</v>
+        <v>7093014</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15141,23 +15151,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126912676</v>
+        <v>126912651</v>
       </c>
       <c r="B146" t="n">
         <v>79014</v>
@@ -15192,10 +15198,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>674259</v>
+        <v>674297</v>
       </c>
       <c r="R146" t="n">
-        <v>7093064</v>
+        <v>7092976</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15228,6 +15234,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15254,32 +15265,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126915991</v>
+        <v>126913182</v>
       </c>
       <c r="B147" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15289,13 +15300,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>673971</v>
+        <v>674316</v>
       </c>
       <c r="R147" t="n">
-        <v>7092936</v>
+        <v>7093018</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15339,12 +15350,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15355,32 +15366,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126919017</v>
+        <v>126912676</v>
       </c>
       <c r="B148" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15390,10 +15401,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>673668</v>
+        <v>674259</v>
       </c>
       <c r="R148" t="n">
-        <v>7092943</v>
+        <v>7093064</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15428,11 +15439,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -15445,48 +15451,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126915629</v>
+        <v>126912688</v>
       </c>
       <c r="B149" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15496,10 +15498,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>674305</v>
+        <v>674231</v>
       </c>
       <c r="R149" t="n">
-        <v>7093077</v>
+        <v>7092932</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15546,23 +15548,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126919007</v>
+        <v>126919075</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -15597,10 +15595,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>673940</v>
+        <v>673825</v>
       </c>
       <c r="R150" t="n">
-        <v>7093045</v>
+        <v>7092923</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15635,30 +15633,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15669,7 +15661,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126912688</v>
+        <v>126919069</v>
       </c>
       <c r="B151" t="n">
         <v>79014</v>
@@ -15704,10 +15696,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>674231</v>
+        <v>673685</v>
       </c>
       <c r="R151" t="n">
-        <v>7092932</v>
+        <v>7092946</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15754,44 +15746,48 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126912651</v>
+        <v>126919017</v>
       </c>
       <c r="B152" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15801,10 +15797,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>674297</v>
+        <v>673668</v>
       </c>
       <c r="R152" t="n">
-        <v>7092976</v>
+        <v>7092943</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15841,7 +15837,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
+          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15856,44 +15852,48 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126913182</v>
+        <v>126915629</v>
       </c>
       <c r="B153" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>674316</v>
+        <v>674305</v>
       </c>
       <c r="R153" t="n">
-        <v>7093018</v>
+        <v>7093077</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15953,12 +15953,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126918792</v>
+        <v>126915634</v>
       </c>
       <c r="B155" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674129</v>
+        <v>674163</v>
       </c>
       <c r="R155" t="n">
-        <v>7093003</v>
+        <v>7092870</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,12 +16155,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16171,32 +16171,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126915634</v>
+        <v>126915613</v>
       </c>
       <c r="B156" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>674163</v>
+        <v>674171</v>
       </c>
       <c r="R156" t="n">
-        <v>7092870</v>
+        <v>7092865</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16272,32 +16272,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126915603</v>
+        <v>126918792</v>
       </c>
       <c r="B157" t="n">
-        <v>98347</v>
+        <v>98443</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16307,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>674278</v>
+        <v>674129</v>
       </c>
       <c r="R157" t="n">
-        <v>7092923</v>
+        <v>7093003</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16357,12 +16357,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16373,7 +16373,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126915602</v>
+        <v>126915603</v>
       </c>
       <c r="B158" t="n">
         <v>98347</v>
@@ -16408,10 +16408,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674319</v>
+        <v>674278</v>
       </c>
       <c r="R158" t="n">
-        <v>7092980</v>
+        <v>7092923</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16474,32 +16474,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126912692</v>
+        <v>126915602</v>
       </c>
       <c r="B159" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674236</v>
+        <v>674319</v>
       </c>
       <c r="R159" t="n">
-        <v>7092908</v>
+        <v>7092980</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16559,19 +16559,23 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126919063</v>
+        <v>126912692</v>
       </c>
       <c r="B160" t="n">
         <v>79014</v>
@@ -16606,10 +16610,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>673530</v>
+        <v>674236</v>
       </c>
       <c r="R160" t="n">
-        <v>7093126</v>
+        <v>7092908</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16656,23 +16660,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126919070</v>
+        <v>126919063</v>
       </c>
       <c r="B161" t="n">
         <v>79014</v>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>673731</v>
+        <v>673530</v>
       </c>
       <c r="R161" t="n">
-        <v>7092924</v>
+        <v>7093126</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16773,32 +16773,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126915613</v>
+        <v>126919070</v>
       </c>
       <c r="B162" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>674171</v>
+        <v>673731</v>
       </c>
       <c r="R162" t="n">
-        <v>7092865</v>
+        <v>7092924</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,12 +16858,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16971,7 +16971,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912684</v>
+        <v>126918809</v>
       </c>
       <c r="B164" t="n">
         <v>79014</v>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674292</v>
+        <v>674196</v>
       </c>
       <c r="R164" t="n">
-        <v>7092976</v>
+        <v>7092846</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17056,19 +17056,23 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126918809</v>
+        <v>126912684</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17103,10 +17107,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>674196</v>
+        <v>674292</v>
       </c>
       <c r="R165" t="n">
-        <v>7092846</v>
+        <v>7092976</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17153,19 +17157,15 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19929,10 +19929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126913471</v>
+        <v>126913476</v>
       </c>
       <c r="B193" t="n">
-        <v>78772</v>
+        <v>77992</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19940,21 +19940,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19964,10 +19964,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>673564</v>
+        <v>673565</v>
       </c>
       <c r="R193" t="n">
-        <v>7093086</v>
+        <v>7093070</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20008,6 +20008,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20030,10 +20031,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126913476</v>
+        <v>126913471</v>
       </c>
       <c r="B194" t="n">
-        <v>77992</v>
+        <v>78772</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20041,21 +20042,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20065,10 +20066,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>673565</v>
+        <v>673564</v>
       </c>
       <c r="R194" t="n">
-        <v>7093070</v>
+        <v>7093086</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20109,7 +20110,6 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -20233,10 +20233,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126913448</v>
+        <v>126913475</v>
       </c>
       <c r="B196" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20244,21 +20244,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20268,10 +20268,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>673558</v>
+        <v>673753</v>
       </c>
       <c r="R196" t="n">
-        <v>7093130</v>
+        <v>7093083</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20334,10 +20334,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126913475</v>
+        <v>126913448</v>
       </c>
       <c r="B197" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20345,21 +20345,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20369,10 +20369,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>673753</v>
+        <v>673558</v>
       </c>
       <c r="R197" t="n">
-        <v>7093083</v>
+        <v>7093130</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919065</v>
+        <v>126918800</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673619</v>
+        <v>674103</v>
       </c>
       <c r="R9" t="n">
-        <v>7092978</v>
+        <v>7093056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918800</v>
+        <v>126916005</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674103</v>
+        <v>673879</v>
       </c>
       <c r="R10" t="n">
-        <v>7093056</v>
+        <v>7092985</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916005</v>
+        <v>126918995</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673879</v>
+        <v>673947</v>
       </c>
       <c r="R11" t="n">
-        <v>7092985</v>
+        <v>7093045</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B12" t="n">
-        <v>80021</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R12" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126915585</v>
+        <v>126919065</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674324</v>
+        <v>673619</v>
       </c>
       <c r="R13" t="n">
-        <v>7093076</v>
+        <v>7092978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919040</v>
+        <v>126915632</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673649</v>
+        <v>674279</v>
       </c>
       <c r="R14" t="n">
-        <v>7092943</v>
+        <v>7092915</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,7 +2065,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918793</v>
+        <v>126919040</v>
       </c>
       <c r="B15" t="n">
         <v>98443</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674251</v>
+        <v>673649</v>
       </c>
       <c r="R15" t="n">
-        <v>7092837</v>
+        <v>7092943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126913215</v>
+        <v>126918793</v>
       </c>
       <c r="B16" t="n">
         <v>98443</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674258</v>
+        <v>674251</v>
       </c>
       <c r="R16" t="n">
-        <v>7092817</v>
+        <v>7092837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126915632</v>
+        <v>126913215</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674279</v>
+        <v>674258</v>
       </c>
       <c r="R17" t="n">
-        <v>7092915</v>
+        <v>7092817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915627</v>
+        <v>126912574</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674167</v>
+        <v>674224</v>
       </c>
       <c r="R18" t="n">
-        <v>7093069</v>
+        <v>7092965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,48 +2453,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912574</v>
+        <v>126912616</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>80145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674224</v>
+        <v>674220</v>
       </c>
       <c r="R19" t="n">
-        <v>7092965</v>
+        <v>7092919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,32 +2562,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126912616</v>
+        <v>126915627</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674220</v>
+        <v>674167</v>
       </c>
       <c r="R20" t="n">
-        <v>7092919</v>
+        <v>7093069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,15 +2647,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126919071</v>
+        <v>126919077</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673738</v>
+        <v>673852</v>
       </c>
       <c r="R28" t="n">
-        <v>7092907</v>
+        <v>7092910</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126919077</v>
+        <v>126919071</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673852</v>
+        <v>673738</v>
       </c>
       <c r="R29" t="n">
-        <v>7092910</v>
+        <v>7092907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126918790</v>
+        <v>126912685</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674101</v>
+        <v>674236</v>
       </c>
       <c r="R42" t="n">
-        <v>7092979</v>
+        <v>7092969</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,48 +4854,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915612</v>
+        <v>126912666</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674198</v>
+        <v>674176</v>
       </c>
       <c r="R43" t="n">
-        <v>7092843</v>
+        <v>7093061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,23 +4951,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912685</v>
+        <v>126913207</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5006,10 +4998,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674236</v>
+        <v>674182</v>
       </c>
       <c r="R44" t="n">
-        <v>7092969</v>
+        <v>7092837</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,19 +5048,23 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912666</v>
+        <v>126912683</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5103,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674176</v>
+        <v>674310</v>
       </c>
       <c r="R45" t="n">
-        <v>7093061</v>
+        <v>7092998</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5165,7 +5161,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913207</v>
+        <v>126919067</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5200,10 +5196,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674182</v>
+        <v>673610</v>
       </c>
       <c r="R46" t="n">
-        <v>7092837</v>
+        <v>7092955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,12 +5246,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5266,32 +5262,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912683</v>
+        <v>126915572</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5297,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674310</v>
+        <v>674324</v>
       </c>
       <c r="R47" t="n">
-        <v>7092998</v>
+        <v>7093076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,19 +5347,23 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919067</v>
+        <v>126919074</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673610</v>
+        <v>673796</v>
       </c>
       <c r="R48" t="n">
-        <v>7092955</v>
+        <v>7092899</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5464,32 +5464,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126915572</v>
+        <v>126918790</v>
       </c>
       <c r="B49" t="n">
-        <v>91291</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674324</v>
+        <v>674101</v>
       </c>
       <c r="R49" t="n">
-        <v>7093076</v>
+        <v>7092979</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,12 +5549,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919074</v>
+        <v>126915612</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>673796</v>
+        <v>674198</v>
       </c>
       <c r="R50" t="n">
-        <v>7092899</v>
+        <v>7092843</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919076</v>
+        <v>126919000</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>673836</v>
+        <v>673939</v>
       </c>
       <c r="R51" t="n">
-        <v>7092910</v>
+        <v>7093012</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,12 +5751,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5767,32 +5767,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126913208</v>
+        <v>126915630</v>
       </c>
       <c r="B52" t="n">
-        <v>91276</v>
+        <v>98360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>112</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674181</v>
+        <v>674328</v>
       </c>
       <c r="R52" t="n">
-        <v>7092836</v>
+        <v>7092980</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5852,12 +5852,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,32 +5868,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912576</v>
+        <v>126912700</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>98360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674200</v>
+        <v>674267</v>
       </c>
       <c r="R53" t="n">
-        <v>7092950</v>
+        <v>7093044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5965,37 +5965,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913179</v>
+        <v>126913214</v>
       </c>
       <c r="B54" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6003,10 +6016,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>673719</v>
+        <v>674219</v>
       </c>
       <c r="R54" t="n">
-        <v>7093035</v>
+        <v>7092815</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6070,10 +6083,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919000</v>
+        <v>126913208</v>
       </c>
       <c r="B55" t="n">
-        <v>78773</v>
+        <v>91276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6081,21 +6094,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>112</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6105,10 +6118,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>673939</v>
+        <v>674181</v>
       </c>
       <c r="R55" t="n">
-        <v>7093012</v>
+        <v>7092836</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6155,12 +6168,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6171,32 +6184,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126915630</v>
+        <v>126912576</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6206,10 +6219,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674328</v>
+        <v>674200</v>
       </c>
       <c r="R56" t="n">
-        <v>7092980</v>
+        <v>7092950</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,26 +6269,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912700</v>
+        <v>126913179</v>
       </c>
       <c r="B57" t="n">
-        <v>98360</v>
+        <v>80021</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6283,34 +6292,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674267</v>
+        <v>673719</v>
       </c>
       <c r="R57" t="n">
-        <v>7093044</v>
+        <v>7093035</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6351,50 +6363,55 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126915608</v>
+        <v>126919076</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6404,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674257</v>
+        <v>673836</v>
       </c>
       <c r="R58" t="n">
-        <v>7092823</v>
+        <v>7092910</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6454,12 +6471,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6470,7 +6487,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126913214</v>
+        <v>126915608</v>
       </c>
       <c r="B59" t="n">
         <v>98443</v>
@@ -6498,33 +6515,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674219</v>
+        <v>674257</v>
       </c>
       <c r="R59" t="n">
-        <v>7092815</v>
+        <v>7092823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,19 +6566,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918787</v>
+        <v>126918806</v>
       </c>
       <c r="B60" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674167</v>
+        <v>674216</v>
       </c>
       <c r="R60" t="n">
-        <v>7092848</v>
+        <v>7092860</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126915584</v>
+        <v>126912592</v>
       </c>
       <c r="B61" t="n">
-        <v>98464</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674316</v>
+        <v>674188</v>
       </c>
       <c r="R61" t="n">
-        <v>7092989</v>
+        <v>7092955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6774,48 +6774,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918806</v>
+        <v>126918996</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674216</v>
+        <v>673948</v>
       </c>
       <c r="R62" t="n">
-        <v>7092860</v>
+        <v>7093016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,12 +6871,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6891,32 +6887,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912592</v>
+        <v>126919031</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6926,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674188</v>
+        <v>673796</v>
       </c>
       <c r="R63" t="n">
-        <v>7092955</v>
+        <v>7092899</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6976,19 +6972,23 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918996</v>
+        <v>126912617</v>
       </c>
       <c r="B64" t="n">
         <v>80145</v>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673948</v>
+        <v>674214</v>
       </c>
       <c r="R64" t="n">
-        <v>7093016</v>
+        <v>7092881</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7073,26 +7073,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126919031</v>
+        <v>126912687</v>
       </c>
       <c r="B65" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7100,21 +7096,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7124,10 +7120,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>673796</v>
+        <v>674226</v>
       </c>
       <c r="R65" t="n">
-        <v>7092899</v>
+        <v>7092929</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7174,26 +7170,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126912617</v>
+        <v>126918787</v>
       </c>
       <c r="B66" t="n">
-        <v>80145</v>
+        <v>98464</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7201,21 +7193,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7225,10 +7217,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674214</v>
+        <v>674167</v>
       </c>
       <c r="R66" t="n">
-        <v>7092881</v>
+        <v>7092848</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7275,44 +7267,48 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126912687</v>
+        <v>126915584</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7322,10 +7318,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674226</v>
+        <v>674316</v>
       </c>
       <c r="R67" t="n">
-        <v>7092929</v>
+        <v>7092989</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7372,15 +7368,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912579</v>
+        <v>126912625</v>
       </c>
       <c r="B73" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,21 +7892,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912680</v>
+        <v>126912579</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,21 +7989,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>674302</v>
+        <v>674239</v>
       </c>
       <c r="R74" t="n">
-        <v>7093031</v>
+        <v>7092908</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126919068</v>
+        <v>126912680</v>
       </c>
       <c r="B75" t="n">
         <v>79014</v>
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>673630</v>
+        <v>674302</v>
       </c>
       <c r="R75" t="n">
-        <v>7092929</v>
+        <v>7093031</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8160,26 +8160,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912590</v>
+        <v>126919068</v>
       </c>
       <c r="B76" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8187,39 +8183,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673958</v>
+        <v>673630</v>
       </c>
       <c r="R76" t="n">
-        <v>7093109</v>
+        <v>7092929</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8266,22 +8257,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126912625</v>
+        <v>126912590</v>
       </c>
       <c r="B77" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8289,34 +8284,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>674239</v>
+        <v>673958</v>
       </c>
       <c r="R77" t="n">
-        <v>7092908</v>
+        <v>7093109</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8375,50 +8375,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126912599</v>
+        <v>126912669</v>
       </c>
       <c r="B78" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674251</v>
+        <v>674218</v>
       </c>
       <c r="R78" t="n">
-        <v>7093028</v>
+        <v>7093013</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8477,32 +8472,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918795</v>
+        <v>126918802</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8512,10 +8507,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674236</v>
+        <v>674315</v>
       </c>
       <c r="R79" t="n">
-        <v>7092852</v>
+        <v>7093023</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8578,32 +8573,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126912669</v>
+        <v>126913210</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8613,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674218</v>
+        <v>674282</v>
       </c>
       <c r="R80" t="n">
-        <v>7093013</v>
+        <v>7092828</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8663,57 +8658,66 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918802</v>
+        <v>126912599</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674315</v>
+        <v>674251</v>
       </c>
       <c r="R81" t="n">
-        <v>7093023</v>
+        <v>7093028</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8760,48 +8764,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126913210</v>
+        <v>126918795</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674282</v>
+        <v>674236</v>
       </c>
       <c r="R82" t="n">
-        <v>7092828</v>
+        <v>7092852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8861,12 +8861,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9265,32 +9265,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912699</v>
+        <v>126915607</v>
       </c>
       <c r="B87" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674260</v>
+        <v>674262</v>
       </c>
       <c r="R87" t="n">
-        <v>7093031</v>
+        <v>7092824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9350,19 +9350,23 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126915607</v>
+        <v>126913212</v>
       </c>
       <c r="B88" t="n">
         <v>98443</v>
@@ -9397,10 +9401,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674262</v>
+        <v>674207</v>
       </c>
       <c r="R88" t="n">
-        <v>7092824</v>
+        <v>7092818</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9451,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,7 +9467,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126913212</v>
+        <v>126919037</v>
       </c>
       <c r="B89" t="n">
         <v>98443</v>
@@ -9498,10 +9502,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674207</v>
+        <v>673555</v>
       </c>
       <c r="R89" t="n">
-        <v>7092818</v>
+        <v>7093132</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9552,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,32 +9568,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126919037</v>
+        <v>126912699</v>
       </c>
       <c r="B90" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9603,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>673555</v>
+        <v>674260</v>
       </c>
       <c r="R90" t="n">
-        <v>7093132</v>
+        <v>7093031</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,19 +9653,15 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10857,45 +10857,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912575</v>
+        <v>126912642</v>
       </c>
       <c r="B103" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674215</v>
+        <v>674117</v>
       </c>
       <c r="R103" t="n">
-        <v>7092959</v>
+        <v>7092933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,45 +10963,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912572</v>
+        <v>126912637</v>
       </c>
       <c r="B104" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674310</v>
+        <v>674166</v>
       </c>
       <c r="R104" t="n">
-        <v>7092998</v>
+        <v>7092881</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11051,10 +11069,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912679</v>
+        <v>126912575</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11062,21 +11080,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11086,10 +11104,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674324</v>
+        <v>674215</v>
       </c>
       <c r="R105" t="n">
-        <v>7093051</v>
+        <v>7092959</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,10 +11166,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912671</v>
+        <v>126912572</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11159,21 +11177,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11183,10 +11201,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674238</v>
+        <v>674310</v>
       </c>
       <c r="R106" t="n">
-        <v>7093012</v>
+        <v>7092998</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11245,7 +11263,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126913197</v>
+        <v>126912679</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11280,10 +11298,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>673791</v>
+        <v>674324</v>
       </c>
       <c r="R107" t="n">
-        <v>7092931</v>
+        <v>7093051</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11330,23 +11348,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912686</v>
+        <v>126912671</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11381,10 +11395,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674222</v>
+        <v>674238</v>
       </c>
       <c r="R108" t="n">
-        <v>7092926</v>
+        <v>7093012</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11443,32 +11457,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126915582</v>
+        <v>126913197</v>
       </c>
       <c r="B109" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11478,10 +11492,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674302</v>
+        <v>673791</v>
       </c>
       <c r="R109" t="n">
-        <v>7093071</v>
+        <v>7092931</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11528,12 +11542,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11544,54 +11558,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912642</v>
+        <v>126912686</v>
       </c>
       <c r="B110" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674117</v>
+        <v>674222</v>
       </c>
       <c r="R110" t="n">
-        <v>7092933</v>
+        <v>7092926</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11650,54 +11655,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126912637</v>
+        <v>126915582</v>
       </c>
       <c r="B111" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674166</v>
+        <v>674302</v>
       </c>
       <c r="R111" t="n">
-        <v>7092881</v>
+        <v>7093071</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11744,15 +11740,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918800</v>
+        <v>126915585</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674103</v>
+        <v>674324</v>
       </c>
       <c r="R9" t="n">
-        <v>7093056</v>
+        <v>7093076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916005</v>
+        <v>126918800</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673879</v>
+        <v>674103</v>
       </c>
       <c r="R10" t="n">
-        <v>7092985</v>
+        <v>7093056</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918995</v>
+        <v>126916005</v>
       </c>
       <c r="B11" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673947</v>
+        <v>673879</v>
       </c>
       <c r="R11" t="n">
-        <v>7093045</v>
+        <v>7092985</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126915585</v>
+        <v>126918995</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>80021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674324</v>
+        <v>673947</v>
       </c>
       <c r="R12" t="n">
-        <v>7093076</v>
+        <v>7093045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912574</v>
+        <v>126915627</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674224</v>
+        <v>674167</v>
       </c>
       <c r="R18" t="n">
-        <v>7092965</v>
+        <v>7093069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,44 +2453,48 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912616</v>
+        <v>126912574</v>
       </c>
       <c r="B19" t="n">
-        <v>80145</v>
+        <v>79632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674220</v>
+        <v>674224</v>
       </c>
       <c r="R19" t="n">
-        <v>7092919</v>
+        <v>7092965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,32 +2566,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126915627</v>
+        <v>126912616</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674167</v>
+        <v>674220</v>
       </c>
       <c r="R20" t="n">
-        <v>7093069</v>
+        <v>7092919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,19 +2651,15 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912685</v>
+        <v>126918790</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674236</v>
+        <v>674101</v>
       </c>
       <c r="R42" t="n">
-        <v>7092969</v>
+        <v>7092979</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,44 +4854,48 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912666</v>
+        <v>126915612</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674176</v>
+        <v>674198</v>
       </c>
       <c r="R43" t="n">
-        <v>7093061</v>
+        <v>7092843</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,19 +4955,23 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126913207</v>
+        <v>126912685</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -4998,10 +5006,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674182</v>
+        <v>674236</v>
       </c>
       <c r="R44" t="n">
-        <v>7092837</v>
+        <v>7092969</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,23 +5056,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912683</v>
+        <v>126912666</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -5099,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674310</v>
+        <v>674176</v>
       </c>
       <c r="R45" t="n">
-        <v>7092998</v>
+        <v>7093061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5161,7 +5165,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919067</v>
+        <v>126913207</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5196,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673610</v>
+        <v>674182</v>
       </c>
       <c r="R46" t="n">
-        <v>7092955</v>
+        <v>7092837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5262,32 +5266,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126915572</v>
+        <v>126912683</v>
       </c>
       <c r="B47" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5297,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674324</v>
+        <v>674310</v>
       </c>
       <c r="R47" t="n">
-        <v>7093076</v>
+        <v>7092998</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5347,23 +5351,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919074</v>
+        <v>126919067</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673796</v>
+        <v>673610</v>
       </c>
       <c r="R48" t="n">
-        <v>7092899</v>
+        <v>7092955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5464,32 +5464,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126918790</v>
+        <v>126915572</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674101</v>
+        <v>674324</v>
       </c>
       <c r="R49" t="n">
-        <v>7092979</v>
+        <v>7093076</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,12 +5549,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5565,32 +5565,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126915612</v>
+        <v>126919074</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674198</v>
+        <v>673796</v>
       </c>
       <c r="R50" t="n">
-        <v>7092843</v>
+        <v>7092899</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918806</v>
+        <v>126912592</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674216</v>
+        <v>674188</v>
       </c>
       <c r="R60" t="n">
-        <v>7092860</v>
+        <v>7092955</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,26 +6673,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912592</v>
+        <v>126918996</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>80145</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6700,21 +6696,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6720,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674188</v>
+        <v>673948</v>
       </c>
       <c r="R61" t="n">
-        <v>7092955</v>
+        <v>7093016</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6774,44 +6770,48 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918996</v>
+        <v>126919031</v>
       </c>
       <c r="B62" t="n">
-        <v>80145</v>
+        <v>78772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673948</v>
+        <v>673796</v>
       </c>
       <c r="R62" t="n">
-        <v>7093016</v>
+        <v>7092899</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,12 +6871,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6887,32 +6887,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126919031</v>
+        <v>126912617</v>
       </c>
       <c r="B63" t="n">
-        <v>78772</v>
+        <v>80145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673796</v>
+        <v>674214</v>
       </c>
       <c r="R63" t="n">
-        <v>7092899</v>
+        <v>7092881</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,48 +6972,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126912617</v>
+        <v>126918806</v>
       </c>
       <c r="B64" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674214</v>
+        <v>674216</v>
       </c>
       <c r="R64" t="n">
-        <v>7092881</v>
+        <v>7092860</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7073,15 +7069,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9265,32 +9265,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126915607</v>
+        <v>126912699</v>
       </c>
       <c r="B87" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674262</v>
+        <v>674260</v>
       </c>
       <c r="R87" t="n">
-        <v>7092824</v>
+        <v>7093031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9350,23 +9350,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126913212</v>
+        <v>126915607</v>
       </c>
       <c r="B88" t="n">
         <v>98443</v>
@@ -9401,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674207</v>
+        <v>674262</v>
       </c>
       <c r="R88" t="n">
-        <v>7092818</v>
+        <v>7092824</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9451,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9467,7 +9463,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126919037</v>
+        <v>126913212</v>
       </c>
       <c r="B89" t="n">
         <v>98443</v>
@@ -9502,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>673555</v>
+        <v>674207</v>
       </c>
       <c r="R89" t="n">
-        <v>7093132</v>
+        <v>7092818</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9552,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9568,32 +9564,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126912699</v>
+        <v>126919037</v>
       </c>
       <c r="B90" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9603,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674260</v>
+        <v>673555</v>
       </c>
       <c r="R90" t="n">
-        <v>7093031</v>
+        <v>7093132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9653,22 +9649,26 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918807</v>
+        <v>126912703</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674208</v>
+        <v>674269</v>
       </c>
       <c r="R91" t="n">
-        <v>7092856</v>
+        <v>7092979</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,23 +9750,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126913181</v>
+        <v>126918807</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -9801,10 +9797,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674236</v>
+        <v>674208</v>
       </c>
       <c r="R92" t="n">
-        <v>7093024</v>
+        <v>7092856</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9851,12 +9847,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9867,10 +9863,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912578</v>
+        <v>126913181</v>
       </c>
       <c r="B93" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9878,21 +9874,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9902,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674218</v>
+        <v>674236</v>
       </c>
       <c r="R93" t="n">
-        <v>7092914</v>
+        <v>7093024</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9952,44 +9948,48 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126912614</v>
+        <v>126912578</v>
       </c>
       <c r="B94" t="n">
-        <v>80145</v>
+        <v>79632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674319</v>
+        <v>674218</v>
       </c>
       <c r="R94" t="n">
-        <v>7093047</v>
+        <v>7092914</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10061,32 +10061,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912634</v>
+        <v>126912614</v>
       </c>
       <c r="B95" t="n">
-        <v>78772</v>
+        <v>80145</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674203</v>
+        <v>674319</v>
       </c>
       <c r="R95" t="n">
-        <v>7092932</v>
+        <v>7093047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10158,7 +10158,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126918789</v>
+        <v>126912634</v>
       </c>
       <c r="B96" t="n">
         <v>78772</v>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674310</v>
+        <v>674203</v>
       </c>
       <c r="R96" t="n">
-        <v>7092997</v>
+        <v>7092932</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10243,26 +10243,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918984</v>
+        <v>126918789</v>
       </c>
       <c r="B97" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,21 +10266,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10290,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>673919</v>
+        <v>674310</v>
       </c>
       <c r="R97" t="n">
-        <v>7093017</v>
+        <v>7092997</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,12 +10340,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10360,10 +10356,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126919072</v>
+        <v>126918984</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10371,21 +10367,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10395,10 +10391,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>673738</v>
+        <v>673919</v>
       </c>
       <c r="R98" t="n">
-        <v>7092885</v>
+        <v>7093017</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10445,12 +10441,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10461,32 +10457,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915609</v>
+        <v>126919072</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10496,10 +10492,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674231</v>
+        <v>673738</v>
       </c>
       <c r="R99" t="n">
-        <v>7092812</v>
+        <v>7092885</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10546,12 +10542,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10562,10 +10558,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126912703</v>
+        <v>126912624</v>
       </c>
       <c r="B100" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10573,21 +10569,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10597,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674269</v>
+        <v>674218</v>
       </c>
       <c r="R100" t="n">
-        <v>7092979</v>
+        <v>7092914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10760,32 +10756,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126912624</v>
+        <v>126915609</v>
       </c>
       <c r="B102" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10795,10 +10791,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674218</v>
+        <v>674231</v>
       </c>
       <c r="R102" t="n">
-        <v>7092914</v>
+        <v>7092812</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10845,66 +10841,61 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912642</v>
+        <v>126915582</v>
       </c>
       <c r="B103" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674117</v>
+        <v>674302</v>
       </c>
       <c r="R103" t="n">
-        <v>7092933</v>
+        <v>7093071</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10951,19 +10942,23 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912637</v>
+        <v>126912642</v>
       </c>
       <c r="B104" t="n">
         <v>98443</v>
@@ -10993,7 +10988,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11007,10 +11002,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674166</v>
+        <v>674117</v>
       </c>
       <c r="R104" t="n">
-        <v>7092881</v>
+        <v>7092933</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11069,45 +11064,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912575</v>
+        <v>126912637</v>
       </c>
       <c r="B105" t="n">
-        <v>79632</v>
+        <v>98443</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674215</v>
+        <v>674166</v>
       </c>
       <c r="R105" t="n">
-        <v>7092959</v>
+        <v>7092881</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11166,10 +11170,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912572</v>
+        <v>126912679</v>
       </c>
       <c r="B106" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11177,21 +11181,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11201,10 +11205,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674310</v>
+        <v>674324</v>
       </c>
       <c r="R106" t="n">
-        <v>7092998</v>
+        <v>7093051</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11263,7 +11267,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126912679</v>
+        <v>126912671</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11298,10 +11302,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674324</v>
+        <v>674238</v>
       </c>
       <c r="R107" t="n">
-        <v>7093051</v>
+        <v>7093012</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11360,7 +11364,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912671</v>
+        <v>126913197</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11395,10 +11399,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674238</v>
+        <v>673791</v>
       </c>
       <c r="R108" t="n">
-        <v>7093012</v>
+        <v>7092931</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11445,19 +11449,23 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126913197</v>
+        <v>126912686</v>
       </c>
       <c r="B109" t="n">
         <v>79014</v>
@@ -11492,10 +11500,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>673791</v>
+        <v>674222</v>
       </c>
       <c r="R109" t="n">
-        <v>7092931</v>
+        <v>7092926</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11542,26 +11550,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912686</v>
+        <v>126912575</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11569,21 +11573,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11593,10 +11597,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674222</v>
+        <v>674215</v>
       </c>
       <c r="R110" t="n">
-        <v>7092926</v>
+        <v>7092959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11655,32 +11659,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126915582</v>
+        <v>126912572</v>
       </c>
       <c r="B111" t="n">
-        <v>98464</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674302</v>
+        <v>674310</v>
       </c>
       <c r="R111" t="n">
-        <v>7093071</v>
+        <v>7092998</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11740,26 +11744,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126912689</v>
+        <v>126918998</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674237</v>
+        <v>673861</v>
       </c>
       <c r="R112" t="n">
-        <v>7092921</v>
+        <v>7093031</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,22 +11841,26 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918801</v>
+        <v>126918776</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11864,21 +11868,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11888,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674148</v>
+        <v>674139</v>
       </c>
       <c r="R113" t="n">
-        <v>7093061</v>
+        <v>7092939</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11954,32 +11958,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918810</v>
+        <v>126915628</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11993,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674189</v>
+        <v>674258</v>
       </c>
       <c r="R114" t="n">
-        <v>7092854</v>
+        <v>7093046</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,12 +12043,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12055,10 +12059,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126912577</v>
+        <v>126912689</v>
       </c>
       <c r="B115" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12070,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12094,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674204</v>
+        <v>674237</v>
       </c>
       <c r="R115" t="n">
-        <v>7092934</v>
+        <v>7092921</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12152,10 +12156,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918998</v>
+        <v>126918801</v>
       </c>
       <c r="B116" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12163,21 +12167,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12191,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>673861</v>
+        <v>674148</v>
       </c>
       <c r="R116" t="n">
-        <v>7093031</v>
+        <v>7093061</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12237,12 +12241,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12253,10 +12257,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918776</v>
+        <v>126918810</v>
       </c>
       <c r="B117" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12264,21 +12268,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12288,10 +12292,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674139</v>
+        <v>674189</v>
       </c>
       <c r="R117" t="n">
-        <v>7092939</v>
+        <v>7092854</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12354,32 +12358,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126915628</v>
+        <v>126912577</v>
       </c>
       <c r="B118" t="n">
-        <v>98360</v>
+        <v>79632</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12393,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674258</v>
+        <v>674204</v>
       </c>
       <c r="R118" t="n">
-        <v>7093046</v>
+        <v>7092934</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12439,26 +12443,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126912708</v>
+        <v>126918808</v>
       </c>
       <c r="B119" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>674243</v>
+        <v>674199</v>
       </c>
       <c r="R119" t="n">
-        <v>7092914</v>
+        <v>7092849</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12528,11 +12528,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12545,22 +12540,26 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126918808</v>
+        <v>126912708</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12568,21 +12567,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12592,10 +12591,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674199</v>
+        <v>674243</v>
       </c>
       <c r="R120" t="n">
-        <v>7092849</v>
+        <v>7092914</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12630,6 +12629,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12642,19 +12646,15 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13846,32 +13846,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912675</v>
+        <v>126912593</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674268</v>
+        <v>674210</v>
       </c>
       <c r="R133" t="n">
-        <v>7093042</v>
+        <v>7092877</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13943,10 +13943,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126918997</v>
+        <v>126913960</v>
       </c>
       <c r="B134" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13954,34 +13954,38 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>673855</v>
+        <v>673577</v>
       </c>
       <c r="R134" t="n">
-        <v>7093043</v>
+        <v>7093132</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14016,6 +14020,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14028,12 +14037,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14150,32 +14159,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126912593</v>
+        <v>126912675</v>
       </c>
       <c r="B136" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14185,10 +14194,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>674210</v>
+        <v>674268</v>
       </c>
       <c r="R136" t="n">
-        <v>7092877</v>
+        <v>7093042</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14247,10 +14256,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126913960</v>
+        <v>126918997</v>
       </c>
       <c r="B137" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14258,38 +14267,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>673577</v>
+        <v>673855</v>
       </c>
       <c r="R137" t="n">
-        <v>7093132</v>
+        <v>7093043</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14324,11 +14329,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD137" t="b">
         <v>0</v>
       </c>
@@ -14341,12 +14341,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14559,10 +14559,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126919027</v>
+        <v>126912678</v>
       </c>
       <c r="B140" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14570,21 +14570,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14594,10 +14594,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>673554</v>
+        <v>674334</v>
       </c>
       <c r="R140" t="n">
-        <v>7093135</v>
+        <v>7093055</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14644,26 +14644,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126912678</v>
+        <v>126919027</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14671,21 +14667,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14695,10 +14691,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>674334</v>
+        <v>673554</v>
       </c>
       <c r="R141" t="n">
-        <v>7093055</v>
+        <v>7093135</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14745,15 +14741,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14858,10 +14858,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126915991</v>
+        <v>126915629</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>98360</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14869,21 +14869,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14893,13 +14893,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>673971</v>
+        <v>674305</v>
       </c>
       <c r="R143" t="n">
-        <v>7092936</v>
+        <v>7093077</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14943,12 +14943,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14959,32 +14959,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126919007</v>
+        <v>126919041</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14994,10 +14994,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>673940</v>
+        <v>673735</v>
       </c>
       <c r="R144" t="n">
-        <v>7093045</v>
+        <v>7092926</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15032,30 +15032,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15066,7 +15060,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126912670</v>
+        <v>126919007</v>
       </c>
       <c r="B145" t="n">
         <v>79014</v>
@@ -15101,10 +15095,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>674225</v>
+        <v>673940</v>
       </c>
       <c r="R145" t="n">
-        <v>7093014</v>
+        <v>7093045</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15139,31 +15133,41 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126912651</v>
+        <v>126912670</v>
       </c>
       <c r="B146" t="n">
         <v>79014</v>
@@ -15198,10 +15202,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>674297</v>
+        <v>674225</v>
       </c>
       <c r="R146" t="n">
-        <v>7092976</v>
+        <v>7093014</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15234,11 +15238,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15265,7 +15264,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126913182</v>
+        <v>126912651</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15300,10 +15299,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>674316</v>
+        <v>674297</v>
       </c>
       <c r="R147" t="n">
-        <v>7093018</v>
+        <v>7092976</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15338,6 +15337,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -15350,23 +15354,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126912676</v>
+        <v>126913182</v>
       </c>
       <c r="B148" t="n">
         <v>79014</v>
@@ -15401,10 +15401,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>674259</v>
+        <v>674316</v>
       </c>
       <c r="R148" t="n">
-        <v>7093064</v>
+        <v>7093018</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15451,19 +15451,23 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126912688</v>
+        <v>126912676</v>
       </c>
       <c r="B149" t="n">
         <v>79014</v>
@@ -15498,10 +15502,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>674231</v>
+        <v>674259</v>
       </c>
       <c r="R149" t="n">
-        <v>7092932</v>
+        <v>7093064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15560,32 +15564,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126919075</v>
+        <v>126915991</v>
       </c>
       <c r="B150" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15595,13 +15599,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>673825</v>
+        <v>673971</v>
       </c>
       <c r="R150" t="n">
-        <v>7092923</v>
+        <v>7092936</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15645,12 +15649,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15661,7 +15665,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126919069</v>
+        <v>126912688</v>
       </c>
       <c r="B151" t="n">
         <v>79014</v>
@@ -15696,10 +15700,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>673685</v>
+        <v>674231</v>
       </c>
       <c r="R151" t="n">
-        <v>7092946</v>
+        <v>7092932</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15746,48 +15750,44 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126919017</v>
+        <v>126919075</v>
       </c>
       <c r="B152" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15797,10 +15797,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>673668</v>
+        <v>673825</v>
       </c>
       <c r="R152" t="n">
-        <v>7092943</v>
+        <v>7092923</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15833,11 +15833,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15868,32 +15863,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126915629</v>
+        <v>126919069</v>
       </c>
       <c r="B153" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15903,10 +15898,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>674305</v>
+        <v>673685</v>
       </c>
       <c r="R153" t="n">
-        <v>7093077</v>
+        <v>7092946</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15953,12 +15948,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -15969,32 +15964,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126919041</v>
+        <v>126919017</v>
       </c>
       <c r="B154" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16004,10 +15999,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>673735</v>
+        <v>673668</v>
       </c>
       <c r="R154" t="n">
-        <v>7092926</v>
+        <v>7092943</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16040,6 +16035,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126915634</v>
+        <v>126912692</v>
       </c>
       <c r="B155" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674163</v>
+        <v>674236</v>
       </c>
       <c r="R155" t="n">
-        <v>7092870</v>
+        <v>7092908</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,48 +16155,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126915613</v>
+        <v>126919063</v>
       </c>
       <c r="B156" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16206,10 +16202,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>674171</v>
+        <v>673530</v>
       </c>
       <c r="R156" t="n">
-        <v>7092865</v>
+        <v>7093126</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16256,12 +16252,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16272,32 +16268,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126918792</v>
+        <v>126919070</v>
       </c>
       <c r="B157" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16307,10 +16303,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>674129</v>
+        <v>673731</v>
       </c>
       <c r="R157" t="n">
-        <v>7093003</v>
+        <v>7092924</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16357,12 +16353,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16373,10 +16369,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126915603</v>
+        <v>126915634</v>
       </c>
       <c r="B158" t="n">
-        <v>98347</v>
+        <v>98360</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16384,21 +16380,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16408,10 +16404,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674278</v>
+        <v>674163</v>
       </c>
       <c r="R158" t="n">
-        <v>7092923</v>
+        <v>7092870</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16474,32 +16470,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126915602</v>
+        <v>126915613</v>
       </c>
       <c r="B159" t="n">
-        <v>98347</v>
+        <v>98443</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16509,10 +16505,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674319</v>
+        <v>674171</v>
       </c>
       <c r="R159" t="n">
-        <v>7092980</v>
+        <v>7092865</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16575,32 +16571,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126912692</v>
+        <v>126918792</v>
       </c>
       <c r="B160" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16610,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>674236</v>
+        <v>674129</v>
       </c>
       <c r="R160" t="n">
-        <v>7092908</v>
+        <v>7093003</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16660,44 +16656,48 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126919063</v>
+        <v>126915603</v>
       </c>
       <c r="B161" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>673530</v>
+        <v>674278</v>
       </c>
       <c r="R161" t="n">
-        <v>7093126</v>
+        <v>7092923</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16757,12 +16757,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16773,32 +16773,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126919070</v>
+        <v>126915602</v>
       </c>
       <c r="B162" t="n">
-        <v>79014</v>
+        <v>98347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>673731</v>
+        <v>674319</v>
       </c>
       <c r="R162" t="n">
-        <v>7092924</v>
+        <v>7092980</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,12 +16858,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16874,32 +16874,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126912704</v>
+        <v>126915599</v>
       </c>
       <c r="B163" t="n">
-        <v>78681</v>
+        <v>98347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674200</v>
+        <v>674272</v>
       </c>
       <c r="R163" t="n">
-        <v>7092950</v>
+        <v>7093054</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16959,22 +16959,26 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126918809</v>
+        <v>126912704</v>
       </c>
       <c r="B164" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16982,21 +16986,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17010,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674196</v>
+        <v>674200</v>
       </c>
       <c r="R164" t="n">
-        <v>7092846</v>
+        <v>7092950</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17056,23 +17060,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126912684</v>
+        <v>126918809</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17107,10 +17107,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>674292</v>
+        <v>674196</v>
       </c>
       <c r="R165" t="n">
-        <v>7092976</v>
+        <v>7092846</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17157,44 +17157,48 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126912594</v>
+        <v>126912684</v>
       </c>
       <c r="B166" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17204,10 +17208,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674121</v>
+        <v>674292</v>
       </c>
       <c r="R166" t="n">
-        <v>7092931</v>
+        <v>7092976</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17266,10 +17270,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126918993</v>
+        <v>126912594</v>
       </c>
       <c r="B167" t="n">
-        <v>80021</v>
+        <v>80146</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17277,21 +17281,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17301,10 +17305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>673937</v>
+        <v>674121</v>
       </c>
       <c r="R167" t="n">
-        <v>7093103</v>
+        <v>7092931</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17345,33 +17349,28 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126915599</v>
+        <v>126918993</v>
       </c>
       <c r="B168" t="n">
-        <v>98347</v>
+        <v>80021</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17379,21 +17378,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17403,10 +17402,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674272</v>
+        <v>673937</v>
       </c>
       <c r="R168" t="n">
-        <v>7093054</v>
+        <v>7093103</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17447,6 +17446,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126915585</v>
+        <v>126918800</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674324</v>
+        <v>674103</v>
       </c>
       <c r="R9" t="n">
-        <v>7093076</v>
+        <v>7093056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918800</v>
+        <v>126915632</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674103</v>
+        <v>674279</v>
       </c>
       <c r="R10" t="n">
-        <v>7093056</v>
+        <v>7092915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126916005</v>
+        <v>126918793</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673879</v>
+        <v>674251</v>
       </c>
       <c r="R11" t="n">
-        <v>7092985</v>
+        <v>7092837</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918995</v>
+        <v>126913215</v>
       </c>
       <c r="B12" t="n">
-        <v>80021</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673947</v>
+        <v>674258</v>
       </c>
       <c r="R12" t="n">
-        <v>7093045</v>
+        <v>7092817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919065</v>
+        <v>126919040</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673619</v>
+        <v>673649</v>
       </c>
       <c r="R13" t="n">
-        <v>7092978</v>
+        <v>7092943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126915632</v>
+        <v>126918995</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>80025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674279</v>
+        <v>673947</v>
       </c>
       <c r="R14" t="n">
-        <v>7092915</v>
+        <v>7093045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919040</v>
+        <v>126919065</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673649</v>
+        <v>673619</v>
       </c>
       <c r="R15" t="n">
-        <v>7092943</v>
+        <v>7092978</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918793</v>
+        <v>126916005</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>674251</v>
+        <v>673879</v>
       </c>
       <c r="R16" t="n">
-        <v>7092837</v>
+        <v>7092985</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126913215</v>
+        <v>126915585</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674258</v>
+        <v>674324</v>
       </c>
       <c r="R17" t="n">
-        <v>7092817</v>
+        <v>7093076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126915627</v>
+        <v>126912574</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674167</v>
+        <v>674224</v>
       </c>
       <c r="R18" t="n">
-        <v>7093069</v>
+        <v>7092965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,26 +2453,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912574</v>
+        <v>126915627</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674224</v>
+        <v>674167</v>
       </c>
       <c r="R19" t="n">
-        <v>7092965</v>
+        <v>7093069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,22 +2550,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126912616</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126919035</v>
+        <v>126915606</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673577</v>
+        <v>674275</v>
       </c>
       <c r="R21" t="n">
-        <v>7093132</v>
+        <v>7092845</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,12 +2748,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126915611</v>
+        <v>126913188</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674207</v>
+        <v>673761</v>
       </c>
       <c r="R22" t="n">
-        <v>7092810</v>
+        <v>7092946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126913188</v>
+        <v>126919035</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673761</v>
+        <v>673577</v>
       </c>
       <c r="R23" t="n">
-        <v>7092946</v>
+        <v>7093132</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,12 +2950,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126915606</v>
+        <v>126915611</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674275</v>
+        <v>674207</v>
       </c>
       <c r="R24" t="n">
-        <v>7092845</v>
+        <v>7092810</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,7 +3070,7 @@
         <v>126912667</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
         <v>126912633</v>
       </c>
       <c r="B26" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126915593</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>126919077</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>126919071</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3564,32 +3564,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126915590</v>
+        <v>126913209</v>
       </c>
       <c r="B30" t="n">
-        <v>58488</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674272</v>
+        <v>674212</v>
       </c>
       <c r="R30" t="n">
-        <v>7092912</v>
+        <v>7092826</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3665,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918783</v>
+        <v>126919043</v>
       </c>
       <c r="B31" t="n">
-        <v>98464</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674284</v>
+        <v>673945</v>
       </c>
       <c r="R31" t="n">
-        <v>7093057</v>
+        <v>7092938</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,12 +3750,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3766,32 +3766,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126919043</v>
+        <v>126918783</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>673945</v>
+        <v>674284</v>
       </c>
       <c r="R32" t="n">
-        <v>7092938</v>
+        <v>7093057</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126913209</v>
+        <v>126915590</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>58492</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674212</v>
+        <v>674272</v>
       </c>
       <c r="R33" t="n">
-        <v>7092826</v>
+        <v>7092912</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3971,7 +3971,7 @@
         <v>126918803</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>126912691</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126912681</v>
+        <v>126912635</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674304</v>
+        <v>674239</v>
       </c>
       <c r="R36" t="n">
-        <v>7093019</v>
+        <v>7092908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919009</v>
+        <v>126912681</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673944</v>
+        <v>674304</v>
       </c>
       <c r="R37" t="n">
-        <v>7093050</v>
+        <v>7093019</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,11 +4336,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4353,26 +4348,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919008</v>
+        <v>126919009</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673843</v>
+        <v>673944</v>
       </c>
       <c r="R38" t="n">
-        <v>7093104</v>
+        <v>7093050</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4440,6 +4431,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4470,10 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912635</v>
+        <v>126919078</v>
       </c>
       <c r="B39" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4477,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4501,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674239</v>
+        <v>673893</v>
       </c>
       <c r="R39" t="n">
-        <v>7092908</v>
+        <v>7092920</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,22 +4551,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919078</v>
+        <v>126919008</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673893</v>
+        <v>673843</v>
       </c>
       <c r="R40" t="n">
-        <v>7092920</v>
+        <v>7093104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,12 +4652,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4671,7 +4671,7 @@
         <v>126913201</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126918790</v>
+        <v>126912685</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674101</v>
+        <v>674236</v>
       </c>
       <c r="R42" t="n">
-        <v>7092979</v>
+        <v>7092969</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,48 +4854,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126915612</v>
+        <v>126912666</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674198</v>
+        <v>674176</v>
       </c>
       <c r="R43" t="n">
-        <v>7092843</v>
+        <v>7093061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,26 +4951,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912685</v>
+        <v>126913207</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5006,10 +4998,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674236</v>
+        <v>674182</v>
       </c>
       <c r="R44" t="n">
-        <v>7092969</v>
+        <v>7092837</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5056,22 +5048,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912666</v>
+        <v>126919067</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5103,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674176</v>
+        <v>673610</v>
       </c>
       <c r="R45" t="n">
-        <v>7093061</v>
+        <v>7092955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,44 +5149,48 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913207</v>
+        <v>126915572</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674182</v>
+        <v>674324</v>
       </c>
       <c r="R46" t="n">
-        <v>7092837</v>
+        <v>7093076</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5266,10 +5266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912683</v>
+        <v>126919074</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674310</v>
+        <v>673796</v>
       </c>
       <c r="R47" t="n">
-        <v>7092998</v>
+        <v>7092899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,22 +5351,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919067</v>
+        <v>126912683</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673610</v>
+        <v>674310</v>
       </c>
       <c r="R48" t="n">
-        <v>7092955</v>
+        <v>7092998</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,48 +5452,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126915572</v>
+        <v>126915612</v>
       </c>
       <c r="B49" t="n">
-        <v>91291</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674324</v>
+        <v>674198</v>
       </c>
       <c r="R49" t="n">
-        <v>7093076</v>
+        <v>7092843</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,32 +5565,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919074</v>
+        <v>126918790</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>673796</v>
+        <v>674101</v>
       </c>
       <c r="R50" t="n">
-        <v>7092899</v>
+        <v>7092979</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919000</v>
+        <v>126912576</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>673939</v>
+        <v>674200</v>
       </c>
       <c r="R51" t="n">
-        <v>7093012</v>
+        <v>7092950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,26 +5751,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126915630</v>
+        <v>126913179</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>80025</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,34 +5774,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>674328</v>
+        <v>673719</v>
       </c>
       <c r="R52" t="n">
-        <v>7092980</v>
+        <v>7093035</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5846,18 +5845,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,32 +5868,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912700</v>
+        <v>126919076</v>
       </c>
       <c r="B53" t="n">
-        <v>98360</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674267</v>
+        <v>673836</v>
       </c>
       <c r="R53" t="n">
-        <v>7093044</v>
+        <v>7092910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5953,73 +5953,61 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913214</v>
+        <v>126915630</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674219</v>
+        <v>674328</v>
       </c>
       <c r="R54" t="n">
-        <v>7092815</v>
+        <v>7092980</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6060,19 +6048,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6083,32 +6070,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913208</v>
+        <v>126912700</v>
       </c>
       <c r="B55" t="n">
-        <v>91276</v>
+        <v>98364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>112</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6118,10 +6105,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674181</v>
+        <v>674267</v>
       </c>
       <c r="R55" t="n">
-        <v>7092836</v>
+        <v>7093044</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6168,61 +6155,73 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912576</v>
+        <v>126913214</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674200</v>
+        <v>674219</v>
       </c>
       <c r="R56" t="n">
-        <v>7092950</v>
+        <v>7092815</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6263,66 +6262,68 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126913179</v>
+        <v>126915608</v>
       </c>
       <c r="B57" t="n">
-        <v>80021</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673719</v>
+        <v>674257</v>
       </c>
       <c r="R57" t="n">
-        <v>7093035</v>
+        <v>7092823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6363,19 +6364,18 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6386,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919076</v>
+        <v>126919000</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,21 +6397,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673836</v>
+        <v>673939</v>
       </c>
       <c r="R58" t="n">
-        <v>7092910</v>
+        <v>7093012</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6471,12 +6471,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6487,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126915608</v>
+        <v>126913208</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>91280</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674257</v>
+        <v>674181</v>
       </c>
       <c r="R59" t="n">
-        <v>7092823</v>
+        <v>7092836</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,12 +6572,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6591,7 +6591,7 @@
         <v>126912592</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6685,32 +6685,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918996</v>
+        <v>126918806</v>
       </c>
       <c r="B61" t="n">
-        <v>80145</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673948</v>
+        <v>674216</v>
       </c>
       <c r="R61" t="n">
-        <v>7093016</v>
+        <v>7092860</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6770,12 +6770,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6786,32 +6786,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919031</v>
+        <v>126918996</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673796</v>
+        <v>673948</v>
       </c>
       <c r="R62" t="n">
-        <v>7092899</v>
+        <v>7093016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,12 +6871,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6887,32 +6887,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912617</v>
+        <v>126919031</v>
       </c>
       <c r="B63" t="n">
-        <v>80145</v>
+        <v>78776</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>674214</v>
+        <v>673796</v>
       </c>
       <c r="R63" t="n">
-        <v>7092881</v>
+        <v>7092899</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,44 +6972,48 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126918806</v>
+        <v>126912617</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7019,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674216</v>
+        <v>674214</v>
       </c>
       <c r="R64" t="n">
-        <v>7092860</v>
+        <v>7092881</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,26 +7073,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>126912687</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7182,32 +7182,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918787</v>
+        <v>126912622</v>
       </c>
       <c r="B66" t="n">
-        <v>98464</v>
+        <v>78777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674167</v>
+        <v>674225</v>
       </c>
       <c r="R66" t="n">
-        <v>7092848</v>
+        <v>7092965</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7267,48 +7267,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126915584</v>
+        <v>126912620</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>78777</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7318,10 +7314,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674316</v>
+        <v>674229</v>
       </c>
       <c r="R67" t="n">
-        <v>7092989</v>
+        <v>7092964</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,26 +7364,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126912622</v>
+        <v>126918999</v>
       </c>
       <c r="B68" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,10 +7411,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674225</v>
+        <v>673919</v>
       </c>
       <c r="R68" t="n">
-        <v>7092965</v>
+        <v>7093017</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7469,44 +7461,48 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126912620</v>
+        <v>126913211</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7516,10 +7512,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>674229</v>
+        <v>674214</v>
       </c>
       <c r="R69" t="n">
-        <v>7092964</v>
+        <v>7092818</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7566,44 +7562,48 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918999</v>
+        <v>126919039</v>
       </c>
       <c r="B70" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>673919</v>
+        <v>673525</v>
       </c>
       <c r="R70" t="n">
-        <v>7093017</v>
+        <v>7093040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7663,12 +7663,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7679,32 +7679,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126919039</v>
+        <v>126918787</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>673525</v>
+        <v>674167</v>
       </c>
       <c r="R71" t="n">
-        <v>7093040</v>
+        <v>7092848</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,12 +7764,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7780,32 +7780,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126913211</v>
+        <v>126915584</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>674214</v>
+        <v>674316</v>
       </c>
       <c r="R72" t="n">
-        <v>7092818</v>
+        <v>7092989</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912625</v>
+        <v>126912590</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>57821</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,34 +7892,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674239</v>
+        <v>673958</v>
       </c>
       <c r="R73" t="n">
-        <v>7092908</v>
+        <v>7093109</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7978,10 +7983,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912579</v>
+        <v>126912625</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,21 +7994,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8075,10 +8080,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912680</v>
+        <v>126912579</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8086,21 +8091,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8110,10 +8115,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674302</v>
+        <v>674239</v>
       </c>
       <c r="R75" t="n">
-        <v>7093031</v>
+        <v>7092908</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8172,10 +8177,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126919068</v>
+        <v>126912680</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8207,10 +8212,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673630</v>
+        <v>674302</v>
       </c>
       <c r="R76" t="n">
-        <v>7092929</v>
+        <v>7093031</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8257,26 +8262,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126912590</v>
+        <v>126919068</v>
       </c>
       <c r="B77" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8284,39 +8285,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>673958</v>
+        <v>673630</v>
       </c>
       <c r="R77" t="n">
-        <v>7093109</v>
+        <v>7092929</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8363,22 +8359,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>126912669</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8465,39 +8465,39 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126918802</v>
+        <v>126913210</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674315</v>
+        <v>674282</v>
       </c>
       <c r="R79" t="n">
-        <v>7093023</v>
+        <v>7092828</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,12 +8557,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8573,32 +8573,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913210</v>
+        <v>126918802</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674282</v>
+        <v>674315</v>
       </c>
       <c r="R80" t="n">
-        <v>7092828</v>
+        <v>7093023</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8658,12 +8658,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8674,50 +8674,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126912599</v>
+        <v>126918795</v>
       </c>
       <c r="B81" t="n">
-        <v>98464</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674251</v>
+        <v>674236</v>
       </c>
       <c r="R81" t="n">
-        <v>7093028</v>
+        <v>7092852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8764,57 +8759,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918795</v>
+        <v>126912599</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674236</v>
+        <v>674251</v>
       </c>
       <c r="R82" t="n">
-        <v>7092852</v>
+        <v>7093028</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8861,26 +8865,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126912668</v>
+        <v>126912674</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674214</v>
+        <v>674251</v>
       </c>
       <c r="R83" t="n">
-        <v>7093041</v>
+        <v>7093028</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8974,32 +8974,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126912672</v>
+        <v>126913212</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674248</v>
+        <v>674207</v>
       </c>
       <c r="R84" t="n">
-        <v>7093018</v>
+        <v>7092818</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9059,44 +9059,48 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912618</v>
+        <v>126919037</v>
       </c>
       <c r="B85" t="n">
-        <v>80145</v>
+        <v>98447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9106,10 +9110,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674104</v>
+        <v>673555</v>
       </c>
       <c r="R85" t="n">
-        <v>7092938</v>
+        <v>7093132</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9156,44 +9160,48 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126912674</v>
+        <v>126915607</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9203,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674251</v>
+        <v>674262</v>
       </c>
       <c r="R86" t="n">
-        <v>7093028</v>
+        <v>7092824</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9253,44 +9261,48 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912699</v>
+        <v>126912668</v>
       </c>
       <c r="B87" t="n">
-        <v>98360</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,10 +9312,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674260</v>
+        <v>674214</v>
       </c>
       <c r="R87" t="n">
-        <v>7093031</v>
+        <v>7093041</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9355,39 +9367,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126915607</v>
+        <v>126912618</v>
       </c>
       <c r="B88" t="n">
-        <v>98443</v>
+        <v>80149</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9409,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674262</v>
+        <v>674104</v>
       </c>
       <c r="R88" t="n">
-        <v>7092824</v>
+        <v>7092938</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,48 +9459,44 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126913212</v>
+        <v>126912672</v>
       </c>
       <c r="B89" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9498,10 +9506,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674207</v>
+        <v>674248</v>
       </c>
       <c r="R89" t="n">
-        <v>7092818</v>
+        <v>7093018</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,48 +9556,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126919037</v>
+        <v>126912699</v>
       </c>
       <c r="B90" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9603,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>673555</v>
+        <v>674260</v>
       </c>
       <c r="R90" t="n">
-        <v>7093132</v>
+        <v>7093031</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,26 +9653,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912703</v>
+        <v>126918807</v>
       </c>
       <c r="B91" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674269</v>
+        <v>674208</v>
       </c>
       <c r="R91" t="n">
-        <v>7092979</v>
+        <v>7092856</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,22 +9750,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918807</v>
+        <v>126912578</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9773,21 +9777,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9797,10 +9801,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674208</v>
+        <v>674218</v>
       </c>
       <c r="R92" t="n">
-        <v>7092856</v>
+        <v>7092914</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9847,26 +9851,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126913181</v>
+        <v>126912634</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674236</v>
+        <v>674203</v>
       </c>
       <c r="R93" t="n">
-        <v>7093024</v>
+        <v>7092932</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9948,26 +9948,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126912578</v>
+        <v>126918789</v>
       </c>
       <c r="B94" t="n">
-        <v>79632</v>
+        <v>78776</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9975,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9999,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R94" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10049,44 +10045,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912614</v>
+        <v>126918984</v>
       </c>
       <c r="B95" t="n">
-        <v>80145</v>
+        <v>79636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674319</v>
+        <v>673919</v>
       </c>
       <c r="R95" t="n">
-        <v>7093047</v>
+        <v>7093017</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,22 +10146,26 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126912634</v>
+        <v>126913181</v>
       </c>
       <c r="B96" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10169,21 +10173,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10193,10 +10197,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674203</v>
+        <v>674236</v>
       </c>
       <c r="R96" t="n">
-        <v>7092932</v>
+        <v>7093024</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10243,22 +10247,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918789</v>
+        <v>126919072</v>
       </c>
       <c r="B97" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10266,21 +10274,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10290,10 +10298,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674310</v>
+        <v>673738</v>
       </c>
       <c r="R97" t="n">
-        <v>7092997</v>
+        <v>7092885</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10340,12 +10348,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10356,10 +10364,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918984</v>
+        <v>126912703</v>
       </c>
       <c r="B98" t="n">
-        <v>79632</v>
+        <v>78685</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10367,21 +10375,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10391,10 +10399,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>673919</v>
+        <v>674269</v>
       </c>
       <c r="R98" t="n">
-        <v>7093017</v>
+        <v>7092979</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,26 +10449,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126919072</v>
+        <v>126912624</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10468,21 +10472,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10492,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>673738</v>
+        <v>674218</v>
       </c>
       <c r="R99" t="n">
-        <v>7092885</v>
+        <v>7092914</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10542,48 +10546,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126912624</v>
+        <v>126912614</v>
       </c>
       <c r="B100" t="n">
-        <v>78773</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674218</v>
+        <v>674319</v>
       </c>
       <c r="R100" t="n">
-        <v>7092914</v>
+        <v>7093047</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10658,7 +10658,7 @@
         <v>126915610</v>
       </c>
       <c r="B101" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>126915609</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10857,32 +10857,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126915582</v>
+        <v>126912575</v>
       </c>
       <c r="B103" t="n">
-        <v>98464</v>
+        <v>79636</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674302</v>
+        <v>674215</v>
       </c>
       <c r="R103" t="n">
-        <v>7093071</v>
+        <v>7092959</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10942,70 +10942,57 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912642</v>
+        <v>126912679</v>
       </c>
       <c r="B104" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674117</v>
+        <v>674324</v>
       </c>
       <c r="R104" t="n">
-        <v>7092933</v>
+        <v>7093051</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11064,54 +11051,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912637</v>
+        <v>126912572</v>
       </c>
       <c r="B105" t="n">
-        <v>98443</v>
+        <v>79636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674166</v>
+        <v>674310</v>
       </c>
       <c r="R105" t="n">
-        <v>7092881</v>
+        <v>7092998</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11170,10 +11148,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912679</v>
+        <v>126912671</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11205,10 +11183,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674324</v>
+        <v>674238</v>
       </c>
       <c r="R106" t="n">
-        <v>7093051</v>
+        <v>7093012</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11267,10 +11245,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126912671</v>
+        <v>126913197</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11302,10 +11280,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674238</v>
+        <v>673791</v>
       </c>
       <c r="R107" t="n">
-        <v>7093012</v>
+        <v>7092931</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11352,22 +11330,26 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126913197</v>
+        <v>126912686</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11399,10 +11381,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>673791</v>
+        <v>674222</v>
       </c>
       <c r="R108" t="n">
-        <v>7092931</v>
+        <v>7092926</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11449,61 +11431,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126912686</v>
+        <v>126912637</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674222</v>
+        <v>674166</v>
       </c>
       <c r="R109" t="n">
-        <v>7092926</v>
+        <v>7092881</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11562,45 +11549,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912575</v>
+        <v>126912642</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674215</v>
+        <v>674117</v>
       </c>
       <c r="R110" t="n">
-        <v>7092959</v>
+        <v>7092933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11659,32 +11655,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126912572</v>
+        <v>126915582</v>
       </c>
       <c r="B111" t="n">
-        <v>79632</v>
+        <v>98468</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11694,10 +11690,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674310</v>
+        <v>674302</v>
       </c>
       <c r="R111" t="n">
-        <v>7092998</v>
+        <v>7093071</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11744,22 +11740,26 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918998</v>
+        <v>126918776</v>
       </c>
       <c r="B112" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>673861</v>
+        <v>674139</v>
       </c>
       <c r="R112" t="n">
-        <v>7093031</v>
+        <v>7092939</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,12 +11841,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -11857,10 +11857,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918776</v>
+        <v>126918801</v>
       </c>
       <c r="B113" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11868,21 +11868,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674139</v>
+        <v>674148</v>
       </c>
       <c r="R113" t="n">
-        <v>7092939</v>
+        <v>7093061</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11958,32 +11958,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126915628</v>
+        <v>126912577</v>
       </c>
       <c r="B114" t="n">
-        <v>98360</v>
+        <v>79636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11993,10 +11993,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674258</v>
+        <v>674204</v>
       </c>
       <c r="R114" t="n">
-        <v>7093046</v>
+        <v>7092934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12043,26 +12043,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126912689</v>
+        <v>126918810</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12094,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674237</v>
+        <v>674189</v>
       </c>
       <c r="R115" t="n">
-        <v>7092921</v>
+        <v>7092854</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12144,22 +12140,26 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918801</v>
+        <v>126912689</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12191,10 +12191,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674148</v>
+        <v>674237</v>
       </c>
       <c r="R116" t="n">
-        <v>7093061</v>
+        <v>7092921</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12241,48 +12241,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918810</v>
+        <v>126915628</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12292,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674189</v>
+        <v>674258</v>
       </c>
       <c r="R117" t="n">
-        <v>7092854</v>
+        <v>7093046</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12342,12 +12338,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12358,10 +12354,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126912577</v>
+        <v>126918998</v>
       </c>
       <c r="B118" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12369,21 +12365,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12393,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674204</v>
+        <v>673861</v>
       </c>
       <c r="R118" t="n">
-        <v>7092934</v>
+        <v>7093031</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12443,22 +12439,26 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>126918808</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>126912708</v>
       </c>
       <c r="B120" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>126912573</v>
       </c>
       <c r="B121" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12755,32 +12755,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126919026</v>
+        <v>126918778</v>
       </c>
       <c r="B122" t="n">
-        <v>78773</v>
+        <v>98351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>673796</v>
+        <v>674279</v>
       </c>
       <c r="R122" t="n">
-        <v>7092899</v>
+        <v>7092923</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12840,12 +12840,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12856,32 +12856,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126912623</v>
+        <v>126913194</v>
       </c>
       <c r="B123" t="n">
-        <v>78773</v>
+        <v>98447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12891,10 +12891,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>674215</v>
+        <v>673917</v>
       </c>
       <c r="R123" t="n">
-        <v>7092959</v>
+        <v>7092948</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,44 +12941,48 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126913194</v>
+        <v>126919026</v>
       </c>
       <c r="B124" t="n">
-        <v>98443</v>
+        <v>78777</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12988,10 +12992,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>673917</v>
+        <v>673796</v>
       </c>
       <c r="R124" t="n">
-        <v>7092948</v>
+        <v>7092899</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13038,12 +13042,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13054,32 +13058,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126918778</v>
+        <v>126912623</v>
       </c>
       <c r="B125" t="n">
-        <v>98347</v>
+        <v>78777</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220093</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13089,10 +13093,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>674279</v>
+        <v>674215</v>
       </c>
       <c r="R125" t="n">
-        <v>7092923</v>
+        <v>7092959</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13139,48 +13143,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126912615</v>
+        <v>126912665</v>
       </c>
       <c r="B126" t="n">
-        <v>80145</v>
+        <v>79018</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>674322</v>
+        <v>674174</v>
       </c>
       <c r="R126" t="n">
-        <v>7093041</v>
+        <v>7093073</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13245,39 +13245,39 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126919003</v>
+        <v>126912615</v>
       </c>
       <c r="B127" t="n">
-        <v>78772</v>
+        <v>80149</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>673948</v>
+        <v>674322</v>
       </c>
       <c r="R127" t="n">
-        <v>7093011</v>
+        <v>7093041</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13337,26 +13337,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126912665</v>
+        <v>126919003</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13364,21 +13360,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13388,10 +13384,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>674174</v>
+        <v>673948</v>
       </c>
       <c r="R128" t="n">
-        <v>7093073</v>
+        <v>7093011</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13438,22 +13434,26 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>126912690</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13547,10 +13547,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126915614</v>
+        <v>126919036</v>
       </c>
       <c r="B130" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>674163</v>
+        <v>673559</v>
       </c>
       <c r="R130" t="n">
-        <v>7092870</v>
+        <v>7093141</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13632,12 +13632,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13648,10 +13648,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126919036</v>
+        <v>126915614</v>
       </c>
       <c r="B131" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>673559</v>
+        <v>674163</v>
       </c>
       <c r="R131" t="n">
-        <v>7093141</v>
+        <v>7092870</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13733,12 +13733,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13749,10 +13749,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126912682</v>
+        <v>126913960</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13760,34 +13760,38 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>674304</v>
+        <v>673577</v>
       </c>
       <c r="R132" t="n">
-        <v>7093013</v>
+        <v>7093132</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13822,6 +13826,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -13834,44 +13843,48 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912593</v>
+        <v>126912682</v>
       </c>
       <c r="B133" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13881,10 +13894,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674210</v>
+        <v>674304</v>
       </c>
       <c r="R133" t="n">
-        <v>7092877</v>
+        <v>7093013</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13943,49 +13956,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126913960</v>
+        <v>126912593</v>
       </c>
       <c r="B134" t="n">
-        <v>57657</v>
+        <v>80150</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>673577</v>
+        <v>674210</v>
       </c>
       <c r="R134" t="n">
-        <v>7093132</v>
+        <v>7092877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14020,11 +14029,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14037,70 +14041,57 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126912638</v>
+        <v>126912675</v>
       </c>
       <c r="B135" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>674111</v>
+        <v>674268</v>
       </c>
       <c r="R135" t="n">
-        <v>7092937</v>
+        <v>7093042</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14159,45 +14150,54 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126912675</v>
+        <v>126912638</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>674268</v>
+        <v>674111</v>
       </c>
       <c r="R136" t="n">
-        <v>7093042</v>
+        <v>7092937</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14259,7 +14259,7 @@
         <v>126918997</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14357,10 +14357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126918805</v>
+        <v>126919027</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>674241</v>
+        <v>673554</v>
       </c>
       <c r="R138" t="n">
-        <v>7092850</v>
+        <v>7093135</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,12 +14442,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14458,10 +14458,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126918804</v>
+        <v>126912678</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14493,10 +14493,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>674299</v>
+        <v>674334</v>
       </c>
       <c r="R139" t="n">
-        <v>7092979</v>
+        <v>7093055</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14543,26 +14543,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126912678</v>
+        <v>126918805</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14594,10 +14590,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>674334</v>
+        <v>674241</v>
       </c>
       <c r="R140" t="n">
-        <v>7093055</v>
+        <v>7092850</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14644,22 +14640,26 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126919027</v>
+        <v>126918804</v>
       </c>
       <c r="B141" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14667,21 +14667,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14691,10 +14691,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>673554</v>
+        <v>674299</v>
       </c>
       <c r="R141" t="n">
-        <v>7093135</v>
+        <v>7092979</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14741,12 +14741,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14760,7 +14760,7 @@
         <v>126913193</v>
       </c>
       <c r="B142" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>126915629</v>
       </c>
       <c r="B143" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>126919041</v>
       </c>
       <c r="B144" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15060,10 +15060,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126919007</v>
+        <v>126912670</v>
       </c>
       <c r="B145" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>673940</v>
+        <v>674225</v>
       </c>
       <c r="R145" t="n">
-        <v>7093045</v>
+        <v>7093014</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15133,44 +15133,34 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126912670</v>
+        <v>126912688</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15202,10 +15192,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>674225</v>
+        <v>674231</v>
       </c>
       <c r="R146" t="n">
-        <v>7093014</v>
+        <v>7092932</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15267,7 +15257,7 @@
         <v>126912651</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15359,39 +15349,39 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126913182</v>
+        <v>126915991</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15401,13 +15391,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>674316</v>
+        <v>673971</v>
       </c>
       <c r="R148" t="n">
-        <v>7093018</v>
+        <v>7092936</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15451,12 +15441,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15467,10 +15457,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126912676</v>
+        <v>126919007</v>
       </c>
       <c r="B149" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15502,10 +15492,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>674259</v>
+        <v>673940</v>
       </c>
       <c r="R149" t="n">
-        <v>7093064</v>
+        <v>7093045</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15540,56 +15530,66 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126915991</v>
+        <v>126919075</v>
       </c>
       <c r="B150" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15599,13 +15599,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>673971</v>
+        <v>673825</v>
       </c>
       <c r="R150" t="n">
-        <v>7092936</v>
+        <v>7092923</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15649,12 +15649,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15665,10 +15665,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126912688</v>
+        <v>126919069</v>
       </c>
       <c r="B151" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15700,10 +15700,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>674231</v>
+        <v>673685</v>
       </c>
       <c r="R151" t="n">
-        <v>7092932</v>
+        <v>7092946</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15750,22 +15750,26 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126919075</v>
+        <v>126913182</v>
       </c>
       <c r="B152" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15797,10 +15801,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>673825</v>
+        <v>674316</v>
       </c>
       <c r="R152" t="n">
-        <v>7092923</v>
+        <v>7093018</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15847,12 +15851,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15863,10 +15867,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126919069</v>
+        <v>126912676</v>
       </c>
       <c r="B153" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15898,10 +15902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>673685</v>
+        <v>674259</v>
       </c>
       <c r="R153" t="n">
-        <v>7092946</v>
+        <v>7093064</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15948,26 +15952,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>126919017</v>
       </c>
       <c r="B154" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>126912692</v>
       </c>
       <c r="B155" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>126919063</v>
       </c>
       <c r="B156" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>126919070</v>
       </c>
       <c r="B157" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>126915634</v>
       </c>
       <c r="B158" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16470,32 +16470,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126915613</v>
+        <v>126915603</v>
       </c>
       <c r="B159" t="n">
-        <v>98443</v>
+        <v>98351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16505,10 +16505,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674171</v>
+        <v>674278</v>
       </c>
       <c r="R159" t="n">
-        <v>7092865</v>
+        <v>7092923</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16571,32 +16571,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126918792</v>
+        <v>126915602</v>
       </c>
       <c r="B160" t="n">
-        <v>98443</v>
+        <v>98351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16606,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>674129</v>
+        <v>674319</v>
       </c>
       <c r="R160" t="n">
-        <v>7093003</v>
+        <v>7092980</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16656,12 +16656,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16672,32 +16672,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126915603</v>
+        <v>126915613</v>
       </c>
       <c r="B161" t="n">
-        <v>98347</v>
+        <v>98447</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>674278</v>
+        <v>674171</v>
       </c>
       <c r="R161" t="n">
-        <v>7092923</v>
+        <v>7092865</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16773,32 +16773,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126915602</v>
+        <v>126918792</v>
       </c>
       <c r="B162" t="n">
-        <v>98347</v>
+        <v>98447</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>674319</v>
+        <v>674129</v>
       </c>
       <c r="R162" t="n">
-        <v>7092980</v>
+        <v>7093003</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,12 +16858,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16874,32 +16874,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126915599</v>
+        <v>126912704</v>
       </c>
       <c r="B163" t="n">
-        <v>98347</v>
+        <v>78685</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220093</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674272</v>
+        <v>674200</v>
       </c>
       <c r="R163" t="n">
-        <v>7093054</v>
+        <v>7092950</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16959,48 +16959,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912704</v>
+        <v>126912594</v>
       </c>
       <c r="B164" t="n">
-        <v>78681</v>
+        <v>80150</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17010,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674200</v>
+        <v>674121</v>
       </c>
       <c r="R164" t="n">
-        <v>7092950</v>
+        <v>7092931</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17075,7 +17071,7 @@
         <v>126918809</v>
       </c>
       <c r="B165" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17173,32 +17169,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126912684</v>
+        <v>126918993</v>
       </c>
       <c r="B166" t="n">
-        <v>79014</v>
+        <v>80025</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17208,10 +17204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>674292</v>
+        <v>673937</v>
       </c>
       <c r="R166" t="n">
-        <v>7092976</v>
+        <v>7093103</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17252,50 +17248,55 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126912594</v>
+        <v>126912684</v>
       </c>
       <c r="B167" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17305,10 +17306,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>674121</v>
+        <v>674292</v>
       </c>
       <c r="R167" t="n">
-        <v>7092931</v>
+        <v>7092976</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17367,10 +17368,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126918993</v>
+        <v>126915599</v>
       </c>
       <c r="B168" t="n">
-        <v>80021</v>
+        <v>98351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17378,21 +17379,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6456</v>
+        <v>220093</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17402,10 +17403,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>673937</v>
+        <v>674272</v>
       </c>
       <c r="R168" t="n">
-        <v>7093103</v>
+        <v>7093054</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17446,7 +17447,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17472,7 +17472,7 @@
         <v>126916006</v>
       </c>
       <c r="B169" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>126916008</v>
       </c>
       <c r="B170" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>126915992</v>
       </c>
       <c r="B171" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>126915987</v>
       </c>
       <c r="B172" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>126916003</v>
       </c>
       <c r="B173" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>126916004</v>
       </c>
       <c r="B174" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>126915981</v>
       </c>
       <c r="B175" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>126916009</v>
       </c>
       <c r="B176" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>126915996</v>
       </c>
       <c r="B177" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>126916002</v>
       </c>
       <c r="B178" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>126915993</v>
       </c>
       <c r="B179" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>126915989</v>
       </c>
       <c r="B180" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>126916000</v>
       </c>
       <c r="B181" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>126916007</v>
       </c>
       <c r="B182" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>126915997</v>
       </c>
       <c r="B183" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>126913458</v>
       </c>
       <c r="B184" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>126913469</v>
       </c>
       <c r="B185" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>126913474</v>
       </c>
       <c r="B186" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>126913445</v>
       </c>
       <c r="B187" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>126913472</v>
       </c>
       <c r="B188" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>126913482</v>
       </c>
       <c r="B189" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>126913479</v>
       </c>
       <c r="B190" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>126913478</v>
       </c>
       <c r="B191" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>126913470</v>
       </c>
       <c r="B192" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>126913476</v>
       </c>
       <c r="B193" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>126913471</v>
       </c>
       <c r="B194" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>126913473</v>
       </c>
       <c r="B195" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20233,10 +20233,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126913475</v>
+        <v>126913448</v>
       </c>
       <c r="B196" t="n">
-        <v>78773</v>
+        <v>80121</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20244,21 +20244,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20268,10 +20268,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>673753</v>
+        <v>673558</v>
       </c>
       <c r="R196" t="n">
-        <v>7093083</v>
+        <v>7093130</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20334,10 +20334,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126913448</v>
+        <v>126913475</v>
       </c>
       <c r="B197" t="n">
-        <v>80117</v>
+        <v>78777</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20345,21 +20345,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20369,10 +20369,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>673558</v>
+        <v>673753</v>
       </c>
       <c r="R197" t="n">
-        <v>7093130</v>
+        <v>7093083</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20438,7 +20438,7 @@
         <v>126913213</v>
       </c>
       <c r="B198" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1560,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126915632</v>
+        <v>126916005</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>674279</v>
+        <v>673879</v>
       </c>
       <c r="R10" t="n">
-        <v>7092915</v>
+        <v>7092985</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918793</v>
+        <v>126918995</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>80025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674251</v>
+        <v>673947</v>
       </c>
       <c r="R11" t="n">
-        <v>7092837</v>
+        <v>7093045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126913215</v>
+        <v>126919065</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>674258</v>
+        <v>673619</v>
       </c>
       <c r="R12" t="n">
-        <v>7092817</v>
+        <v>7092978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919040</v>
+        <v>126915585</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673649</v>
+        <v>674324</v>
       </c>
       <c r="R13" t="n">
-        <v>7092943</v>
+        <v>7093076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918995</v>
+        <v>126915632</v>
       </c>
       <c r="B14" t="n">
-        <v>80025</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673947</v>
+        <v>674279</v>
       </c>
       <c r="R14" t="n">
-        <v>7093045</v>
+        <v>7092915</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,32 +2065,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919065</v>
+        <v>126918793</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673619</v>
+        <v>674251</v>
       </c>
       <c r="R15" t="n">
-        <v>7092978</v>
+        <v>7092837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,32 +2166,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126916005</v>
+        <v>126919040</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673879</v>
+        <v>673649</v>
       </c>
       <c r="R16" t="n">
-        <v>7092985</v>
+        <v>7092943</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126915585</v>
+        <v>126913215</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674324</v>
+        <v>674258</v>
       </c>
       <c r="R17" t="n">
-        <v>7093076</v>
+        <v>7092817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912574</v>
+        <v>126913188</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674224</v>
+        <v>673761</v>
       </c>
       <c r="R18" t="n">
-        <v>7092965</v>
+        <v>7092946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,22 +2453,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126915627</v>
+        <v>126912574</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674167</v>
+        <v>674224</v>
       </c>
       <c r="R19" t="n">
-        <v>7093069</v>
+        <v>7092965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,48 +2554,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126912616</v>
+        <v>126915627</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674220</v>
+        <v>674167</v>
       </c>
       <c r="R20" t="n">
-        <v>7092919</v>
+        <v>7093069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,44 +2651,48 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126915606</v>
+        <v>126912616</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2702,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674275</v>
+        <v>674220</v>
       </c>
       <c r="R21" t="n">
-        <v>7092845</v>
+        <v>7092919</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,23 +2752,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126913188</v>
+        <v>126915606</v>
       </c>
       <c r="B22" t="n">
         <v>98447</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673761</v>
+        <v>674275</v>
       </c>
       <c r="R22" t="n">
-        <v>7092946</v>
+        <v>7092845</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126912633</v>
+        <v>126919071</v>
       </c>
       <c r="B26" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>674218</v>
+        <v>673738</v>
       </c>
       <c r="R26" t="n">
-        <v>7092957</v>
+        <v>7092907</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,44 +3249,48 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126915593</v>
+        <v>126919077</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3296,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>674310</v>
+        <v>673852</v>
       </c>
       <c r="R27" t="n">
-        <v>7093054</v>
+        <v>7092910</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,12 +3350,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3362,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126919077</v>
+        <v>126912633</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673852</v>
+        <v>674218</v>
       </c>
       <c r="R28" t="n">
-        <v>7092910</v>
+        <v>7092957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,48 +3451,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126919071</v>
+        <v>126915593</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673738</v>
+        <v>674310</v>
       </c>
       <c r="R29" t="n">
-        <v>7092907</v>
+        <v>7093054</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,12 +3548,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126913209</v>
+        <v>126918783</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674212</v>
+        <v>674284</v>
       </c>
       <c r="R30" t="n">
-        <v>7092826</v>
+        <v>7093057</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3766,32 +3766,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126918783</v>
+        <v>126913209</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674284</v>
+        <v>674212</v>
       </c>
       <c r="R32" t="n">
-        <v>7093057</v>
+        <v>7092826</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4069,7 +4069,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912691</v>
+        <v>126912681</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674239</v>
+        <v>674304</v>
       </c>
       <c r="R35" t="n">
-        <v>7092910</v>
+        <v>7093019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4166,10 +4166,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126912635</v>
+        <v>126919009</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>674239</v>
+        <v>673944</v>
       </c>
       <c r="R36" t="n">
-        <v>7092908</v>
+        <v>7093050</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,6 +4239,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4251,19 +4256,23 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912681</v>
+        <v>126919008</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4298,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>674304</v>
+        <v>673843</v>
       </c>
       <c r="R37" t="n">
-        <v>7093019</v>
+        <v>7093104</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,19 +4357,23 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919009</v>
+        <v>126912691</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4395,10 +4408,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673944</v>
+        <v>674239</v>
       </c>
       <c r="R38" t="n">
-        <v>7093050</v>
+        <v>7092910</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,11 +4446,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4450,26 +4458,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919078</v>
+        <v>126912635</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4501,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673893</v>
+        <v>674239</v>
       </c>
       <c r="R39" t="n">
-        <v>7092920</v>
+        <v>7092908</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,23 +4555,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919008</v>
+        <v>126919078</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673843</v>
+        <v>673893</v>
       </c>
       <c r="R40" t="n">
-        <v>7093104</v>
+        <v>7092920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,12 +4652,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912685</v>
+        <v>126915572</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674236</v>
+        <v>674324</v>
       </c>
       <c r="R42" t="n">
-        <v>7092969</v>
+        <v>7093076</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,19 +4854,23 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912666</v>
+        <v>126912685</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -4901,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674176</v>
+        <v>674236</v>
       </c>
       <c r="R43" t="n">
-        <v>7093061</v>
+        <v>7092969</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4956,14 +4960,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126913207</v>
+        <v>126912666</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -4998,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674182</v>
+        <v>674176</v>
       </c>
       <c r="R44" t="n">
-        <v>7092837</v>
+        <v>7093061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,23 +5052,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126919067</v>
+        <v>126913207</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673610</v>
+        <v>674182</v>
       </c>
       <c r="R45" t="n">
-        <v>7092955</v>
+        <v>7092837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,12 +5149,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5165,32 +5165,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126915572</v>
+        <v>126919067</v>
       </c>
       <c r="B46" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674324</v>
+        <v>673610</v>
       </c>
       <c r="R46" t="n">
-        <v>7093076</v>
+        <v>7092955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912576</v>
+        <v>126913208</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>91280</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674200</v>
+        <v>674181</v>
       </c>
       <c r="R51" t="n">
-        <v>7092950</v>
+        <v>7092836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,60 +5751,61 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126913179</v>
+        <v>126919000</v>
       </c>
       <c r="B52" t="n">
-        <v>80025</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673719</v>
+        <v>673939</v>
       </c>
       <c r="R52" t="n">
-        <v>7093035</v>
+        <v>7093012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5845,19 +5846,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5969,32 +5969,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126915630</v>
+        <v>126912576</v>
       </c>
       <c r="B54" t="n">
-        <v>98364</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674328</v>
+        <v>674200</v>
       </c>
       <c r="R54" t="n">
-        <v>7092980</v>
+        <v>7092950</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,26 +6054,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912700</v>
+        <v>126913179</v>
       </c>
       <c r="B55" t="n">
-        <v>98364</v>
+        <v>80025</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6081,34 +6077,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674267</v>
+        <v>673719</v>
       </c>
       <c r="R55" t="n">
-        <v>7093044</v>
+        <v>7093035</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6149,79 +6148,68 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126913214</v>
+        <v>126915630</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674219</v>
+        <v>674328</v>
       </c>
       <c r="R56" t="n">
-        <v>7092815</v>
+        <v>7092980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6262,19 +6250,18 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6285,32 +6272,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126915608</v>
+        <v>126912700</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6320,10 +6307,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674257</v>
+        <v>674267</v>
       </c>
       <c r="R57" t="n">
-        <v>7092823</v>
+        <v>7093044</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6370,48 +6357,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919000</v>
+        <v>126915608</v>
       </c>
       <c r="B58" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6421,10 +6404,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673939</v>
+        <v>674257</v>
       </c>
       <c r="R58" t="n">
-        <v>7093012</v>
+        <v>7092823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6476,7 +6459,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6487,45 +6470,61 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126913208</v>
+        <v>126913214</v>
       </c>
       <c r="B59" t="n">
-        <v>91280</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674181</v>
+        <v>674219</v>
       </c>
       <c r="R59" t="n">
-        <v>7092836</v>
+        <v>7092815</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6566,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912592</v>
+        <v>126918806</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674188</v>
+        <v>674216</v>
       </c>
       <c r="R60" t="n">
-        <v>7092955</v>
+        <v>7092860</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,19 +6673,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126918806</v>
+        <v>126912687</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6720,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674216</v>
+        <v>674226</v>
       </c>
       <c r="R61" t="n">
-        <v>7092860</v>
+        <v>7092929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6770,26 +6774,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126918996</v>
+        <v>126912592</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673948</v>
+        <v>674188</v>
       </c>
       <c r="R62" t="n">
-        <v>7093016</v>
+        <v>7092955</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,48 +6871,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126919031</v>
+        <v>126918996</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6918,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673796</v>
+        <v>673948</v>
       </c>
       <c r="R63" t="n">
-        <v>7092899</v>
+        <v>7093016</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,12 +6968,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6988,32 +6984,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126912617</v>
+        <v>126919031</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>78776</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>674214</v>
+        <v>673796</v>
       </c>
       <c r="R64" t="n">
-        <v>7092881</v>
+        <v>7092899</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7073,44 +7069,48 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126912687</v>
+        <v>126912617</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674226</v>
+        <v>674214</v>
       </c>
       <c r="R65" t="n">
-        <v>7092929</v>
+        <v>7092881</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7182,32 +7182,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126912622</v>
+        <v>126918787</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674225</v>
+        <v>674167</v>
       </c>
       <c r="R66" t="n">
-        <v>7092965</v>
+        <v>7092848</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7267,44 +7267,48 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126912620</v>
+        <v>126915584</v>
       </c>
       <c r="B67" t="n">
-        <v>78777</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7314,10 +7318,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674229</v>
+        <v>674316</v>
       </c>
       <c r="R67" t="n">
-        <v>7092964</v>
+        <v>7092989</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7364,19 +7368,23 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126918999</v>
+        <v>126912622</v>
       </c>
       <c r="B68" t="n">
         <v>78777</v>
@@ -7411,10 +7419,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673919</v>
+        <v>674225</v>
       </c>
       <c r="R68" t="n">
-        <v>7093017</v>
+        <v>7092965</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7461,48 +7469,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126913211</v>
+        <v>126912620</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7512,10 +7516,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>674214</v>
+        <v>674229</v>
       </c>
       <c r="R69" t="n">
-        <v>7092818</v>
+        <v>7092964</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7562,48 +7566,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126919039</v>
+        <v>126918999</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>673525</v>
+        <v>673919</v>
       </c>
       <c r="R70" t="n">
-        <v>7093040</v>
+        <v>7093017</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7663,12 +7663,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7679,32 +7679,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126918787</v>
+        <v>126919039</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>674167</v>
+        <v>673525</v>
       </c>
       <c r="R71" t="n">
-        <v>7092848</v>
+        <v>7093040</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,12 +7764,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7780,32 +7780,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126915584</v>
+        <v>126913211</v>
       </c>
       <c r="B72" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>674316</v>
+        <v>674214</v>
       </c>
       <c r="R72" t="n">
-        <v>7092989</v>
+        <v>7092818</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912590</v>
+        <v>126912680</v>
       </c>
       <c r="B73" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,39 +7892,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>673958</v>
+        <v>674302</v>
       </c>
       <c r="R73" t="n">
-        <v>7093109</v>
+        <v>7093031</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7983,10 +7978,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912625</v>
+        <v>126912579</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7994,21 +7989,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8080,10 +8075,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912579</v>
+        <v>126919068</v>
       </c>
       <c r="B75" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8091,21 +8086,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8115,10 +8110,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674239</v>
+        <v>673630</v>
       </c>
       <c r="R75" t="n">
-        <v>7092908</v>
+        <v>7092929</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8165,22 +8160,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912680</v>
+        <v>126912590</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,34 +8187,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>674302</v>
+        <v>673958</v>
       </c>
       <c r="R76" t="n">
-        <v>7093031</v>
+        <v>7093109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8274,10 +8278,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126919068</v>
+        <v>126912625</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8285,21 +8289,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8309,10 +8313,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>673630</v>
+        <v>674239</v>
       </c>
       <c r="R77" t="n">
-        <v>7092929</v>
+        <v>7092908</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8359,19 +8363,15 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8573,32 +8573,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918802</v>
+        <v>126918795</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674315</v>
+        <v>674236</v>
       </c>
       <c r="R80" t="n">
-        <v>7093023</v>
+        <v>7092852</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8674,45 +8674,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918795</v>
+        <v>126912599</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674236</v>
+        <v>674251</v>
       </c>
       <c r="R81" t="n">
-        <v>7092852</v>
+        <v>7093028</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8759,66 +8764,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126912599</v>
+        <v>126918802</v>
       </c>
       <c r="B82" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674251</v>
+        <v>674315</v>
       </c>
       <c r="R82" t="n">
-        <v>7093028</v>
+        <v>7093023</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8865,44 +8861,48 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126912674</v>
+        <v>126919037</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>674251</v>
+        <v>673555</v>
       </c>
       <c r="R83" t="n">
-        <v>7093028</v>
+        <v>7093132</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,19 +8962,23 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913212</v>
+        <v>126915607</v>
       </c>
       <c r="B84" t="n">
         <v>98447</v>
@@ -9009,10 +9013,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674207</v>
+        <v>674262</v>
       </c>
       <c r="R84" t="n">
-        <v>7092818</v>
+        <v>7092824</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9059,12 +9063,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9075,32 +9079,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126919037</v>
+        <v>126912674</v>
       </c>
       <c r="B85" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9110,10 +9114,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>673555</v>
+        <v>674251</v>
       </c>
       <c r="R85" t="n">
-        <v>7093132</v>
+        <v>7093028</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9160,48 +9164,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126915607</v>
+        <v>126912668</v>
       </c>
       <c r="B86" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674262</v>
+        <v>674214</v>
       </c>
       <c r="R86" t="n">
-        <v>7092824</v>
+        <v>7093041</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9261,48 +9261,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912668</v>
+        <v>126912618</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9312,10 +9308,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674214</v>
+        <v>674104</v>
       </c>
       <c r="R87" t="n">
-        <v>7093041</v>
+        <v>7092938</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9367,39 +9363,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126912618</v>
+        <v>126912672</v>
       </c>
       <c r="B88" t="n">
-        <v>80149</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9409,10 +9405,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674104</v>
+        <v>674248</v>
       </c>
       <c r="R88" t="n">
-        <v>7092938</v>
+        <v>7093018</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9471,32 +9467,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126912672</v>
+        <v>126912699</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9506,10 +9502,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674248</v>
+        <v>674260</v>
       </c>
       <c r="R89" t="n">
-        <v>7093018</v>
+        <v>7093031</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9568,32 +9564,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126912699</v>
+        <v>126913212</v>
       </c>
       <c r="B90" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9603,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674260</v>
+        <v>674207</v>
       </c>
       <c r="R90" t="n">
-        <v>7093031</v>
+        <v>7092818</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9653,22 +9649,26 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918807</v>
+        <v>126912634</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674208</v>
+        <v>674203</v>
       </c>
       <c r="R91" t="n">
-        <v>7092856</v>
+        <v>7092932</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,26 +9750,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126912578</v>
+        <v>126918789</v>
       </c>
       <c r="B92" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9777,21 +9773,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9801,10 +9797,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674218</v>
+        <v>674310</v>
       </c>
       <c r="R92" t="n">
-        <v>7092914</v>
+        <v>7092997</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9851,22 +9847,26 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912634</v>
+        <v>126912703</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>78685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674203</v>
+        <v>674269</v>
       </c>
       <c r="R93" t="n">
-        <v>7092932</v>
+        <v>7092979</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918789</v>
+        <v>126918807</v>
       </c>
       <c r="B94" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674310</v>
+        <v>674208</v>
       </c>
       <c r="R94" t="n">
-        <v>7092997</v>
+        <v>7092856</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10061,7 +10061,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126918984</v>
+        <v>126912578</v>
       </c>
       <c r="B95" t="n">
         <v>79636</v>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>673919</v>
+        <v>674218</v>
       </c>
       <c r="R95" t="n">
-        <v>7093017</v>
+        <v>7092914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10146,19 +10146,15 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10364,32 +10360,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126912703</v>
+        <v>126912614</v>
       </c>
       <c r="B98" t="n">
-        <v>78685</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10399,10 +10395,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674269</v>
+        <v>674319</v>
       </c>
       <c r="R98" t="n">
-        <v>7092979</v>
+        <v>7093047</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10461,10 +10457,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126912624</v>
+        <v>126918984</v>
       </c>
       <c r="B99" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10472,21 +10468,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10496,10 +10492,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674218</v>
+        <v>673919</v>
       </c>
       <c r="R99" t="n">
-        <v>7092914</v>
+        <v>7093017</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10546,44 +10542,48 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126912614</v>
+        <v>126912624</v>
       </c>
       <c r="B100" t="n">
-        <v>80149</v>
+        <v>78777</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674319</v>
+        <v>674218</v>
       </c>
       <c r="R100" t="n">
-        <v>7093047</v>
+        <v>7092914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11051,10 +11051,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912572</v>
+        <v>126912671</v>
       </c>
       <c r="B105" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11062,21 +11062,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11086,10 +11086,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674310</v>
+        <v>674238</v>
       </c>
       <c r="R105" t="n">
-        <v>7092998</v>
+        <v>7093012</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126912671</v>
+        <v>126913197</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>674238</v>
+        <v>673791</v>
       </c>
       <c r="R106" t="n">
-        <v>7093012</v>
+        <v>7092931</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11233,22 +11233,26 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126913197</v>
+        <v>126912572</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11256,21 +11260,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11280,10 +11284,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>673791</v>
+        <v>674310</v>
       </c>
       <c r="R107" t="n">
-        <v>7092931</v>
+        <v>7092998</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11330,19 +11334,15 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11756,10 +11756,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126918776</v>
+        <v>126912689</v>
       </c>
       <c r="B112" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11767,21 +11767,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674139</v>
+        <v>674237</v>
       </c>
       <c r="R112" t="n">
-        <v>7092939</v>
+        <v>7092921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,19 +11841,15 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11958,10 +11954,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126912577</v>
+        <v>126918810</v>
       </c>
       <c r="B114" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11969,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11993,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674204</v>
+        <v>674189</v>
       </c>
       <c r="R114" t="n">
-        <v>7092934</v>
+        <v>7092854</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12043,22 +12039,26 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126918810</v>
+        <v>126912577</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674189</v>
+        <v>674204</v>
       </c>
       <c r="R115" t="n">
-        <v>7092854</v>
+        <v>7092934</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12140,26 +12140,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126912689</v>
+        <v>126918998</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12167,21 +12163,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12191,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674237</v>
+        <v>673861</v>
       </c>
       <c r="R116" t="n">
-        <v>7092921</v>
+        <v>7093031</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12241,44 +12237,48 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126915628</v>
+        <v>126918776</v>
       </c>
       <c r="B117" t="n">
-        <v>98364</v>
+        <v>78777</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674258</v>
+        <v>674139</v>
       </c>
       <c r="R117" t="n">
-        <v>7093046</v>
+        <v>7092939</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12338,12 +12338,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12354,32 +12354,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126918998</v>
+        <v>126915628</v>
       </c>
       <c r="B118" t="n">
-        <v>78777</v>
+        <v>98364</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>673861</v>
+        <v>674258</v>
       </c>
       <c r="R118" t="n">
-        <v>7093031</v>
+        <v>7093046</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12556,32 +12556,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126912708</v>
+        <v>126918778</v>
       </c>
       <c r="B120" t="n">
-        <v>77996</v>
+        <v>98351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6487</v>
+        <v>220093</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>674243</v>
+        <v>674279</v>
       </c>
       <c r="R120" t="n">
-        <v>7092914</v>
+        <v>7092923</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12629,11 +12629,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>På torraka med bohål</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12646,44 +12641,48 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126912573</v>
+        <v>126913194</v>
       </c>
       <c r="B121" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12693,10 +12692,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>674270</v>
+        <v>673917</v>
       </c>
       <c r="R121" t="n">
-        <v>7092973</v>
+        <v>7092948</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12743,44 +12742,48 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126918778</v>
+        <v>126912708</v>
       </c>
       <c r="B122" t="n">
-        <v>98351</v>
+        <v>77996</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220093</v>
+        <v>6487</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12790,10 +12793,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>674279</v>
+        <v>674243</v>
       </c>
       <c r="R122" t="n">
-        <v>7092923</v>
+        <v>7092914</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12828,6 +12831,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>På torraka med bohål</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12840,48 +12848,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126913194</v>
+        <v>126912573</v>
       </c>
       <c r="B123" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12891,10 +12895,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>673917</v>
+        <v>674270</v>
       </c>
       <c r="R123" t="n">
-        <v>7092948</v>
+        <v>7092973</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12941,19 +12945,15 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126913960</v>
+        <v>126912682</v>
       </c>
       <c r="B132" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13760,38 +13760,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>673577</v>
+        <v>674304</v>
       </c>
       <c r="R132" t="n">
-        <v>7093132</v>
+        <v>7093013</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13826,11 +13822,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -13843,23 +13834,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912682</v>
+        <v>126912675</v>
       </c>
       <c r="B133" t="n">
         <v>79018</v>
@@ -13894,10 +13881,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674304</v>
+        <v>674268</v>
       </c>
       <c r="R133" t="n">
-        <v>7093013</v>
+        <v>7093042</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14053,10 +14040,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126912675</v>
+        <v>126913960</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14064,34 +14051,38 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>674268</v>
+        <v>673577</v>
       </c>
       <c r="R135" t="n">
-        <v>7093042</v>
+        <v>7093132</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14126,6 +14117,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14138,15 +14134,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14357,10 +14357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126919027</v>
+        <v>126913193</v>
       </c>
       <c r="B138" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>673554</v>
+        <v>673849</v>
       </c>
       <c r="R138" t="n">
-        <v>7093135</v>
+        <v>7092944</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,12 +14442,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14757,10 +14757,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126913193</v>
+        <v>126919027</v>
       </c>
       <c r="B142" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>673849</v>
+        <v>673554</v>
       </c>
       <c r="R142" t="n">
-        <v>7092944</v>
+        <v>7093135</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15060,7 +15060,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126912670</v>
+        <v>126919007</v>
       </c>
       <c r="B145" t="n">
         <v>79018</v>
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>674225</v>
+        <v>673940</v>
       </c>
       <c r="R145" t="n">
-        <v>7093014</v>
+        <v>7093045</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15133,27 +15133,37 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15254,7 +15264,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126912651</v>
+        <v>126919075</v>
       </c>
       <c r="B147" t="n">
         <v>79018</v>
@@ -15289,10 +15299,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>674297</v>
+        <v>673825</v>
       </c>
       <c r="R147" t="n">
-        <v>7092976</v>
+        <v>7092923</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15327,11 +15337,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -15344,44 +15349,48 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126915991</v>
+        <v>126912651</v>
       </c>
       <c r="B148" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15391,13 +15400,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>673971</v>
+        <v>674297</v>
       </c>
       <c r="R148" t="n">
-        <v>7092936</v>
+        <v>7092976</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15427,6 +15436,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15441,23 +15455,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126919007</v>
+        <v>126913182</v>
       </c>
       <c r="B149" t="n">
         <v>79018</v>
@@ -15492,10 +15502,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>673940</v>
+        <v>674316</v>
       </c>
       <c r="R149" t="n">
-        <v>7093045</v>
+        <v>7093018</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15530,30 +15540,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15564,7 +15568,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126919075</v>
+        <v>126912676</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -15599,10 +15603,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>673825</v>
+        <v>674259</v>
       </c>
       <c r="R150" t="n">
-        <v>7092923</v>
+        <v>7093064</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15649,23 +15653,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126919069</v>
+        <v>126912670</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -15700,10 +15700,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>673685</v>
+        <v>674225</v>
       </c>
       <c r="R151" t="n">
-        <v>7092946</v>
+        <v>7093014</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15750,23 +15750,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126913182</v>
+        <v>126919069</v>
       </c>
       <c r="B152" t="n">
         <v>79018</v>
@@ -15801,10 +15797,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>674316</v>
+        <v>673685</v>
       </c>
       <c r="R152" t="n">
-        <v>7093018</v>
+        <v>7092946</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15851,12 +15847,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15867,32 +15863,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126912676</v>
+        <v>126915991</v>
       </c>
       <c r="B153" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15902,13 +15898,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>674259</v>
+        <v>673971</v>
       </c>
       <c r="R153" t="n">
-        <v>7093064</v>
+        <v>7092936</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -15952,15 +15948,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr"/>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16070,32 +16070,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126912692</v>
+        <v>126915602</v>
       </c>
       <c r="B155" t="n">
-        <v>79018</v>
+        <v>98351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674236</v>
+        <v>674319</v>
       </c>
       <c r="R155" t="n">
-        <v>7092908</v>
+        <v>7092980</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16155,44 +16155,48 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126919063</v>
+        <v>126915603</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>98351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16202,10 +16206,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>673530</v>
+        <v>674278</v>
       </c>
       <c r="R156" t="n">
-        <v>7093126</v>
+        <v>7092923</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16252,12 +16256,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16268,32 +16272,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126919070</v>
+        <v>126915634</v>
       </c>
       <c r="B157" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16303,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>673731</v>
+        <v>674163</v>
       </c>
       <c r="R157" t="n">
-        <v>7092924</v>
+        <v>7092870</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16353,12 +16357,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16369,32 +16373,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126915634</v>
+        <v>126912692</v>
       </c>
       <c r="B158" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16404,10 +16408,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674163</v>
+        <v>674236</v>
       </c>
       <c r="R158" t="n">
-        <v>7092870</v>
+        <v>7092908</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16454,48 +16458,44 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126915603</v>
+        <v>126919063</v>
       </c>
       <c r="B159" t="n">
-        <v>98351</v>
+        <v>79018</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16505,10 +16505,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>674278</v>
+        <v>673530</v>
       </c>
       <c r="R159" t="n">
-        <v>7092923</v>
+        <v>7093126</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16555,12 +16555,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16571,32 +16571,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126915602</v>
+        <v>126919070</v>
       </c>
       <c r="B160" t="n">
-        <v>98351</v>
+        <v>79018</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16606,10 +16606,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>674319</v>
+        <v>673731</v>
       </c>
       <c r="R160" t="n">
-        <v>7092980</v>
+        <v>7092924</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16656,12 +16656,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16971,10 +16971,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912594</v>
+        <v>126915599</v>
       </c>
       <c r="B164" t="n">
-        <v>80150</v>
+        <v>98351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16982,21 +16982,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674121</v>
+        <v>674272</v>
       </c>
       <c r="R164" t="n">
-        <v>7092931</v>
+        <v>7093054</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17056,15 +17056,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17169,32 +17173,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126918993</v>
+        <v>126912684</v>
       </c>
       <c r="B166" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17204,10 +17208,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>673937</v>
+        <v>674292</v>
       </c>
       <c r="R166" t="n">
-        <v>7093103</v>
+        <v>7092976</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17248,55 +17252,50 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126912684</v>
+        <v>126912594</v>
       </c>
       <c r="B167" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17306,10 +17305,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>674292</v>
+        <v>674121</v>
       </c>
       <c r="R167" t="n">
-        <v>7092976</v>
+        <v>7092931</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17368,10 +17367,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126915599</v>
+        <v>126918993</v>
       </c>
       <c r="B168" t="n">
-        <v>98351</v>
+        <v>80025</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17379,21 +17378,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17403,10 +17402,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>674272</v>
+        <v>673937</v>
       </c>
       <c r="R168" t="n">
-        <v>7093054</v>
+        <v>7093103</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17447,6 +17446,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20233,10 +20233,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126913448</v>
+        <v>126913475</v>
       </c>
       <c r="B196" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20244,21 +20244,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20268,10 +20268,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>673558</v>
+        <v>673753</v>
       </c>
       <c r="R196" t="n">
-        <v>7093130</v>
+        <v>7093083</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20334,10 +20334,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126913475</v>
+        <v>126913448</v>
       </c>
       <c r="B197" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20345,21 +20345,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20369,10 +20369,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>673753</v>
+        <v>673558</v>
       </c>
       <c r="R197" t="n">
-        <v>7093083</v>
+        <v>7093130</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126913188</v>
+        <v>126912574</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673761</v>
+        <v>674224</v>
       </c>
       <c r="R18" t="n">
-        <v>7092946</v>
+        <v>7092965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,26 +2453,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126912574</v>
+        <v>126915627</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674224</v>
+        <v>674167</v>
       </c>
       <c r="R19" t="n">
-        <v>7092965</v>
+        <v>7093069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,44 +2550,48 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126915627</v>
+        <v>126912616</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674167</v>
+        <v>674220</v>
       </c>
       <c r="R20" t="n">
-        <v>7093069</v>
+        <v>7092919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,48 +2651,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126912616</v>
+        <v>126915606</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2702,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674220</v>
+        <v>674275</v>
       </c>
       <c r="R21" t="n">
-        <v>7092919</v>
+        <v>7092845</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,19 +2748,23 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126915606</v>
+        <v>126919035</v>
       </c>
       <c r="B22" t="n">
         <v>98447</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>674275</v>
+        <v>673577</v>
       </c>
       <c r="R22" t="n">
-        <v>7092845</v>
+        <v>7093132</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2865,7 +2865,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126919035</v>
+        <v>126915611</v>
       </c>
       <c r="B23" t="n">
         <v>98447</v>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673577</v>
+        <v>674207</v>
       </c>
       <c r="R23" t="n">
-        <v>7093132</v>
+        <v>7092810</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,12 +2950,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2966,7 +2966,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126915611</v>
+        <v>126913188</v>
       </c>
       <c r="B24" t="n">
         <v>98447</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>674207</v>
+        <v>673761</v>
       </c>
       <c r="R24" t="n">
-        <v>7092810</v>
+        <v>7092946</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,12 +3051,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126918783</v>
+        <v>126915590</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>58492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>208245</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674284</v>
+        <v>674272</v>
       </c>
       <c r="R30" t="n">
-        <v>7093057</v>
+        <v>7092912</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3665,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126919043</v>
+        <v>126918783</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673945</v>
+        <v>674284</v>
       </c>
       <c r="R31" t="n">
-        <v>7092938</v>
+        <v>7093057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,12 +3750,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126913209</v>
+        <v>126919043</v>
       </c>
       <c r="B32" t="n">
         <v>98447</v>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>674212</v>
+        <v>673945</v>
       </c>
       <c r="R32" t="n">
-        <v>7092826</v>
+        <v>7092938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,12 +3851,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126915590</v>
+        <v>126913209</v>
       </c>
       <c r="B33" t="n">
-        <v>58492</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674272</v>
+        <v>674212</v>
       </c>
       <c r="R33" t="n">
-        <v>7092912</v>
+        <v>7092826</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915572</v>
+        <v>126915612</v>
       </c>
       <c r="B42" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674324</v>
+        <v>674198</v>
       </c>
       <c r="R42" t="n">
-        <v>7093076</v>
+        <v>7092843</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912685</v>
+        <v>126918790</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674236</v>
+        <v>674101</v>
       </c>
       <c r="R43" t="n">
-        <v>7092969</v>
+        <v>7092979</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,19 +4955,23 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912666</v>
+        <v>126912685</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -5002,10 +5006,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674176</v>
+        <v>674236</v>
       </c>
       <c r="R44" t="n">
-        <v>7093061</v>
+        <v>7092969</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5064,7 +5068,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913207</v>
+        <v>126912666</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5099,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674182</v>
+        <v>674176</v>
       </c>
       <c r="R45" t="n">
-        <v>7092837</v>
+        <v>7093061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,23 +5153,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919067</v>
+        <v>126913207</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673610</v>
+        <v>674182</v>
       </c>
       <c r="R46" t="n">
-        <v>7092955</v>
+        <v>7092837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5266,32 +5266,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919074</v>
+        <v>126915572</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673796</v>
+        <v>674324</v>
       </c>
       <c r="R47" t="n">
-        <v>7092899</v>
+        <v>7093076</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912683</v>
+        <v>126919067</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674310</v>
+        <v>673610</v>
       </c>
       <c r="R48" t="n">
-        <v>7092998</v>
+        <v>7092955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,44 +5452,48 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126915612</v>
+        <v>126919074</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5499,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674198</v>
+        <v>673796</v>
       </c>
       <c r="R49" t="n">
-        <v>7092843</v>
+        <v>7092899</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,12 +5553,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5565,32 +5569,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918790</v>
+        <v>126912683</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5600,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674101</v>
+        <v>674310</v>
       </c>
       <c r="R50" t="n">
-        <v>7092979</v>
+        <v>7092998</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,19 +5654,15 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912680</v>
+        <v>126912590</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,34 +7892,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674302</v>
+        <v>673958</v>
       </c>
       <c r="R73" t="n">
-        <v>7093031</v>
+        <v>7093109</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7978,10 +7983,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912579</v>
+        <v>126912625</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,21 +7994,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8075,7 +8080,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126919068</v>
+        <v>126912680</v>
       </c>
       <c r="B75" t="n">
         <v>79018</v>
@@ -8110,10 +8115,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>673630</v>
+        <v>674302</v>
       </c>
       <c r="R75" t="n">
-        <v>7092929</v>
+        <v>7093031</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8160,26 +8165,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912590</v>
+        <v>126912579</v>
       </c>
       <c r="B76" t="n">
-        <v>57821</v>
+        <v>79636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8187,39 +8188,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673958</v>
+        <v>674239</v>
       </c>
       <c r="R76" t="n">
-        <v>7093109</v>
+        <v>7092908</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8278,10 +8274,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126912625</v>
+        <v>126919068</v>
       </c>
       <c r="B77" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8289,21 +8285,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8313,10 +8309,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>674239</v>
+        <v>673630</v>
       </c>
       <c r="R77" t="n">
-        <v>7092908</v>
+        <v>7092929</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8363,15 +8359,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8573,32 +8573,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918795</v>
+        <v>126918802</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674236</v>
+        <v>674315</v>
       </c>
       <c r="R80" t="n">
-        <v>7092852</v>
+        <v>7093023</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8674,50 +8674,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126912599</v>
+        <v>126918795</v>
       </c>
       <c r="B81" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674251</v>
+        <v>674236</v>
       </c>
       <c r="R81" t="n">
-        <v>7093028</v>
+        <v>7092852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8764,57 +8759,66 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918802</v>
+        <v>126912599</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674315</v>
+        <v>674251</v>
       </c>
       <c r="R82" t="n">
-        <v>7093023</v>
+        <v>7093028</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8861,19 +8865,15 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9665,10 +9665,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126912634</v>
+        <v>126918807</v>
       </c>
       <c r="B91" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674203</v>
+        <v>674208</v>
       </c>
       <c r="R91" t="n">
-        <v>7092932</v>
+        <v>7092856</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,22 +9750,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126918789</v>
+        <v>126912578</v>
       </c>
       <c r="B92" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9773,21 +9777,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9797,10 +9801,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R92" t="n">
-        <v>7092997</v>
+        <v>7092914</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9847,26 +9851,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126912703</v>
+        <v>126913181</v>
       </c>
       <c r="B93" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674269</v>
+        <v>674236</v>
       </c>
       <c r="R93" t="n">
-        <v>7092979</v>
+        <v>7093024</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9948,19 +9948,23 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126918807</v>
+        <v>126919072</v>
       </c>
       <c r="B94" t="n">
         <v>79018</v>
@@ -9995,10 +9999,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>674208</v>
+        <v>673738</v>
       </c>
       <c r="R94" t="n">
-        <v>7092856</v>
+        <v>7092885</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,12 +10049,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10061,32 +10065,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912578</v>
+        <v>126912614</v>
       </c>
       <c r="B95" t="n">
-        <v>79636</v>
+        <v>80149</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10096,10 +10100,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674218</v>
+        <v>674319</v>
       </c>
       <c r="R95" t="n">
-        <v>7092914</v>
+        <v>7093047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10158,10 +10162,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126913181</v>
+        <v>126912634</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10169,21 +10173,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10193,10 +10197,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674236</v>
+        <v>674203</v>
       </c>
       <c r="R96" t="n">
-        <v>7093024</v>
+        <v>7092932</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10243,26 +10247,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126919072</v>
+        <v>126918789</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,21 +10270,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>673738</v>
+        <v>674310</v>
       </c>
       <c r="R97" t="n">
-        <v>7092885</v>
+        <v>7092997</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,12 +10344,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10360,32 +10360,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126912614</v>
+        <v>126918984</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>79636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>674319</v>
+        <v>673919</v>
       </c>
       <c r="R98" t="n">
-        <v>7093047</v>
+        <v>7093017</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10445,44 +10445,48 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126918984</v>
+        <v>126915610</v>
       </c>
       <c r="B99" t="n">
-        <v>79636</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10492,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>673919</v>
+        <v>674211</v>
       </c>
       <c r="R99" t="n">
-        <v>7093017</v>
+        <v>7092807</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10547,7 +10551,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10558,32 +10562,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126912624</v>
+        <v>126915609</v>
       </c>
       <c r="B100" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10593,10 +10597,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674218</v>
+        <v>674231</v>
       </c>
       <c r="R100" t="n">
-        <v>7092914</v>
+        <v>7092812</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10643,44 +10647,48 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126915610</v>
+        <v>126912624</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10698,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>674211</v>
+        <v>674218</v>
       </c>
       <c r="R101" t="n">
-        <v>7092807</v>
+        <v>7092914</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,48 +10748,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126915609</v>
+        <v>126912703</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>78685</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10791,10 +10795,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674231</v>
+        <v>674269</v>
       </c>
       <c r="R102" t="n">
-        <v>7092812</v>
+        <v>7092979</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10841,19 +10845,15 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11756,32 +11756,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126912689</v>
+        <v>126915628</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674237</v>
+        <v>674258</v>
       </c>
       <c r="R112" t="n">
-        <v>7092921</v>
+        <v>7093046</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,19 +11841,23 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126918801</v>
+        <v>126912689</v>
       </c>
       <c r="B113" t="n">
         <v>79018</v>
@@ -11888,10 +11892,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674148</v>
+        <v>674237</v>
       </c>
       <c r="R113" t="n">
-        <v>7093061</v>
+        <v>7092921</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11938,23 +11942,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918810</v>
+        <v>126918801</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674189</v>
+        <v>674148</v>
       </c>
       <c r="R114" t="n">
-        <v>7092854</v>
+        <v>7093061</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12055,10 +12055,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126912577</v>
+        <v>126918810</v>
       </c>
       <c r="B115" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,21 +12066,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>674204</v>
+        <v>674189</v>
       </c>
       <c r="R115" t="n">
-        <v>7092934</v>
+        <v>7092854</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12140,22 +12140,26 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126918998</v>
+        <v>126912577</v>
       </c>
       <c r="B116" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12163,21 +12167,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12187,10 +12191,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>673861</v>
+        <v>674204</v>
       </c>
       <c r="R116" t="n">
-        <v>7093031</v>
+        <v>7092934</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12237,23 +12241,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126918776</v>
+        <v>126918998</v>
       </c>
       <c r="B117" t="n">
         <v>78777</v>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>674139</v>
+        <v>673861</v>
       </c>
       <c r="R117" t="n">
-        <v>7092939</v>
+        <v>7093031</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12338,12 +12338,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12354,32 +12354,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126915628</v>
+        <v>126918776</v>
       </c>
       <c r="B118" t="n">
-        <v>98364</v>
+        <v>78777</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12389,10 +12389,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>674258</v>
+        <v>674139</v>
       </c>
       <c r="R118" t="n">
-        <v>7093046</v>
+        <v>7092939</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12439,12 +12439,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13749,45 +13749,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126912682</v>
+        <v>126912638</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>674304</v>
+        <v>674111</v>
       </c>
       <c r="R132" t="n">
-        <v>7093013</v>
+        <v>7092937</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13846,7 +13855,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912675</v>
+        <v>126912682</v>
       </c>
       <c r="B133" t="n">
         <v>79018</v>
@@ -13881,10 +13890,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674268</v>
+        <v>674304</v>
       </c>
       <c r="R133" t="n">
-        <v>7093042</v>
+        <v>7093013</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13943,32 +13952,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126912593</v>
+        <v>126912675</v>
       </c>
       <c r="B134" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13978,10 +13987,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>674210</v>
+        <v>674268</v>
       </c>
       <c r="R134" t="n">
-        <v>7092877</v>
+        <v>7093042</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14040,49 +14049,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126913960</v>
+        <v>126912593</v>
       </c>
       <c r="B135" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>673577</v>
+        <v>674210</v>
       </c>
       <c r="R135" t="n">
-        <v>7093132</v>
+        <v>7092877</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14117,11 +14122,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14134,70 +14134,61 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126912638</v>
+        <v>126913960</v>
       </c>
       <c r="B136" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>674111</v>
+        <v>673577</v>
       </c>
       <c r="R136" t="n">
-        <v>7092937</v>
+        <v>7093132</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14232,6 +14223,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14244,15 +14240,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14357,10 +14357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126913193</v>
+        <v>126919027</v>
       </c>
       <c r="B138" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>673849</v>
+        <v>673554</v>
       </c>
       <c r="R138" t="n">
-        <v>7092944</v>
+        <v>7093135</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,12 +14442,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14757,10 +14757,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126919027</v>
+        <v>126913193</v>
       </c>
       <c r="B142" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>673554</v>
+        <v>673849</v>
       </c>
       <c r="R142" t="n">
-        <v>7093135</v>
+        <v>7092944</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -16070,10 +16070,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126915602</v>
+        <v>126915634</v>
       </c>
       <c r="B155" t="n">
-        <v>98351</v>
+        <v>98364</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16081,21 +16081,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>674319</v>
+        <v>674163</v>
       </c>
       <c r="R155" t="n">
-        <v>7092980</v>
+        <v>7092870</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16171,7 +16171,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126915603</v>
+        <v>126915602</v>
       </c>
       <c r="B156" t="n">
         <v>98351</v>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>674278</v>
+        <v>674319</v>
       </c>
       <c r="R156" t="n">
-        <v>7092923</v>
+        <v>7092980</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16272,10 +16272,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126915634</v>
+        <v>126915603</v>
       </c>
       <c r="B157" t="n">
-        <v>98364</v>
+        <v>98351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16283,21 +16283,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16307,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>674163</v>
+        <v>674278</v>
       </c>
       <c r="R157" t="n">
-        <v>7092870</v>
+        <v>7092923</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16373,32 +16373,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126912692</v>
+        <v>126915613</v>
       </c>
       <c r="B158" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16408,10 +16408,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>674236</v>
+        <v>674171</v>
       </c>
       <c r="R158" t="n">
-        <v>7092908</v>
+        <v>7092865</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16458,44 +16458,48 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126919063</v>
+        <v>126918792</v>
       </c>
       <c r="B159" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16505,10 +16509,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>673530</v>
+        <v>674129</v>
       </c>
       <c r="R159" t="n">
-        <v>7093126</v>
+        <v>7093003</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16555,12 +16559,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16571,7 +16575,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126919070</v>
+        <v>126919063</v>
       </c>
       <c r="B160" t="n">
         <v>79018</v>
@@ -16606,10 +16610,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>673731</v>
+        <v>673530</v>
       </c>
       <c r="R160" t="n">
-        <v>7092924</v>
+        <v>7093126</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16672,32 +16676,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126915613</v>
+        <v>126919070</v>
       </c>
       <c r="B161" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16707,10 +16711,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>674171</v>
+        <v>673731</v>
       </c>
       <c r="R161" t="n">
-        <v>7092865</v>
+        <v>7092924</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16757,12 +16761,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16773,32 +16777,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126918792</v>
+        <v>126912692</v>
       </c>
       <c r="B162" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16812,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>674129</v>
+        <v>674236</v>
       </c>
       <c r="R162" t="n">
-        <v>7093003</v>
+        <v>7092908</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16858,48 +16862,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126912704</v>
+        <v>126915599</v>
       </c>
       <c r="B163" t="n">
-        <v>78685</v>
+        <v>98351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674200</v>
+        <v>674272</v>
       </c>
       <c r="R163" t="n">
-        <v>7092950</v>
+        <v>7093054</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16959,44 +16959,48 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126915599</v>
+        <v>126912704</v>
       </c>
       <c r="B164" t="n">
-        <v>98351</v>
+        <v>78685</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220093</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17006,10 +17010,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674272</v>
+        <v>674200</v>
       </c>
       <c r="R164" t="n">
-        <v>7093054</v>
+        <v>7092950</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17056,19 +17060,15 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17570,10 +17570,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126916008</v>
+        <v>126915992</v>
       </c>
       <c r="B170" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17581,21 +17581,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>673779</v>
+        <v>673832</v>
       </c>
       <c r="R170" t="n">
-        <v>7092998</v>
+        <v>7092995</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17671,10 +17671,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126915992</v>
+        <v>126915987</v>
       </c>
       <c r="B171" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17682,21 +17682,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17706,10 +17706,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>673832</v>
+        <v>673839</v>
       </c>
       <c r="R171" t="n">
-        <v>7092995</v>
+        <v>7093005</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -17772,10 +17772,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126915987</v>
+        <v>126916008</v>
       </c>
       <c r="B172" t="n">
-        <v>79607</v>
+        <v>78685</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17783,21 +17783,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17807,10 +17807,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>673839</v>
+        <v>673779</v>
       </c>
       <c r="R172" t="n">
-        <v>7093005</v>
+        <v>7092998</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1661,32 +1661,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B11" t="n">
-        <v>80025</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R11" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919065</v>
+        <v>126918995</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673619</v>
+        <v>673947</v>
       </c>
       <c r="R12" t="n">
-        <v>7092978</v>
+        <v>7093045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126915585</v>
+        <v>126919065</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>674324</v>
+        <v>673619</v>
       </c>
       <c r="R13" t="n">
-        <v>7093076</v>
+        <v>7092978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915612</v>
+        <v>126915572</v>
       </c>
       <c r="B42" t="n">
-        <v>98447</v>
+        <v>91295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674198</v>
+        <v>674324</v>
       </c>
       <c r="R42" t="n">
-        <v>7092843</v>
+        <v>7093076</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126918790</v>
+        <v>126912685</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674101</v>
+        <v>674236</v>
       </c>
       <c r="R43" t="n">
-        <v>7092979</v>
+        <v>7092969</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,23 +4955,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912685</v>
+        <v>126912666</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -5006,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674236</v>
+        <v>674176</v>
       </c>
       <c r="R44" t="n">
-        <v>7092969</v>
+        <v>7093061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,7 +5064,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912666</v>
+        <v>126913207</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5103,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674176</v>
+        <v>674182</v>
       </c>
       <c r="R45" t="n">
-        <v>7093061</v>
+        <v>7092837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,19 +5149,23 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913207</v>
+        <v>126919067</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>674182</v>
+        <v>673610</v>
       </c>
       <c r="R46" t="n">
-        <v>7092837</v>
+        <v>7092955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,12 +5250,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5266,32 +5266,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126915572</v>
+        <v>126919074</v>
       </c>
       <c r="B47" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>674324</v>
+        <v>673796</v>
       </c>
       <c r="R47" t="n">
-        <v>7093076</v>
+        <v>7092899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919067</v>
+        <v>126912683</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673610</v>
+        <v>674310</v>
       </c>
       <c r="R48" t="n">
-        <v>7092955</v>
+        <v>7092998</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,48 +5452,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919074</v>
+        <v>126915612</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>673796</v>
+        <v>674198</v>
       </c>
       <c r="R49" t="n">
-        <v>7092899</v>
+        <v>7092843</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5553,12 +5549,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5569,32 +5565,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912683</v>
+        <v>126918790</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674310</v>
+        <v>674101</v>
       </c>
       <c r="R50" t="n">
-        <v>7092998</v>
+        <v>7092979</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5654,15 +5650,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5767,10 +5767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919000</v>
+        <v>126919076</v>
       </c>
       <c r="B52" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,21 +5778,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673939</v>
+        <v>673836</v>
       </c>
       <c r="R52" t="n">
-        <v>7093012</v>
+        <v>7092910</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5852,12 +5852,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126919076</v>
+        <v>126912576</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>673836</v>
+        <v>674200</v>
       </c>
       <c r="R53" t="n">
-        <v>7092910</v>
+        <v>7092950</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5953,61 +5953,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912576</v>
+        <v>126913179</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>80025</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>674200</v>
+        <v>673719</v>
       </c>
       <c r="R54" t="n">
-        <v>7092950</v>
+        <v>7093035</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6048,66 +6047,68 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913179</v>
+        <v>126915608</v>
       </c>
       <c r="B55" t="n">
-        <v>80025</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>673719</v>
+        <v>674257</v>
       </c>
       <c r="R55" t="n">
-        <v>7093035</v>
+        <v>7092823</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6148,19 +6149,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6171,45 +6171,61 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126915630</v>
+        <v>126913214</v>
       </c>
       <c r="B56" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674328</v>
+        <v>674219</v>
       </c>
       <c r="R56" t="n">
-        <v>7092980</v>
+        <v>7092815</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6250,18 +6266,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6272,7 +6289,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912700</v>
+        <v>126915630</v>
       </c>
       <c r="B57" t="n">
         <v>98364</v>
@@ -6307,10 +6324,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674267</v>
+        <v>674328</v>
       </c>
       <c r="R57" t="n">
-        <v>7093044</v>
+        <v>7092980</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6357,44 +6374,48 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126915608</v>
+        <v>126912700</v>
       </c>
       <c r="B58" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6404,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674257</v>
+        <v>674267</v>
       </c>
       <c r="R58" t="n">
-        <v>7092823</v>
+        <v>7093044</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6454,77 +6475,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126913214</v>
+        <v>126919000</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>674219</v>
+        <v>673939</v>
       </c>
       <c r="R59" t="n">
-        <v>7092815</v>
+        <v>7093012</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,19 +6566,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912590</v>
+        <v>126912680</v>
       </c>
       <c r="B73" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,39 +7892,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>673958</v>
+        <v>674302</v>
       </c>
       <c r="R73" t="n">
-        <v>7093109</v>
+        <v>7093031</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7983,10 +7978,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912625</v>
+        <v>126912579</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7994,21 +7989,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8080,7 +8075,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912680</v>
+        <v>126919068</v>
       </c>
       <c r="B75" t="n">
         <v>79018</v>
@@ -8115,10 +8110,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>674302</v>
+        <v>673630</v>
       </c>
       <c r="R75" t="n">
-        <v>7093031</v>
+        <v>7092929</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8165,22 +8160,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912579</v>
+        <v>126912590</v>
       </c>
       <c r="B76" t="n">
-        <v>79636</v>
+        <v>57821</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,34 +8187,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>674239</v>
+        <v>673958</v>
       </c>
       <c r="R76" t="n">
-        <v>7092908</v>
+        <v>7093109</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8274,10 +8278,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126919068</v>
+        <v>126912625</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8285,21 +8289,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8309,10 +8313,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>673630</v>
+        <v>674239</v>
       </c>
       <c r="R77" t="n">
-        <v>7092929</v>
+        <v>7092908</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8359,48 +8363,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126912669</v>
+        <v>126918795</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674218</v>
+        <v>674236</v>
       </c>
       <c r="R78" t="n">
-        <v>7093013</v>
+        <v>7092852</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,22 +8460,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913210</v>
+        <v>126912599</v>
       </c>
       <c r="B79" t="n">
-        <v>80150</v>
+        <v>98468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8483,34 +8487,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674282</v>
+        <v>674251</v>
       </c>
       <c r="R79" t="n">
-        <v>7092828</v>
+        <v>7093028</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,23 +8566,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126918802</v>
+        <v>126912669</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -8608,10 +8613,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674315</v>
+        <v>674218</v>
       </c>
       <c r="R80" t="n">
-        <v>7093023</v>
+        <v>7093013</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8658,48 +8663,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126918795</v>
+        <v>126913210</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8709,10 +8710,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674236</v>
+        <v>674282</v>
       </c>
       <c r="R81" t="n">
-        <v>7092852</v>
+        <v>7092828</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8759,12 +8760,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8775,50 +8776,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126912599</v>
+        <v>126918802</v>
       </c>
       <c r="B82" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674251</v>
+        <v>674315</v>
       </c>
       <c r="R82" t="n">
-        <v>7093028</v>
+        <v>7093023</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8865,15 +8861,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -13749,54 +13749,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126912638</v>
+        <v>126912682</v>
       </c>
       <c r="B132" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>674111</v>
+        <v>674304</v>
       </c>
       <c r="R132" t="n">
-        <v>7092937</v>
+        <v>7093013</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13855,7 +13846,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126912682</v>
+        <v>126912675</v>
       </c>
       <c r="B133" t="n">
         <v>79018</v>
@@ -13890,10 +13881,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>674304</v>
+        <v>674268</v>
       </c>
       <c r="R133" t="n">
-        <v>7093013</v>
+        <v>7093042</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13952,32 +13943,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126912675</v>
+        <v>126912593</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13987,10 +13978,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>674268</v>
+        <v>674210</v>
       </c>
       <c r="R134" t="n">
-        <v>7093042</v>
+        <v>7092877</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14049,45 +14040,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126912593</v>
+        <v>126913960</v>
       </c>
       <c r="B135" t="n">
-        <v>80150</v>
+        <v>57661</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>674210</v>
+        <v>673577</v>
       </c>
       <c r="R135" t="n">
-        <v>7092877</v>
+        <v>7093132</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14122,6 +14117,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14134,61 +14134,70 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126913960</v>
+        <v>126912638</v>
       </c>
       <c r="B136" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>673577</v>
+        <v>674111</v>
       </c>
       <c r="R136" t="n">
-        <v>7093132</v>
+        <v>7092937</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14223,11 +14232,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14240,19 +14244,15 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14357,10 +14357,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126919027</v>
+        <v>126913193</v>
       </c>
       <c r="B138" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>673554</v>
+        <v>673849</v>
       </c>
       <c r="R138" t="n">
-        <v>7093135</v>
+        <v>7092944</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14442,12 +14442,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14757,10 +14757,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126913193</v>
+        <v>126919027</v>
       </c>
       <c r="B142" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14768,21 +14768,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14792,10 +14792,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>673849</v>
+        <v>673554</v>
       </c>
       <c r="R142" t="n">
-        <v>7092944</v>
+        <v>7093135</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,12 +14842,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -14858,10 +14858,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126915629</v>
+        <v>126919017</v>
       </c>
       <c r="B143" t="n">
-        <v>98364</v>
+        <v>56853</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14869,21 +14869,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>674305</v>
+        <v>673668</v>
       </c>
       <c r="R143" t="n">
-        <v>7093077</v>
+        <v>7092943</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14931,6 +14931,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Skrämde tupp</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -14943,12 +14948,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14959,32 +14964,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126919041</v>
+        <v>126915629</v>
       </c>
       <c r="B144" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14994,10 +14999,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>673735</v>
+        <v>674305</v>
       </c>
       <c r="R144" t="n">
-        <v>7092926</v>
+        <v>7093077</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15044,12 +15049,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15060,32 +15065,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126919007</v>
+        <v>126919041</v>
       </c>
       <c r="B145" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15095,10 +15100,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>673940</v>
+        <v>673735</v>
       </c>
       <c r="R145" t="n">
-        <v>7093045</v>
+        <v>7092926</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15133,30 +15138,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Äldre tal</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15167,7 +15166,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126912688</v>
+        <v>126919007</v>
       </c>
       <c r="B146" t="n">
         <v>79018</v>
@@ -15202,10 +15201,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>674231</v>
+        <v>673940</v>
       </c>
       <c r="R146" t="n">
-        <v>7092932</v>
+        <v>7093045</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15240,31 +15239,41 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Äldre tal</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126919075</v>
+        <v>126912688</v>
       </c>
       <c r="B147" t="n">
         <v>79018</v>
@@ -15299,10 +15308,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>673825</v>
+        <v>674231</v>
       </c>
       <c r="R147" t="n">
-        <v>7092923</v>
+        <v>7092932</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15349,23 +15358,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126912651</v>
+        <v>126919075</v>
       </c>
       <c r="B148" t="n">
         <v>79018</v>
@@ -15400,10 +15405,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>674297</v>
+        <v>673825</v>
       </c>
       <c r="R148" t="n">
-        <v>7092976</v>
+        <v>7092923</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15438,11 +15443,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På tall m brandljud som saknar hänsynsmarkering</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -15455,19 +15455,23 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126913182</v>
+        <v>126912651</v>
       </c>
       <c r="B149" t="n">
         <v>79018</v>
@@ -15502,10 +15506,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>674316</v>
+        <v>674297</v>
       </c>
       <c r="R149" t="n">
-        <v>7093018</v>
+        <v>7092976</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15540,6 +15544,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På tall m brandljud som saknar hänsynsmarkering</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -15552,23 +15561,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126912676</v>
+        <v>126913182</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -15603,10 +15608,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>674259</v>
+        <v>674316</v>
       </c>
       <c r="R150" t="n">
-        <v>7093064</v>
+        <v>7093018</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15653,19 +15658,23 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126912670</v>
+        <v>126912676</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -15700,10 +15709,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>674225</v>
+        <v>674259</v>
       </c>
       <c r="R151" t="n">
-        <v>7093014</v>
+        <v>7093064</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15762,7 +15771,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126919069</v>
+        <v>126912670</v>
       </c>
       <c r="B152" t="n">
         <v>79018</v>
@@ -15797,10 +15806,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>673685</v>
+        <v>674225</v>
       </c>
       <c r="R152" t="n">
-        <v>7092946</v>
+        <v>7093014</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15847,48 +15856,44 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126915991</v>
+        <v>126919069</v>
       </c>
       <c r="B153" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15898,13 +15903,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>673971</v>
+        <v>673685</v>
       </c>
       <c r="R153" t="n">
-        <v>7092936</v>
+        <v>7092946</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -15948,12 +15953,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -15964,10 +15969,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126919017</v>
+        <v>126915991</v>
       </c>
       <c r="B154" t="n">
-        <v>56853</v>
+        <v>80150</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15975,21 +15980,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15999,13 +16004,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>673668</v>
+        <v>673971</v>
       </c>
       <c r="R154" t="n">
-        <v>7092943</v>
+        <v>7092936</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16035,11 +16040,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Skrämde tupp</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16054,12 +16054,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16874,32 +16874,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126915599</v>
+        <v>126912704</v>
       </c>
       <c r="B163" t="n">
-        <v>98351</v>
+        <v>78685</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220093</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16909,10 +16909,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>674272</v>
+        <v>674200</v>
       </c>
       <c r="R163" t="n">
-        <v>7093054</v>
+        <v>7092950</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16959,48 +16959,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126912704</v>
+        <v>126915599</v>
       </c>
       <c r="B164" t="n">
-        <v>78685</v>
+        <v>98351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>220093</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17010,10 +17006,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>674200</v>
+        <v>674272</v>
       </c>
       <c r="R164" t="n">
-        <v>7092950</v>
+        <v>7093054</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17060,15 +17056,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17570,10 +17570,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126915992</v>
+        <v>126916008</v>
       </c>
       <c r="B170" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17581,21 +17581,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>673832</v>
+        <v>673779</v>
       </c>
       <c r="R170" t="n">
-        <v>7092995</v>
+        <v>7092998</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -17671,10 +17671,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126915987</v>
+        <v>126915992</v>
       </c>
       <c r="B171" t="n">
-        <v>79607</v>
+        <v>78777</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17682,21 +17682,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17706,10 +17706,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>673839</v>
+        <v>673832</v>
       </c>
       <c r="R171" t="n">
-        <v>7093005</v>
+        <v>7092995</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -17772,10 +17772,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126916008</v>
+        <v>126915987</v>
       </c>
       <c r="B172" t="n">
-        <v>78685</v>
+        <v>79607</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17783,21 +17783,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17807,10 +17807,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>673779</v>
+        <v>673839</v>
       </c>
       <c r="R172" t="n">
-        <v>7092998</v>
+        <v>7093005</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -20233,10 +20233,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126913475</v>
+        <v>126913448</v>
       </c>
       <c r="B196" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20244,21 +20244,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20268,10 +20268,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>673753</v>
+        <v>673558</v>
       </c>
       <c r="R196" t="n">
-        <v>7093083</v>
+        <v>7093130</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20334,10 +20334,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126913448</v>
+        <v>126913475</v>
       </c>
       <c r="B197" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20345,21 +20345,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20369,10 +20369,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>673558</v>
+        <v>673753</v>
       </c>
       <c r="R197" t="n">
-        <v>7093130</v>
+        <v>7093083</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>

--- a/artfynd/A 25995-2024 artfynd.xlsx
+++ b/artfynd/A 25995-2024 artfynd.xlsx
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918800</v>
+        <v>126919065</v>
       </c>
       <c r="B9" t="n">
         <v>79018</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674103</v>
+        <v>673619</v>
       </c>
       <c r="R9" t="n">
-        <v>7093056</v>
+        <v>7092978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,12 +1544,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126916005</v>
+        <v>126918800</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673879</v>
+        <v>674103</v>
       </c>
       <c r="R10" t="n">
-        <v>7092985</v>
+        <v>7093056</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,12 +1645,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126915585</v>
+        <v>126916005</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>674324</v>
+        <v>673879</v>
       </c>
       <c r="R11" t="n">
-        <v>7093076</v>
+        <v>7092985</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1762,32 +1762,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918995</v>
+        <v>126915585</v>
       </c>
       <c r="B12" t="n">
-        <v>80025</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673947</v>
+        <v>674324</v>
       </c>
       <c r="R12" t="n">
-        <v>7093045</v>
+        <v>7093076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919065</v>
+        <v>126915632</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673619</v>
+        <v>674279</v>
       </c>
       <c r="R13" t="n">
-        <v>7092978</v>
+        <v>7092915</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126915632</v>
+        <v>126919040</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>674279</v>
+        <v>673649</v>
       </c>
       <c r="R14" t="n">
-        <v>7092915</v>
+        <v>7092943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2049,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2065,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918793</v>
+        <v>126913215</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>674251</v>
+        <v>674258</v>
       </c>
       <c r="R15" t="n">
-        <v>7092837</v>
+        <v>7092817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126919040</v>
+        <v>126918793</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673649</v>
+        <v>674251</v>
       </c>
       <c r="R16" t="n">
-        <v>7092943</v>
+        <v>7092837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,12 +2251,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126913215</v>
+        <v>126918995</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>80025</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>674258</v>
+        <v>673947</v>
       </c>
       <c r="R17" t="n">
-        <v>7092817</v>
+        <v>7093045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,12 +2352,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2368,32 +2368,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912574</v>
+        <v>126912616</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>674224</v>
+        <v>674220</v>
       </c>
       <c r="R18" t="n">
-        <v>7092965</v>
+        <v>7092919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126915627</v>
+        <v>126912574</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>674167</v>
+        <v>674224</v>
       </c>
       <c r="R19" t="n">
-        <v>7093069</v>
+        <v>7092965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,48 +2550,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126912616</v>
+        <v>126919035</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>674220</v>
+        <v>673577</v>
       </c>
       <c r="R20" t="n">
-        <v>7092919</v>
+        <v>7093132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,22 +2647,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126915606</v>
+        <v>126915611</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>674275</v>
+        <v>674207</v>
       </c>
       <c r="R21" t="n">
-        <v>7092845</v>
+        <v>7092810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126919035</v>
+        <v>126913188</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673577</v>
+        <v>673761</v>
       </c>
       <c r="R22" t="n">
-        <v>7093132</v>
+        <v>7092946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,12 +2849,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126915611</v>
+        <v>126915606</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>674207</v>
+        <v>674275</v>
       </c>
       <c r="R23" t="n">
-        <v>7092810</v>
+        <v>7092845</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126913188</v>
+        <v>126915627</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673761</v>
+        <v>674167</v>
       </c>
       <c r="R24" t="n">
-        <v>7092946</v>
+        <v>7093069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,12 +3051,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3067,32 +3067,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126912667</v>
+        <v>126915590</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>58492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>674201</v>
+        <v>674272</v>
       </c>
       <c r="R25" t="n">
-        <v>7093054</v>
+        <v>7092912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,44 +3152,48 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126919071</v>
+        <v>126915593</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673738</v>
+        <v>674310</v>
       </c>
       <c r="R26" t="n">
-        <v>7092907</v>
+        <v>7093054</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,12 +3253,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3366,10 +3370,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912633</v>
+        <v>126912667</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>674218</v>
+        <v>674201</v>
       </c>
       <c r="R28" t="n">
-        <v>7092957</v>
+        <v>7093054</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,32 +3467,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126915593</v>
+        <v>126912633</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>674310</v>
+        <v>674218</v>
       </c>
       <c r="R29" t="n">
-        <v>7093054</v>
+        <v>7092957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,48 +3552,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126915590</v>
+        <v>126919071</v>
       </c>
       <c r="B30" t="n">
-        <v>58492</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>674272</v>
+        <v>673738</v>
       </c>
       <c r="R30" t="n">
-        <v>7092912</v>
+        <v>7092907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3649,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3665,32 +3665,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126918783</v>
+        <v>126913209</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>674284</v>
+        <v>674212</v>
       </c>
       <c r="R31" t="n">
-        <v>7093057</v>
+        <v>7092826</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,12 +3750,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3769,7 +3769,7 @@
         <v>126919043</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3867,32 +3867,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126913209</v>
+        <v>126918783</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>674212</v>
+        <v>674284</v>
       </c>
       <c r="R33" t="n">
-        <v>7092826</v>
+        <v>7093057</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,12 +3952,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3968,7 +3968,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126918803</v>
+        <v>126912691</v>
       </c>
       <c r="B34" t="n">
         <v>79018</v>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>674314</v>
+        <v>674239</v>
       </c>
       <c r="R34" t="n">
-        <v>7093009</v>
+        <v>7092910</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,23 +4053,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912681</v>
+        <v>126918803</v>
       </c>
       <c r="B35" t="n">
         <v>79018</v>
@@ -4104,10 +4100,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>674304</v>
+        <v>674314</v>
       </c>
       <c r="R35" t="n">
-        <v>7093019</v>
+        <v>7093009</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,22 +4150,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919009</v>
+        <v>126912635</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673944</v>
+        <v>674239</v>
       </c>
       <c r="R36" t="n">
-        <v>7093050</v>
+        <v>7092908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,11 +4239,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På äldre tall, stam.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4256,23 +4251,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919008</v>
+        <v>126919009</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4307,10 +4298,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673843</v>
+        <v>673944</v>
       </c>
       <c r="R37" t="n">
-        <v>7093104</v>
+        <v>7093050</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4343,6 +4334,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På äldre tall, stam.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4373,7 +4369,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912691</v>
+        <v>126919078</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4408,10 +4404,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>674239</v>
+        <v>673893</v>
       </c>
       <c r="R38" t="n">
-        <v>7092910</v>
+        <v>7092920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,22 +4454,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912635</v>
+        <v>126919008</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>674239</v>
+        <v>673843</v>
       </c>
       <c r="R39" t="n">
-        <v>7092908</v>
+        <v>7093104</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,19 +4555,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919078</v>
+        <v>126912681</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4602,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673893</v>
+        <v>674304</v>
       </c>
       <c r="R40" t="n">
-        <v>7092920</v>
+        <v>7093019</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,26 +4656,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>126913201</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,32 +4769,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126915572</v>
+        <v>126912685</v>
       </c>
       <c r="B42" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>674324</v>
+        <v>674236</v>
       </c>
       <c r="R42" t="n">
-        <v>7093076</v>
+        <v>7092969</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,23 +4854,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912685</v>
+        <v>126912666</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -4905,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>674236</v>
+        <v>674176</v>
       </c>
       <c r="R43" t="n">
-        <v>7092969</v>
+        <v>7093061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,32 +4963,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912666</v>
+        <v>126915572</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +4998,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>674176</v>
+        <v>674324</v>
       </c>
       <c r="R44" t="n">
-        <v>7093061</v>
+        <v>7093076</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,19 +5048,23 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913207</v>
+        <v>126912683</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>674182</v>
+        <v>674310</v>
       </c>
       <c r="R45" t="n">
-        <v>7092837</v>
+        <v>7092998</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,19 +5149,15 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5266,7 +5262,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919074</v>
+        <v>126913207</v>
       </c>
       <c r="B47" t="n">
         <v>79018</v>
@@ -5301,10 +5297,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673796</v>
+        <v>674182</v>
       </c>
       <c r="R47" t="n">
-        <v>7092899</v>
+        <v>7092837</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5347,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5367,7 +5363,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126912683</v>
+        <v>126919074</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5402,10 +5398,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>674310</v>
+        <v>673796</v>
       </c>
       <c r="R48" t="n">
-        <v>7092998</v>
+        <v>7092899</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,22 +5448,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126915612</v>
+        <v>126918790</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>674198</v>
+        <v>674101</v>
       </c>
       <c r="R49" t="n">
-        <v>7092843</v>
+        <v>7092979</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,12 +5549,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5565,10 +5565,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126918790</v>
+        <v>126915612</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>674101</v>
+        <v>674198</v>
       </c>
       <c r="R50" t="n">
-        <v>7092979</v>
+        <v>7092843</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126913208</v>
+        <v>126912576</v>
       </c>
       <c r="B51" t="n">
-        <v>91280</v>
+        <v>79636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>674181</v>
+        <v>674200</v>
       </c>
       <c r="R51" t="n">
-        <v>7092836</v>
+        <v>7092950</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5751,48 +5751,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919076</v>
+        <v>126915630</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5802,10 +5798,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>673836</v>
+        <v>674328</v>
       </c>
       <c r="R52" t="n">
-        <v>7092910</v>
+        <v>7092980</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5852,12 +5848,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5868,32 +5864,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912576</v>
+        <v>126912700</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>98365</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5903,10 +5899,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>674200</v>
+        <v>674267</v>
       </c>
       <c r="R53" t="n">
-        <v>7092950</v>
+        <v>7093044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5965,48 +5961,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913179</v>
+        <v>126913208</v>
       </c>
       <c r="B54" t="n">
-        <v>80025</v>
+        <v>91280</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>673719</v>
+        <v>674181</v>
       </c>
       <c r="R54" t="n">
-        <v>7093035</v>
+        <v>7092836</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,7 +6040,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6070,32 +6062,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126915608</v>
+        <v>126919076</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6105,10 +6097,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>674257</v>
+        <v>673836</v>
       </c>
       <c r="R55" t="n">
-        <v>7092823</v>
+        <v>7092910</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6155,12 +6147,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6171,50 +6163,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126913214</v>
+        <v>126913179</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>80025</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6222,10 +6201,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>674219</v>
+        <v>673719</v>
       </c>
       <c r="R56" t="n">
-        <v>7092815</v>
+        <v>7093035</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6289,32 +6268,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126915630</v>
+        <v>126915608</v>
       </c>
       <c r="B57" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6324,10 +6303,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>674328</v>
+        <v>674257</v>
       </c>
       <c r="R57" t="n">
-        <v>7092980</v>
+        <v>7092823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,45 +6369,61 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912700</v>
+        <v>126913214</v>
       </c>
       <c r="B58" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>674267</v>
+        <v>674219</v>
       </c>
       <c r="R58" t="n">
-        <v>7093044</v>
+        <v>7092815</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6469,21 +6464,26 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6588,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126918806</v>
+        <v>126912592</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>674216</v>
+        <v>674188</v>
       </c>
       <c r="R60" t="n">
-        <v>7092860</v>
+        <v>7092955</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6673,48 +6673,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912687</v>
+        <v>126918996</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6720,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>674226</v>
+        <v>673948</v>
       </c>
       <c r="R61" t="n">
-        <v>7092929</v>
+        <v>7093016</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6774,22 +6770,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912592</v>
+        <v>126912617</v>
       </c>
       <c r="B62" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>674188</v>
+        <v>674214</v>
       </c>
       <c r="R62" t="n">
-        <v>7092955</v>
+        <v>7092881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6883,32 +6883,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126918996</v>
+        <v>126919039</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>98448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673948</v>
+        <v>673525</v>
       </c>
       <c r="R63" t="n">
-        <v>7093016</v>
+        <v>7093040</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6968,12 +6968,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6984,32 +6984,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126919031</v>
+        <v>126913211</v>
       </c>
       <c r="B64" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673796</v>
+        <v>674214</v>
       </c>
       <c r="R64" t="n">
-        <v>7092899</v>
+        <v>7092818</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,12 +7069,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7085,10 +7085,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126912617</v>
+        <v>126918787</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>674214</v>
+        <v>674167</v>
       </c>
       <c r="R65" t="n">
-        <v>7092881</v>
+        <v>7092848</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7170,22 +7170,26 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126918787</v>
+        <v>126915584</v>
       </c>
       <c r="B66" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7217,10 +7221,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>674167</v>
+        <v>674316</v>
       </c>
       <c r="R66" t="n">
-        <v>7092848</v>
+        <v>7092989</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7267,12 +7271,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7283,32 +7287,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126915584</v>
+        <v>126918806</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7318,10 +7322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>674316</v>
+        <v>674216</v>
       </c>
       <c r="R67" t="n">
-        <v>7092989</v>
+        <v>7092860</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,12 +7372,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7384,10 +7388,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126912622</v>
+        <v>126912687</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7395,21 +7399,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7419,10 +7423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>674225</v>
+        <v>674226</v>
       </c>
       <c r="R68" t="n">
-        <v>7092965</v>
+        <v>7092929</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7481,10 +7485,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126912620</v>
+        <v>126919031</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7492,21 +7496,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7516,10 +7520,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>674229</v>
+        <v>673796</v>
       </c>
       <c r="R69" t="n">
-        <v>7092964</v>
+        <v>7092899</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7566,19 +7570,23 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126918999</v>
+        <v>126912622</v>
       </c>
       <c r="B70" t="n">
         <v>78777</v>
@@ -7613,10 +7621,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>673919</v>
+        <v>674225</v>
       </c>
       <c r="R70" t="n">
-        <v>7093017</v>
+        <v>7092965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7663,48 +7671,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126919039</v>
+        <v>126912620</v>
       </c>
       <c r="B71" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7714,10 +7718,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>673525</v>
+        <v>674229</v>
       </c>
       <c r="R71" t="n">
-        <v>7093040</v>
+        <v>7092964</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,48 +7768,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126913211</v>
+        <v>126918999</v>
       </c>
       <c r="B72" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>674214</v>
+        <v>673919</v>
       </c>
       <c r="R72" t="n">
-        <v>7092818</v>
+        <v>7093017</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,12 +7865,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126912680</v>
+        <v>126912590</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,34 +7892,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>674302</v>
+        <v>673958</v>
       </c>
       <c r="R73" t="n">
-        <v>7093031</v>
+        <v>7093109</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7978,10 +7983,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912579</v>
+        <v>126912680</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,21 +7994,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8013,10 +8018,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>674239</v>
+        <v>674302</v>
       </c>
       <c r="R74" t="n">
-        <v>7092908</v>
+        <v>7093031</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8176,10 +8181,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126912590</v>
+        <v>126912579</v>
       </c>
       <c r="B76" t="n">
-        <v>57821</v>
+        <v>79636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8187,39 +8192,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>673958</v>
+        <v>674239</v>
       </c>
       <c r="R76" t="n">
-        <v>7093109</v>
+        <v>7092908</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,32 +8375,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126918795</v>
+        <v>126913210</v>
       </c>
       <c r="B78" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>674236</v>
+        <v>674282</v>
       </c>
       <c r="R78" t="n">
-        <v>7092852</v>
+        <v>7092828</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,12 +8460,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8476,50 +8476,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126912599</v>
+        <v>126912669</v>
       </c>
       <c r="B79" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>674251</v>
+        <v>674218</v>
       </c>
       <c r="R79" t="n">
-        <v>7093028</v>
+        <v>7093013</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8578,7 +8573,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126912669</v>
+        <v>126918802</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -8613,10 +8608,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>674218</v>
+        <v>674315</v>
       </c>
       <c r="R80" t="n">
-        <v>7093013</v>
+        <v>7093023</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8663,44 +8658,48 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126913210</v>
+        <v>126918795</v>
       </c>
       <c r="B81" t="n">
-        <v>80150</v>
+        <v>98448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8710,10 +8709,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>674282</v>
+        <v>674236</v>
       </c>
       <c r="R81" t="n">
-        <v>7092828</v>
+        <v>7092852</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8760,12 +8759,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8776,45 +8775,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126918802</v>
+        <v>126912599</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>674315</v>
+        <v>674251</v>
       </c>
       <c r="R82" t="n">
-        <v>7093023</v>
+        <v>7093028</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8861,48 +8865,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126919037</v>
+        <v>126912674</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>673555</v>
+        <v>674251</v>
       </c>
       <c r="R83" t="n">
-        <v>7093132</v>
+        <v>7093028</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8962,48 +8962,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126915607</v>
+        <v>126912618</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9013,10 +9009,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>674262</v>
+        <v>674104</v>
       </c>
       <c r="R84" t="n">
-        <v>7092824</v>
+        <v>7092938</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9063,23 +9059,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126912674</v>
+        <v>126912668</v>
       </c>
       <c r="B85" t="n">
         <v>79018</v>
@@ -9114,10 +9106,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>674251</v>
+        <v>674214</v>
       </c>
       <c r="R85" t="n">
-        <v>7093028</v>
+        <v>7093041</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9176,7 +9168,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126912668</v>
+        <v>126912672</v>
       </c>
       <c r="B86" t="n">
         <v>79018</v>
@@ -9211,10 +9203,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>674214</v>
+        <v>674248</v>
       </c>
       <c r="R86" t="n">
-        <v>7093041</v>
+        <v>7093018</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9273,10 +9265,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126912618</v>
+        <v>126912699</v>
       </c>
       <c r="B87" t="n">
-        <v>80149</v>
+        <v>98365</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9284,21 +9276,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9308,10 +9300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>674104</v>
+        <v>674260</v>
       </c>
       <c r="R87" t="n">
-        <v>7092938</v>
+        <v>7093031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9370,32 +9362,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126912672</v>
+        <v>126915607</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9405,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>674248</v>
+        <v>674262</v>
       </c>
       <c r="R88" t="n">
-        <v>7093018</v>
+        <v>7092824</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9455,44 +9447,48 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126912699</v>
+        <v>126913212</v>
       </c>
       <c r="B89" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9502,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>674260</v>
+        <v>674207</v>
       </c>
       <c r="R89" t="n">
-        <v>7093031</v>
+        <v>7092818</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9552,22 +9548,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126913212</v>
+        <v>126919037</v>
       </c>
       <c r="B90" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>674207</v>
+        <v>673555</v>
       </c>
       <c r="R90" t="n">
-        <v>7092818</v>
+        <v>7093132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,10 +9665,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126918807</v>
+        <v>126912703</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>674208</v>
+        <v>674269</v>
       </c>
       <c r="R91" t="n">
-        <v>7092856</v>
+        <v>7092979</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9750,23 +9750,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126912578</v>
+        <v>126918984</v>
       </c>
       <c r="B92" t="n">
         <v>79636</v>
@@ -9801,10 +9797,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>674218</v>
+        <v>673919</v>
       </c>
       <c r="R92" t="n">
-        <v>7092914</v>
+        <v>7093017</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9851,44 +9847,48 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126913181</v>
+        <v>126912614</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>674236</v>
+        <v>674319</v>
       </c>
       <c r="R93" t="n">
-        <v>7093024</v>
+        <v>7093047</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9948,48 +9948,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126919072</v>
+        <v>126915610</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9999,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>673738</v>
+        <v>674211</v>
       </c>
       <c r="R94" t="n">
-        <v>7092885</v>
+        <v>7092807</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10049,12 +10045,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10065,32 +10061,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126912614</v>
+        <v>126912578</v>
       </c>
       <c r="B95" t="n">
-        <v>80149</v>
+        <v>79636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10100,10 +10096,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>674319</v>
+        <v>674218</v>
       </c>
       <c r="R95" t="n">
-        <v>7093047</v>
+        <v>7092914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10162,10 +10158,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126912634</v>
+        <v>126918807</v>
       </c>
       <c r="B96" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10173,21 +10169,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10197,10 +10193,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>674203</v>
+        <v>674208</v>
       </c>
       <c r="R96" t="n">
-        <v>7092932</v>
+        <v>7092856</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10247,22 +10243,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126918789</v>
+        <v>126913181</v>
       </c>
       <c r="B97" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10270,21 +10270,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>674310</v>
+        <v>674236</v>
       </c>
       <c r="R97" t="n">
-        <v>7092997</v>
+        <v>7093024</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,12 +10344,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10360,10 +10360,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126918984</v>
+        <v>126919072</v>
       </c>
       <c r="B98" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10371,21 +10371,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>673919</v>
+        <v>673738</v>
       </c>
       <c r="R98" t="n">
-        <v>7093017</v>
+        <v>7092885</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10445,12 +10445,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10461,32 +10461,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126915610</v>
+        <v>126912634</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>674211</v>
+        <v>674203</v>
       </c>
       <c r="R99" t="n">
-        <v>7092807</v>
+        <v>7092932</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10546,48 +10546,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126915609</v>
+        <v>126918789</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10597,10 +10593,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>674231</v>
+        <v>674310</v>
       </c>
       <c r="R100" t="n">
-        <v>7092812</v>
+        <v>7092997</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10647,12 +10643,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10663,32 +10659,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126912624</v>
+        <v>126915609</v>
       </c>
       <c r="B101" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10698,10 +10694,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>674218</v>
+        <v>674231</v>
       </c>
       <c r="R101" t="n">
-        <v>7092914</v>
+        <v>7092812</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10748,22 +10744,26 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126912703</v>
+        <v>126912624</v>
       </c>
       <c r="B102" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10771,21 +10771,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>674269</v>
+        <v>674218</v>
       </c>
       <c r="R102" t="n">
-        <v>7092979</v>
+        <v>7092914</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10857,45 +10857,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126912575</v>
+        <v>126912637</v>
       </c>
       <c r="B103" t="n">
-        <v>79636</v>
+        <v>98448</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>674215</v>
+        <v>674166</v>
       </c>
       <c r="R103" t="n">
-        <v>7092959</v>
+        <v>7092881</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,32 +10963,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126912679</v>
+        <v>126915582</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10989,10 +10998,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>674324</v>
+        <v>674302</v>
       </c>
       <c r="R104" t="n">
-        <v>7093051</v>
+        <v>7093071</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11039,22 +11048,26 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126912671</v>
+        <v>126912575</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11062,21 +11075,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11086,10 +11099,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>674238</v>
+        <v>674215</v>
       </c>
       <c r="R105" t="n">
-        <v>7093012</v>
+        <v>7092959</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11161,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126913197</v>
+        <v>126912679</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11183,10 +11196,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>673791</v>
+        <v>674324</v>
       </c>
       <c r="R106" t="n">
-        <v>7092931</v>
+        <v>7093051</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11233,26 +11246,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126912572</v>
+        <v>126912671</v>
       </c>
       <c r="B107" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11260,21 +11269,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11284,10 +11293,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>674310</v>
+        <v>674238</v>
       </c>
       <c r="R107" t="n">
-        <v>7092998</v>
+        <v>7093012</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11346,45 +11355,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126912686</v>
+        <v>126912642</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>674222</v>
+        <v>674117</v>
       </c>
       <c r="R108" t="n">
-        <v>7092926</v>
+        <v>7092933</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11443,54 +11461,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126912637</v>
+        <v>126913197</v>
       </c>
       <c r="B109" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>674166</v>
+        <v>673791</v>
       </c>
       <c r="R109" t="n">
-        <v>7092881</v>
+        <v>7092931</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11537,66 +11546,61 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126912642</v>
+        <v>126912572</v>
       </c>
       <c r="B110" t="n">
-        <v>98447</v>
+        <v>79636</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kvarnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>674117</v>
+        <v>674310</v>
       </c>
       <c r="R110" t="n">
-        <v>7092933</v>
+        <v>7092998</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11655,32 +11659,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126915582</v>
+        <v>126912686</v>
       </c>
       <c r="B111" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11690,10 +11694,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>674302</v>
+        <v>674222</v>
       </c>
       <c r="R111" t="n">
-        <v>7093071</v>
+        <v>7092926</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11740,48 +11744,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126915628</v>
+        <v>126912689</v>
       </c>
       <c r="B112" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>674258</v>
+        <v>674237</v>
       </c>
       <c r="R112" t="n">
-        <v>7093046</v>
+        <v>7092921</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11841,23 +11841,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126912689</v>
+        <v>126918801</v>
       </c>
       <c r="B113" t="n">
         <v>79018</v>
@@ -11892,10 +11888,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>674237</v>
+        <v>674148</v>
       </c>
       <c r="R113" t="n">
-        <v>7092921</v>
+        <v>7093061</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11942,22 +11938,26 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126918801</v>
+        <v>126912577</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>674148</v>
+        <v>674204</v>
       </c>
       <c r="R114" t="n">
-        <v>7093061</v>
+        <v>7092934</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12039,19 +12039,15 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12156,32 +12152,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126912577</v>
+        <v>126915628</v>
       </c>
       <c r="B116" t="n">
-        <v>79636</v>
+        <v>98365</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12191,10 +12187,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>674204</v>
+        <v>674258</v>
       </c>
       <c r="R116" t="n">
-        <v>7092934</v>
+        <v>7093046</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12241,15 +12237,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12455,10 +12455,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126918808</v>
+        <v>126912708</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>77996</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12466,21 +12466,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12490,10 +12490,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>674199</v>
+        <v>674243</v>
       </c>
       <c r="R119" t="n">
-        <v>7092849</v>
+        <v>7092914</v>
       </c>
       <c r="S119" t="n"